--- a/assets/testing_data/complete_testing.xlsx
+++ b/assets/testing_data/complete_testing.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,20 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anema\OneDrive\Documenten\GitHub\Risky-Game-Development\assets\testing_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{366CA6BF-5AF7-446C-9802-884D485E007C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2934D10-EA3A-41AB-A2B1-C91C81C847E8}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="complete_testing" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1564" uniqueCount="22">
   <si>
     <t>Player-1</t>
   </si>
@@ -80,13 +91,19 @@
     <t>Player-2</t>
   </si>
   <si>
-    <t>Number of wins</t>
+    <t>Number of wins for P1</t>
+  </si>
+  <si>
+    <t>Percentage wins for P1</t>
+  </si>
+  <si>
+    <t>Total number of tests</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -223,7 +240,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -403,6 +420,18 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -533,7 +562,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -576,19 +605,21 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -628,6 +659,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Percent" xfId="42" builtinId="5"/>
     <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
@@ -646,18 +678,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F735" totalsRowShown="0">
-  <autoFilter ref="A1:F735"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F735" totalsRowShown="0">
+  <autoFilter ref="A1:F735" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F735">
     <sortCondition ref="A1:A735"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" name="Player-1"/>
-    <tableColumn id="2" name="Player-2"/>
-    <tableColumn id="3" name=" Winner"/>
-    <tableColumn id="4" name=" Number of Players"/>
-    <tableColumn id="5" name=" Time (ns)"/>
-    <tableColumn id="6" name="Time (min)">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Player-1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Player-2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name=" Winner"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name=" Number of Players"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name=" Time (ns)"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Time (min)">
       <calculatedColumnFormula>ROUND(E2/60000000000, 1)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -961,7 +993,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F735"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1010,7 +1042,7 @@
         <v>8876136918400</v>
       </c>
       <c r="F2">
-        <f>ROUND(E2/60000000000, 1)</f>
+        <f t="shared" ref="F2:F65" si="0">ROUND(E2/60000000000, 1)</f>
         <v>147.9</v>
       </c>
     </row>
@@ -1031,7 +1063,7 @@
         <v>32834154132700</v>
       </c>
       <c r="F3">
-        <f>ROUND(E3/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>547.20000000000005</v>
       </c>
     </row>
@@ -1052,7 +1084,7 @@
         <v>18138288906500</v>
       </c>
       <c r="F4">
-        <f>ROUND(E4/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>302.3</v>
       </c>
     </row>
@@ -1073,7 +1105,7 @@
         <v>12500538078100</v>
       </c>
       <c r="F5">
-        <f>ROUND(E5/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>208.3</v>
       </c>
     </row>
@@ -1094,7 +1126,7 @@
         <v>31880323223700</v>
       </c>
       <c r="F6">
-        <f>ROUND(E6/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>531.29999999999995</v>
       </c>
     </row>
@@ -1115,7 +1147,7 @@
         <v>8179575393300</v>
       </c>
       <c r="F7">
-        <f>ROUND(E7/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>136.30000000000001</v>
       </c>
     </row>
@@ -1136,7 +1168,7 @@
         <v>3468190450466</v>
       </c>
       <c r="F8">
-        <f>ROUND(E8/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>57.8</v>
       </c>
     </row>
@@ -1157,7 +1189,7 @@
         <v>16318453030700</v>
       </c>
       <c r="F9">
-        <f>ROUND(E9/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>272</v>
       </c>
     </row>
@@ -1178,7 +1210,7 @@
         <v>6433953824000</v>
       </c>
       <c r="F10">
-        <f>ROUND(E10/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>107.2</v>
       </c>
     </row>
@@ -1199,7 +1231,7 @@
         <v>3981663976299</v>
       </c>
       <c r="F11">
-        <f>ROUND(E11/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>66.400000000000006</v>
       </c>
     </row>
@@ -1220,7 +1252,7 @@
         <v>11349091871700</v>
       </c>
       <c r="F12">
-        <f>ROUND(E12/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>189.2</v>
       </c>
     </row>
@@ -1241,7 +1273,7 @@
         <v>8805447791100</v>
       </c>
       <c r="F13">
-        <f>ROUND(E13/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>146.80000000000001</v>
       </c>
     </row>
@@ -1262,7 +1294,7 @@
         <v>12855966365999</v>
       </c>
       <c r="F14">
-        <f>ROUND(E14/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>214.3</v>
       </c>
     </row>
@@ -1283,7 +1315,7 @@
         <v>5185425381000</v>
       </c>
       <c r="F15">
-        <f>ROUND(E15/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>86.4</v>
       </c>
     </row>
@@ -1304,7 +1336,7 @@
         <v>5848858848900</v>
       </c>
       <c r="F16">
-        <f>ROUND(E16/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>97.5</v>
       </c>
     </row>
@@ -1325,7 +1357,7 @@
         <v>3314068318368</v>
       </c>
       <c r="F17">
-        <f>ROUND(E17/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>55.2</v>
       </c>
     </row>
@@ -1346,7 +1378,7 @@
         <v>5853687094300</v>
       </c>
       <c r="F18">
-        <f>ROUND(E18/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>97.6</v>
       </c>
     </row>
@@ -1367,7 +1399,7 @@
         <v>8896041715300</v>
       </c>
       <c r="F19">
-        <f>ROUND(E19/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>148.30000000000001</v>
       </c>
     </row>
@@ -1388,7 +1420,7 @@
         <v>99991433500</v>
       </c>
       <c r="F20">
-        <f>ROUND(E20/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>1.7</v>
       </c>
     </row>
@@ -1409,7 +1441,7 @@
         <v>63241219300</v>
       </c>
       <c r="F21">
-        <f>ROUND(E21/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
     </row>
@@ -1430,7 +1462,7 @@
         <v>318901912499</v>
       </c>
       <c r="F22">
-        <f>ROUND(E22/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>5.3</v>
       </c>
     </row>
@@ -1451,7 +1483,7 @@
         <v>75343411500</v>
       </c>
       <c r="F23">
-        <f>ROUND(E23/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>1.3</v>
       </c>
     </row>
@@ -1472,7 +1504,7 @@
         <v>60804980700</v>
       </c>
       <c r="F24">
-        <f>ROUND(E24/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1493,7 +1525,7 @@
         <v>161451832500</v>
       </c>
       <c r="F25">
-        <f>ROUND(E25/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>2.7</v>
       </c>
     </row>
@@ -1514,7 +1546,7 @@
         <v>71187154600</v>
       </c>
       <c r="F26">
-        <f>ROUND(E26/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
     </row>
@@ -1535,7 +1567,7 @@
         <v>27767814373</v>
       </c>
       <c r="F27">
-        <f>ROUND(E27/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
     </row>
@@ -1556,7 +1588,7 @@
         <v>24582179010</v>
       </c>
       <c r="F28">
-        <f>ROUND(E28/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
     </row>
@@ -1577,7 +1609,7 @@
         <v>12476160401</v>
       </c>
       <c r="F29">
-        <f>ROUND(E29/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
     </row>
@@ -1598,7 +1630,7 @@
         <v>89572992600</v>
       </c>
       <c r="F30">
-        <f>ROUND(E30/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
     </row>
@@ -1619,7 +1651,7 @@
         <v>54134925400</v>
       </c>
       <c r="F31">
-        <f>ROUND(E31/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>0.9</v>
       </c>
     </row>
@@ -1640,7 +1672,7 @@
         <v>44898988000</v>
       </c>
       <c r="F32">
-        <f>ROUND(E32/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
@@ -1661,7 +1693,7 @@
         <v>450283972900</v>
       </c>
       <c r="F33">
-        <f>ROUND(E33/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
     </row>
@@ -1682,7 +1714,7 @@
         <v>50569781200</v>
       </c>
       <c r="F34">
-        <f>ROUND(E34/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
     </row>
@@ -1703,7 +1735,7 @@
         <v>13446274600</v>
       </c>
       <c r="F35">
-        <f>ROUND(E35/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
     </row>
@@ -1724,7 +1756,7 @@
         <v>15402433400</v>
       </c>
       <c r="F36">
-        <f>ROUND(E36/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>0.3</v>
       </c>
     </row>
@@ -1745,7 +1777,7 @@
         <v>53091907700</v>
       </c>
       <c r="F37">
-        <f>ROUND(E37/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>0.9</v>
       </c>
     </row>
@@ -1766,7 +1798,7 @@
         <v>125541736500</v>
       </c>
       <c r="F38">
-        <f>ROUND(E38/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>2.1</v>
       </c>
     </row>
@@ -1787,7 +1819,7 @@
         <v>61850281300</v>
       </c>
       <c r="F39">
-        <f>ROUND(E39/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1808,7 +1840,7 @@
         <v>49838625200</v>
       </c>
       <c r="F40">
-        <f>ROUND(E40/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
     </row>
@@ -1829,7 +1861,7 @@
         <v>31414870195</v>
       </c>
       <c r="F41">
-        <f>ROUND(E41/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
     </row>
@@ -1850,7 +1882,7 @@
         <v>53304387900</v>
       </c>
       <c r="F42">
-        <f>ROUND(E42/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>0.9</v>
       </c>
     </row>
@@ -1871,7 +1903,7 @@
         <v>1902021055698</v>
       </c>
       <c r="F43">
-        <f>ROUND(E43/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>31.7</v>
       </c>
     </row>
@@ -1892,7 +1924,7 @@
         <v>15517200079700</v>
       </c>
       <c r="F44">
-        <f>ROUND(E44/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>258.60000000000002</v>
       </c>
     </row>
@@ -1913,7 +1945,7 @@
         <v>4248586866300</v>
       </c>
       <c r="F45">
-        <f>ROUND(E45/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>70.8</v>
       </c>
     </row>
@@ -1934,7 +1966,7 @@
         <v>1469661155711</v>
       </c>
       <c r="F46">
-        <f>ROUND(E46/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>24.5</v>
       </c>
     </row>
@@ -1955,7 +1987,7 @@
         <v>3373860446800</v>
       </c>
       <c r="F47">
-        <f>ROUND(E47/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>56.2</v>
       </c>
     </row>
@@ -1976,7 +2008,7 @@
         <v>3666442499700</v>
       </c>
       <c r="F48">
-        <f>ROUND(E48/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>61.1</v>
       </c>
     </row>
@@ -1997,7 +2029,7 @@
         <v>5121588547500</v>
       </c>
       <c r="F49">
-        <f>ROUND(E49/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>85.4</v>
       </c>
     </row>
@@ -2018,7 +2050,7 @@
         <v>123780890800</v>
       </c>
       <c r="F50">
-        <f>ROUND(E50/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>2.1</v>
       </c>
     </row>
@@ -2039,7 +2071,7 @@
         <v>169056542300</v>
       </c>
       <c r="F51">
-        <f>ROUND(E51/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>2.8</v>
       </c>
     </row>
@@ -2060,7 +2092,7 @@
         <v>149357372800</v>
       </c>
       <c r="F52">
-        <f>ROUND(E52/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
     </row>
@@ -2081,7 +2113,7 @@
         <v>114289218400</v>
       </c>
       <c r="F53">
-        <f>ROUND(E53/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>1.9</v>
       </c>
     </row>
@@ -2102,7 +2134,7 @@
         <v>105544852500</v>
       </c>
       <c r="F54">
-        <f>ROUND(E54/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>1.8</v>
       </c>
     </row>
@@ -2123,7 +2155,7 @@
         <v>111579082600</v>
       </c>
       <c r="F55">
-        <f>ROUND(E55/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>1.9</v>
       </c>
     </row>
@@ -2144,7 +2176,7 @@
         <v>57854461653</v>
       </c>
       <c r="F56">
-        <f>ROUND(E56/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2165,7 +2197,7 @@
         <v>58482861607</v>
       </c>
       <c r="F57">
-        <f>ROUND(E57/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2186,7 +2218,7 @@
         <v>39459228820</v>
       </c>
       <c r="F58">
-        <f>ROUND(E58/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
@@ -2207,7 +2239,7 @@
         <v>37729349209</v>
       </c>
       <c r="F59">
-        <f>ROUND(E59/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
     </row>
@@ -2228,7 +2260,7 @@
         <v>87289833200</v>
       </c>
       <c r="F60">
-        <f>ROUND(E60/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
     </row>
@@ -2249,7 +2281,7 @@
         <v>161198628900</v>
       </c>
       <c r="F61">
-        <f>ROUND(E61/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>2.7</v>
       </c>
     </row>
@@ -2270,7 +2302,7 @@
         <v>128336003100</v>
       </c>
       <c r="F62">
-        <f>ROUND(E62/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>2.1</v>
       </c>
     </row>
@@ -2291,7 +2323,7 @@
         <v>982156018400</v>
       </c>
       <c r="F63">
-        <f>ROUND(E63/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>16.399999999999999</v>
       </c>
     </row>
@@ -2312,7 +2344,7 @@
         <v>155983105900</v>
       </c>
       <c r="F64">
-        <f>ROUND(E64/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>2.6</v>
       </c>
     </row>
@@ -2333,7 +2365,7 @@
         <v>40700246500</v>
       </c>
       <c r="F65">
-        <f>ROUND(E65/60000000000, 1)</f>
+        <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
@@ -2354,7 +2386,7 @@
         <v>51340921600</v>
       </c>
       <c r="F66">
-        <f>ROUND(E66/60000000000, 1)</f>
+        <f t="shared" ref="F66:F129" si="1">ROUND(E66/60000000000, 1)</f>
         <v>0.9</v>
       </c>
     </row>
@@ -2375,7 +2407,7 @@
         <v>209481731200</v>
       </c>
       <c r="F67">
-        <f>ROUND(E67/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>3.5</v>
       </c>
     </row>
@@ -2396,7 +2428,7 @@
         <v>469754923200</v>
       </c>
       <c r="F68">
-        <f>ROUND(E68/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>7.8</v>
       </c>
     </row>
@@ -2417,7 +2449,7 @@
         <v>39129827500</v>
       </c>
       <c r="F69">
-        <f>ROUND(E69/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
     </row>
@@ -2438,7 +2470,7 @@
         <v>202662585500</v>
       </c>
       <c r="F70">
-        <f>ROUND(E70/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>3.4</v>
       </c>
     </row>
@@ -2459,7 +2491,7 @@
         <v>385432267800</v>
       </c>
       <c r="F71">
-        <f>ROUND(E71/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>6.4</v>
       </c>
     </row>
@@ -2480,7 +2512,7 @@
         <v>51229257499</v>
       </c>
       <c r="F72">
-        <f>ROUND(E72/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
     </row>
@@ -2501,7 +2533,7 @@
         <v>183242736500</v>
       </c>
       <c r="F73">
-        <f>ROUND(E73/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>3.1</v>
       </c>
     </row>
@@ -2522,7 +2554,7 @@
         <v>472307211500</v>
       </c>
       <c r="F74">
-        <f>ROUND(E74/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>7.9</v>
       </c>
     </row>
@@ -2543,7 +2575,7 @@
         <v>39001102200</v>
       </c>
       <c r="F75">
-        <f>ROUND(E75/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
     </row>
@@ -2564,7 +2596,7 @@
         <v>189629431400</v>
       </c>
       <c r="F76">
-        <f>ROUND(E76/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>3.2</v>
       </c>
     </row>
@@ -2585,7 +2617,7 @@
         <v>426351297100</v>
       </c>
       <c r="F77">
-        <f>ROUND(E77/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>7.1</v>
       </c>
     </row>
@@ -2606,7 +2638,7 @@
         <v>49147964200</v>
       </c>
       <c r="F78">
-        <f>ROUND(E78/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
     </row>
@@ -2627,7 +2659,7 @@
         <v>224442927300</v>
       </c>
       <c r="F79">
-        <f>ROUND(E79/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>3.7</v>
       </c>
     </row>
@@ -2648,7 +2680,7 @@
         <v>456345155100</v>
       </c>
       <c r="F80">
-        <f>ROUND(E80/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>7.6</v>
       </c>
     </row>
@@ -2669,7 +2701,7 @@
         <v>45031294500</v>
       </c>
       <c r="F81">
-        <f>ROUND(E81/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
     </row>
@@ -2690,7 +2722,7 @@
         <v>240501788700</v>
       </c>
       <c r="F82">
-        <f>ROUND(E82/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -2711,7 +2743,7 @@
         <v>514811839200</v>
       </c>
       <c r="F83">
-        <f>ROUND(E83/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>8.6</v>
       </c>
     </row>
@@ -2732,7 +2764,7 @@
         <v>45103998400</v>
       </c>
       <c r="F84">
-        <f>ROUND(E84/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
     </row>
@@ -2753,7 +2785,7 @@
         <v>215679394300</v>
       </c>
       <c r="F85">
-        <f>ROUND(E85/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>3.6</v>
       </c>
     </row>
@@ -2774,7 +2806,7 @@
         <v>513427541500</v>
       </c>
       <c r="F86">
-        <f>ROUND(E86/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>8.6</v>
       </c>
     </row>
@@ -2795,7 +2827,7 @@
         <v>50479008800</v>
       </c>
       <c r="F87">
-        <f>ROUND(E87/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
     </row>
@@ -2816,7 +2848,7 @@
         <v>240112628200</v>
       </c>
       <c r="F88">
-        <f>ROUND(E88/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -2837,7 +2869,7 @@
         <v>576160495100</v>
       </c>
       <c r="F89">
-        <f>ROUND(E89/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>9.6</v>
       </c>
     </row>
@@ -2858,7 +2890,7 @@
         <v>43837870600</v>
       </c>
       <c r="F90">
-        <f>ROUND(E90/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
     </row>
@@ -2879,7 +2911,7 @@
         <v>297173196000</v>
       </c>
       <c r="F91">
-        <f>ROUND(E91/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
@@ -2900,7 +2932,7 @@
         <v>644012247500</v>
       </c>
       <c r="F92">
-        <f>ROUND(E92/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>10.7</v>
       </c>
     </row>
@@ -2921,7 +2953,7 @@
         <v>52872874800</v>
       </c>
       <c r="F93">
-        <f>ROUND(E93/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
     </row>
@@ -2942,7 +2974,7 @@
         <v>93940746600</v>
       </c>
       <c r="F94">
-        <f>ROUND(E94/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>1.6</v>
       </c>
     </row>
@@ -2963,7 +2995,7 @@
         <v>147866289100</v>
       </c>
       <c r="F95">
-        <f>ROUND(E95/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
     </row>
@@ -2984,7 +3016,7 @@
         <v>44967562672</v>
       </c>
       <c r="F96">
-        <f>ROUND(E96/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
     </row>
@@ -3005,7 +3037,7 @@
         <v>111899591700</v>
       </c>
       <c r="F97">
-        <f>ROUND(E97/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>1.9</v>
       </c>
     </row>
@@ -3026,7 +3058,7 @@
         <v>84820541901</v>
       </c>
       <c r="F98">
-        <f>ROUND(E98/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>1.4</v>
       </c>
     </row>
@@ -3047,7 +3079,7 @@
         <v>75999611300</v>
       </c>
       <c r="F99">
-        <f>ROUND(E99/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>1.3</v>
       </c>
     </row>
@@ -3068,7 +3100,7 @@
         <v>339562421300</v>
       </c>
       <c r="F100">
-        <f>ROUND(E100/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>5.7</v>
       </c>
     </row>
@@ -3089,7 +3121,7 @@
         <v>306667976199</v>
       </c>
       <c r="F101">
-        <f>ROUND(E101/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>5.0999999999999996</v>
       </c>
     </row>
@@ -3110,7 +3142,7 @@
         <v>46983435100</v>
       </c>
       <c r="F102">
-        <f>ROUND(E102/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
     </row>
@@ -3131,7 +3163,7 @@
         <v>173589219000</v>
       </c>
       <c r="F103">
-        <f>ROUND(E103/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>2.9</v>
       </c>
     </row>
@@ -3152,7 +3184,7 @@
         <v>147196253400</v>
       </c>
       <c r="F104">
-        <f>ROUND(E104/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
     </row>
@@ -3173,7 +3205,7 @@
         <v>33286959335</v>
       </c>
       <c r="F105">
-        <f>ROUND(E105/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
     </row>
@@ -3194,7 +3226,7 @@
         <v>32175422218</v>
       </c>
       <c r="F106">
-        <f>ROUND(E106/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
     </row>
@@ -3215,7 +3247,7 @@
         <v>37496887115</v>
       </c>
       <c r="F107">
-        <f>ROUND(E107/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
     </row>
@@ -3236,7 +3268,7 @@
         <v>183173497800</v>
       </c>
       <c r="F108">
-        <f>ROUND(E108/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>3.1</v>
       </c>
     </row>
@@ -3257,7 +3289,7 @@
         <v>40627806500</v>
       </c>
       <c r="F109">
-        <f>ROUND(E109/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
     </row>
@@ -3278,7 +3310,7 @@
         <v>17113819400</v>
       </c>
       <c r="F110">
-        <f>ROUND(E110/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
     </row>
@@ -3299,7 +3331,7 @@
         <v>53488643300</v>
       </c>
       <c r="F111">
-        <f>ROUND(E111/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
     </row>
@@ -3320,7 +3352,7 @@
         <v>118322932500</v>
       </c>
       <c r="F112">
-        <f>ROUND(E112/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -3341,7 +3373,7 @@
         <v>69223260600</v>
       </c>
       <c r="F113">
-        <f>ROUND(E113/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
     </row>
@@ -3362,7 +3394,7 @@
         <v>53198071100</v>
       </c>
       <c r="F114">
-        <f>ROUND(E114/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
     </row>
@@ -3383,7 +3415,7 @@
         <v>14477763724</v>
       </c>
       <c r="F115">
-        <f>ROUND(E115/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.2</v>
       </c>
     </row>
@@ -3404,7 +3436,7 @@
         <v>169394398700</v>
       </c>
       <c r="F116">
-        <f>ROUND(E116/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>2.8</v>
       </c>
     </row>
@@ -3425,7 +3457,7 @@
         <v>105351359900</v>
       </c>
       <c r="F117">
-        <f>ROUND(E117/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>1.8</v>
       </c>
     </row>
@@ -3446,7 +3478,7 @@
         <v>186784206900</v>
       </c>
       <c r="F118">
-        <f>ROUND(E118/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>3.1</v>
       </c>
     </row>
@@ -3467,7 +3499,7 @@
         <v>86479305400</v>
       </c>
       <c r="F119">
-        <f>ROUND(E119/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>1.4</v>
       </c>
     </row>
@@ -3488,7 +3520,7 @@
         <v>71290994500</v>
       </c>
       <c r="F120">
-        <f>ROUND(E120/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
     </row>
@@ -3509,7 +3541,7 @@
         <v>61296231100</v>
       </c>
       <c r="F121">
-        <f>ROUND(E121/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3530,7 +3562,7 @@
         <v>52088800700</v>
       </c>
       <c r="F122">
-        <f>ROUND(E122/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
     </row>
@@ -3551,7 +3583,7 @@
         <v>68387772500</v>
       </c>
       <c r="F123">
-        <f>ROUND(E123/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
     </row>
@@ -3572,7 +3604,7 @@
         <v>64519277800</v>
       </c>
       <c r="F124">
-        <f>ROUND(E124/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
     </row>
@@ -3593,7 +3625,7 @@
         <v>19814321942</v>
       </c>
       <c r="F125">
-        <f>ROUND(E125/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
     </row>
@@ -3614,7 +3646,7 @@
         <v>18573275991</v>
       </c>
       <c r="F126">
-        <f>ROUND(E126/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
     </row>
@@ -3635,7 +3667,7 @@
         <v>14943522929</v>
       </c>
       <c r="F127">
-        <f>ROUND(E127/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.2</v>
       </c>
     </row>
@@ -3656,7 +3688,7 @@
         <v>42906083300</v>
       </c>
       <c r="F128">
-        <f>ROUND(E128/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
     </row>
@@ -3677,7 +3709,7 @@
         <v>89487187900</v>
       </c>
       <c r="F129">
-        <f>ROUND(E129/60000000000, 1)</f>
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
     </row>
@@ -3698,7 +3730,7 @@
         <v>19545187200</v>
       </c>
       <c r="F130">
-        <f>ROUND(E130/60000000000, 1)</f>
+        <f t="shared" ref="F130:F193" si="2">ROUND(E130/60000000000, 1)</f>
         <v>0.3</v>
       </c>
     </row>
@@ -3719,7 +3751,7 @@
         <v>15955517000</v>
       </c>
       <c r="F131">
-        <f>ROUND(E131/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
     </row>
@@ -3740,7 +3772,7 @@
         <v>107322931100</v>
       </c>
       <c r="F132">
-        <f>ROUND(E132/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>1.8</v>
       </c>
     </row>
@@ -3761,7 +3793,7 @@
         <v>120208962500</v>
       </c>
       <c r="F133">
-        <f>ROUND(E133/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
@@ -3782,7 +3814,7 @@
         <v>72527845400</v>
       </c>
       <c r="F134">
-        <f>ROUND(E134/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>1.2</v>
       </c>
     </row>
@@ -3803,7 +3835,7 @@
         <v>51714354400</v>
       </c>
       <c r="F135">
-        <f>ROUND(E135/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
     </row>
@@ -3824,7 +3856,7 @@
         <v>13138449517</v>
       </c>
       <c r="F136">
-        <f>ROUND(E136/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
     </row>
@@ -3845,7 +3877,7 @@
         <v>94872103400</v>
       </c>
       <c r="F137">
-        <f>ROUND(E137/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>1.6</v>
       </c>
     </row>
@@ -3866,7 +3898,7 @@
         <v>81126528301</v>
       </c>
       <c r="F138">
-        <f>ROUND(E138/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>1.4</v>
       </c>
     </row>
@@ -3887,7 +3919,7 @@
         <v>70054069199</v>
       </c>
       <c r="F139">
-        <f>ROUND(E139/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>1.2</v>
       </c>
     </row>
@@ -3908,7 +3940,7 @@
         <v>119259749100</v>
       </c>
       <c r="F140">
-        <f>ROUND(E140/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
@@ -3929,7 +3961,7 @@
         <v>89801586201</v>
       </c>
       <c r="F141">
-        <f>ROUND(E141/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>1.5</v>
       </c>
     </row>
@@ -3950,7 +3982,7 @@
         <v>61115424601</v>
       </c>
       <c r="F142">
-        <f>ROUND(E142/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3971,7 +4003,7 @@
         <v>71968857800</v>
       </c>
       <c r="F143">
-        <f>ROUND(E143/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>1.2</v>
       </c>
     </row>
@@ -3992,7 +4024,7 @@
         <v>47455693200</v>
       </c>
       <c r="F144">
-        <f>ROUND(E144/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
     </row>
@@ -4013,7 +4045,7 @@
         <v>59167838800</v>
       </c>
       <c r="F145">
-        <f>ROUND(E145/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4034,7 +4066,7 @@
         <v>29419818202</v>
       </c>
       <c r="F146">
-        <f>ROUND(E146/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
     </row>
@@ -4055,7 +4087,7 @@
         <v>21832738627</v>
       </c>
       <c r="F147">
-        <f>ROUND(E147/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
     </row>
@@ -4076,7 +4108,7 @@
         <v>13195138956</v>
       </c>
       <c r="F148">
-        <f>ROUND(E148/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
     </row>
@@ -4097,7 +4129,7 @@
         <v>49398520700</v>
       </c>
       <c r="F149">
-        <f>ROUND(E149/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
     </row>
@@ -4118,7 +4150,7 @@
         <v>77373000400</v>
       </c>
       <c r="F150">
-        <f>ROUND(E150/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>1.3</v>
       </c>
     </row>
@@ -4139,7 +4171,7 @@
         <v>71944538000</v>
       </c>
       <c r="F151">
-        <f>ROUND(E151/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>1.2</v>
       </c>
     </row>
@@ -4160,7 +4192,7 @@
         <v>385856577800</v>
       </c>
       <c r="F152">
-        <f>ROUND(E152/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>6.4</v>
       </c>
     </row>
@@ -4181,7 +4213,7 @@
         <v>43324111900</v>
       </c>
       <c r="F153">
-        <f>ROUND(E153/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>0.7</v>
       </c>
     </row>
@@ -4202,7 +4234,7 @@
         <v>17134811000</v>
       </c>
       <c r="F154">
-        <f>ROUND(E154/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
     </row>
@@ -4223,7 +4255,7 @@
         <v>13817730100</v>
       </c>
       <c r="F155">
-        <f>ROUND(E155/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
     </row>
@@ -4244,7 +4276,7 @@
         <v>79306107800</v>
       </c>
       <c r="F156">
-        <f>ROUND(E156/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>1.3</v>
       </c>
     </row>
@@ -4265,7 +4297,7 @@
         <v>133481643200</v>
       </c>
       <c r="F157">
-        <f>ROUND(E157/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -4286,7 +4318,7 @@
         <v>58112012100</v>
       </c>
       <c r="F158">
-        <f>ROUND(E158/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4307,7 +4339,7 @@
         <v>56288303800</v>
       </c>
       <c r="F159">
-        <f>ROUND(E159/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
     </row>
@@ -4328,7 +4360,7 @@
         <v>12531442670</v>
       </c>
       <c r="F160">
-        <f>ROUND(E160/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
     </row>
@@ -4349,7 +4381,7 @@
         <v>75596171200</v>
       </c>
       <c r="F161">
-        <f>ROUND(E161/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>1.3</v>
       </c>
     </row>
@@ -4370,7 +4402,7 @@
         <v>86428990400</v>
       </c>
       <c r="F162">
-        <f>ROUND(E162/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>1.4</v>
       </c>
     </row>
@@ -4391,7 +4423,7 @@
         <v>19929094000</v>
       </c>
       <c r="F163">
-        <f>ROUND(E163/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
     </row>
@@ -4412,7 +4444,7 @@
         <v>118289493800</v>
       </c>
       <c r="F164">
-        <f>ROUND(E164/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
@@ -4433,7 +4465,7 @@
         <v>143458758100</v>
       </c>
       <c r="F165">
-        <f>ROUND(E165/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>2.4</v>
       </c>
     </row>
@@ -4454,7 +4486,7 @@
         <v>154998370000</v>
       </c>
       <c r="F166">
-        <f>ROUND(E166/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>2.6</v>
       </c>
     </row>
@@ -4475,7 +4507,7 @@
         <v>110076691400</v>
       </c>
       <c r="F167">
-        <f>ROUND(E167/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>1.8</v>
       </c>
     </row>
@@ -4496,7 +4528,7 @@
         <v>435120978201</v>
       </c>
       <c r="F168">
-        <f>ROUND(E168/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>7.3</v>
       </c>
     </row>
@@ -4517,7 +4549,7 @@
         <v>125658552000</v>
       </c>
       <c r="F169">
-        <f>ROUND(E169/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>2.1</v>
       </c>
     </row>
@@ -4538,7 +4570,7 @@
         <v>972284363600</v>
       </c>
       <c r="F170">
-        <f>ROUND(E170/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>16.2</v>
       </c>
     </row>
@@ -4559,7 +4591,7 @@
         <v>442034520100</v>
       </c>
       <c r="F171">
-        <f>ROUND(E171/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>7.4</v>
       </c>
     </row>
@@ -4580,7 +4612,7 @@
         <v>132819125900</v>
       </c>
       <c r="F172">
-        <f>ROUND(E172/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -4601,7 +4633,7 @@
         <v>1249522571600</v>
       </c>
       <c r="F173">
-        <f>ROUND(E173/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>20.8</v>
       </c>
     </row>
@@ -4622,7 +4654,7 @@
         <v>541733655800</v>
       </c>
       <c r="F174">
-        <f>ROUND(E174/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
     </row>
@@ -4643,7 +4675,7 @@
         <v>97928397200</v>
       </c>
       <c r="F175">
-        <f>ROUND(E175/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>1.6</v>
       </c>
     </row>
@@ -4664,7 +4696,7 @@
         <v>1099047363100</v>
       </c>
       <c r="F176">
-        <f>ROUND(E176/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>18.3</v>
       </c>
     </row>
@@ -4685,7 +4717,7 @@
         <v>535642964900</v>
       </c>
       <c r="F177">
-        <f>ROUND(E177/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>8.9</v>
       </c>
     </row>
@@ -4706,7 +4738,7 @@
         <v>144236662600</v>
       </c>
       <c r="F178">
-        <f>ROUND(E178/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>2.4</v>
       </c>
     </row>
@@ -4727,7 +4759,7 @@
         <v>1093493221400</v>
       </c>
       <c r="F179">
-        <f>ROUND(E179/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>18.2</v>
       </c>
     </row>
@@ -4748,7 +4780,7 @@
         <v>461344788400</v>
       </c>
       <c r="F180">
-        <f>ROUND(E180/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>7.7</v>
       </c>
     </row>
@@ -4769,7 +4801,7 @@
         <v>107039959600</v>
       </c>
       <c r="F181">
-        <f>ROUND(E181/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>1.8</v>
       </c>
     </row>
@@ -4790,7 +4822,7 @@
         <v>1259900641300</v>
       </c>
       <c r="F182">
-        <f>ROUND(E182/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
     </row>
@@ -4811,7 +4843,7 @@
         <v>577777919500</v>
       </c>
       <c r="F183">
-        <f>ROUND(E183/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>9.6</v>
       </c>
     </row>
@@ -4832,7 +4864,7 @@
         <v>112024759600</v>
       </c>
       <c r="F184">
-        <f>ROUND(E184/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>1.9</v>
       </c>
     </row>
@@ -4853,7 +4885,7 @@
         <v>1048393643700</v>
       </c>
       <c r="F185">
-        <f>ROUND(E185/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>17.5</v>
       </c>
     </row>
@@ -4874,7 +4906,7 @@
         <v>714148725200</v>
       </c>
       <c r="F186">
-        <f>ROUND(E186/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>11.9</v>
       </c>
     </row>
@@ -4895,7 +4927,7 @@
         <v>112910311700</v>
       </c>
       <c r="F187">
-        <f>ROUND(E187/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>1.9</v>
       </c>
     </row>
@@ -4916,7 +4948,7 @@
         <v>1148773141700</v>
       </c>
       <c r="F188">
-        <f>ROUND(E188/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>19.100000000000001</v>
       </c>
     </row>
@@ -4937,7 +4969,7 @@
         <v>43455629600</v>
       </c>
       <c r="F189">
-        <f>ROUND(E189/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>0.7</v>
       </c>
     </row>
@@ -4958,7 +4990,7 @@
         <v>182295325600</v>
       </c>
       <c r="F190">
-        <f>ROUND(E190/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
     </row>
@@ -4979,7 +5011,7 @@
         <v>348662499800</v>
       </c>
       <c r="F191">
-        <f>ROUND(E191/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>5.8</v>
       </c>
     </row>
@@ -5000,7 +5032,7 @@
         <v>39810647800</v>
       </c>
       <c r="F192">
-        <f>ROUND(E192/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>0.7</v>
       </c>
     </row>
@@ -5021,7 +5053,7 @@
         <v>147523129000</v>
       </c>
       <c r="F193">
-        <f>ROUND(E193/60000000000, 1)</f>
+        <f t="shared" si="2"/>
         <v>2.5</v>
       </c>
     </row>
@@ -5042,7 +5074,7 @@
         <v>42164378800</v>
       </c>
       <c r="F194">
-        <f>ROUND(E194/60000000000, 1)</f>
+        <f t="shared" ref="F194:F257" si="3">ROUND(E194/60000000000, 1)</f>
         <v>0.7</v>
       </c>
     </row>
@@ -5063,7 +5095,7 @@
         <v>350217549499</v>
       </c>
       <c r="F195">
-        <f>ROUND(E195/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>5.8</v>
       </c>
     </row>
@@ -5084,7 +5116,7 @@
         <v>169046593599</v>
       </c>
       <c r="F196">
-        <f>ROUND(E196/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>2.8</v>
       </c>
     </row>
@@ -5105,7 +5137,7 @@
         <v>40510080700</v>
       </c>
       <c r="F197">
-        <f>ROUND(E197/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0.7</v>
       </c>
     </row>
@@ -5126,7 +5158,7 @@
         <v>395229067200</v>
       </c>
       <c r="F198">
-        <f>ROUND(E198/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>6.6</v>
       </c>
     </row>
@@ -5147,7 +5179,7 @@
         <v>202350812900</v>
       </c>
       <c r="F199">
-        <f>ROUND(E199/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>3.4</v>
       </c>
     </row>
@@ -5168,7 +5200,7 @@
         <v>55215422700</v>
       </c>
       <c r="F200">
-        <f>ROUND(E200/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0.9</v>
       </c>
     </row>
@@ -5189,7 +5221,7 @@
         <v>535427236000</v>
       </c>
       <c r="F201">
-        <f>ROUND(E201/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>8.9</v>
       </c>
     </row>
@@ -5210,7 +5242,7 @@
         <v>176965758700</v>
       </c>
       <c r="F202">
-        <f>ROUND(E202/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>2.9</v>
       </c>
     </row>
@@ -5231,7 +5263,7 @@
         <v>49256938200</v>
       </c>
       <c r="F203">
-        <f>ROUND(E203/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
     </row>
@@ -5252,7 +5284,7 @@
         <v>439362294800</v>
       </c>
       <c r="F204">
-        <f>ROUND(E204/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>7.3</v>
       </c>
     </row>
@@ -5273,7 +5305,7 @@
         <v>199484052800</v>
       </c>
       <c r="F205">
-        <f>ROUND(E205/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>3.3</v>
       </c>
     </row>
@@ -5294,7 +5326,7 @@
         <v>51156149100</v>
       </c>
       <c r="F206">
-        <f>ROUND(E206/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0.9</v>
       </c>
     </row>
@@ -5315,7 +5347,7 @@
         <v>411294296300</v>
       </c>
       <c r="F207">
-        <f>ROUND(E207/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>6.9</v>
       </c>
     </row>
@@ -5336,7 +5368,7 @@
         <v>160251787100</v>
       </c>
       <c r="F208">
-        <f>ROUND(E208/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>2.7</v>
       </c>
     </row>
@@ -5357,7 +5389,7 @@
         <v>50582778100</v>
       </c>
       <c r="F209">
-        <f>ROUND(E209/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
     </row>
@@ -5378,7 +5410,7 @@
         <v>482746807300</v>
       </c>
       <c r="F210">
-        <f>ROUND(E210/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
     </row>
@@ -5399,7 +5431,7 @@
         <v>283571226500</v>
       </c>
       <c r="F211">
-        <f>ROUND(E211/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>4.7</v>
       </c>
     </row>
@@ -5420,7 +5452,7 @@
         <v>38385675100</v>
       </c>
       <c r="F212">
-        <f>ROUND(E212/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
     </row>
@@ -5441,7 +5473,7 @@
         <v>383793111700</v>
       </c>
       <c r="F213">
-        <f>ROUND(E213/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>6.4</v>
       </c>
     </row>
@@ -5462,7 +5494,7 @@
         <v>218045984600</v>
       </c>
       <c r="F214">
-        <f>ROUND(E214/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>3.6</v>
       </c>
     </row>
@@ -5483,7 +5515,7 @@
         <v>42440236000</v>
       </c>
       <c r="F215">
-        <f>ROUND(E215/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0.7</v>
       </c>
     </row>
@@ -5504,7 +5536,7 @@
         <v>614695839400</v>
       </c>
       <c r="F216">
-        <f>ROUND(E216/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>10.199999999999999</v>
       </c>
     </row>
@@ -5525,7 +5557,7 @@
         <v>135565944800</v>
       </c>
       <c r="F217">
-        <f>ROUND(E217/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>2.2999999999999998</v>
       </c>
     </row>
@@ -5546,7 +5578,7 @@
         <v>1123984963600</v>
       </c>
       <c r="F218">
-        <f>ROUND(E218/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>18.7</v>
       </c>
     </row>
@@ -5567,7 +5599,7 @@
         <v>350816090800</v>
       </c>
       <c r="F219">
-        <f>ROUND(E219/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>5.8</v>
       </c>
     </row>
@@ -5588,7 +5620,7 @@
         <v>146534593200</v>
       </c>
       <c r="F220">
-        <f>ROUND(E220/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>2.4</v>
       </c>
     </row>
@@ -5609,7 +5641,7 @@
         <v>1052143095500</v>
       </c>
       <c r="F221">
-        <f>ROUND(E221/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>17.5</v>
       </c>
     </row>
@@ -5630,7 +5662,7 @@
         <v>440968450500</v>
       </c>
       <c r="F222">
-        <f>ROUND(E222/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>7.3</v>
       </c>
     </row>
@@ -5651,7 +5683,7 @@
         <v>145971735600</v>
       </c>
       <c r="F223">
-        <f>ROUND(E223/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>2.4</v>
       </c>
     </row>
@@ -5672,7 +5704,7 @@
         <v>2956701316700</v>
       </c>
       <c r="F224">
-        <f>ROUND(E224/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>49.3</v>
       </c>
     </row>
@@ -5693,7 +5725,7 @@
         <v>2054132053100</v>
       </c>
       <c r="F225">
-        <f>ROUND(E225/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>34.200000000000003</v>
       </c>
     </row>
@@ -5714,7 +5746,7 @@
         <v>107789192000</v>
       </c>
       <c r="F226">
-        <f>ROUND(E226/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>1.8</v>
       </c>
     </row>
@@ -5735,7 +5767,7 @@
         <v>872452690300</v>
       </c>
       <c r="F227">
-        <f>ROUND(E227/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>14.5</v>
       </c>
     </row>
@@ -5756,7 +5788,7 @@
         <v>347036181600</v>
       </c>
       <c r="F228">
-        <f>ROUND(E228/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>5.8</v>
       </c>
     </row>
@@ -5777,7 +5809,7 @@
         <v>4706882900</v>
       </c>
       <c r="F229">
-        <f>ROUND(E229/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0.1</v>
       </c>
     </row>
@@ -5798,7 +5830,7 @@
         <v>5561329200</v>
       </c>
       <c r="F230">
-        <f>ROUND(E230/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0.1</v>
       </c>
     </row>
@@ -5819,7 +5851,7 @@
         <v>6832334000</v>
       </c>
       <c r="F231">
-        <f>ROUND(E231/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0.1</v>
       </c>
     </row>
@@ -5840,7 +5872,7 @@
         <v>1503006900</v>
       </c>
       <c r="F232">
-        <f>ROUND(E232/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5861,7 +5893,7 @@
         <v>1814416500</v>
       </c>
       <c r="F233">
-        <f>ROUND(E233/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5882,7 +5914,7 @@
         <v>2028869800</v>
       </c>
       <c r="F234">
-        <f>ROUND(E234/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5903,7 +5935,7 @@
         <v>143814300</v>
       </c>
       <c r="F235">
-        <f>ROUND(E235/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5924,7 +5956,7 @@
         <v>600618700</v>
       </c>
       <c r="F236">
-        <f>ROUND(E236/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5945,7 +5977,7 @@
         <v>629672600</v>
       </c>
       <c r="F237">
-        <f>ROUND(E237/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5966,7 +5998,7 @@
         <v>235845500</v>
       </c>
       <c r="F238">
-        <f>ROUND(E238/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5987,7 +6019,7 @@
         <v>1035588600</v>
       </c>
       <c r="F239">
-        <f>ROUND(E239/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -6008,7 +6040,7 @@
         <v>161564800</v>
       </c>
       <c r="F240">
-        <f>ROUND(E240/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -6029,7 +6061,7 @@
         <v>117009000</v>
       </c>
       <c r="F241">
-        <f>ROUND(E241/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -6050,7 +6082,7 @@
         <v>812608700</v>
       </c>
       <c r="F242">
-        <f>ROUND(E242/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -6071,7 +6103,7 @@
         <v>1261079200</v>
       </c>
       <c r="F243">
-        <f>ROUND(E243/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -6092,7 +6124,7 @@
         <v>32320300</v>
       </c>
       <c r="F244">
-        <f>ROUND(E244/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -6113,7 +6145,7 @@
         <v>327981400</v>
       </c>
       <c r="F245">
-        <f>ROUND(E245/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -6134,7 +6166,7 @@
         <v>471387000</v>
       </c>
       <c r="F246">
-        <f>ROUND(E246/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -6155,7 +6187,7 @@
         <v>3706770709100</v>
       </c>
       <c r="F247">
-        <f>ROUND(E247/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>61.8</v>
       </c>
     </row>
@@ -6176,7 +6208,7 @@
         <v>10070735721100</v>
       </c>
       <c r="F248">
-        <f>ROUND(E248/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>167.8</v>
       </c>
     </row>
@@ -6197,7 +6229,7 @@
         <v>5292995482700</v>
       </c>
       <c r="F249">
-        <f>ROUND(E249/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>88.2</v>
       </c>
     </row>
@@ -6218,7 +6250,7 @@
         <v>7892460209400</v>
       </c>
       <c r="F250">
-        <f>ROUND(E250/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>131.5</v>
       </c>
     </row>
@@ -6239,7 +6271,7 @@
         <v>5688526382900</v>
       </c>
       <c r="F251">
-        <f>ROUND(E251/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>94.8</v>
       </c>
     </row>
@@ -6260,7 +6292,7 @@
         <v>4445291781700</v>
       </c>
       <c r="F252">
-        <f>ROUND(E252/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>74.099999999999994</v>
       </c>
     </row>
@@ -6281,7 +6313,7 @@
         <v>3609885035600</v>
       </c>
       <c r="F253">
-        <f>ROUND(E253/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>60.2</v>
       </c>
     </row>
@@ -6302,7 +6334,7 @@
         <v>6557030161100</v>
       </c>
       <c r="F254">
-        <f>ROUND(E254/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>109.3</v>
       </c>
     </row>
@@ -6323,7 +6355,7 @@
         <v>16329182679201</v>
       </c>
       <c r="F255">
-        <f>ROUND(E255/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>272.2</v>
       </c>
     </row>
@@ -6344,7 +6376,7 @@
         <v>386387823000</v>
       </c>
       <c r="F256">
-        <f>ROUND(E256/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>6.4</v>
       </c>
     </row>
@@ -6365,7 +6397,7 @@
         <v>42464805800</v>
       </c>
       <c r="F257">
-        <f>ROUND(E257/60000000000, 1)</f>
+        <f t="shared" si="3"/>
         <v>0.7</v>
       </c>
     </row>
@@ -6386,7 +6418,7 @@
         <v>218366258800</v>
       </c>
       <c r="F258">
-        <f>ROUND(E258/60000000000, 1)</f>
+        <f t="shared" ref="F258:F321" si="4">ROUND(E258/60000000000, 1)</f>
         <v>3.6</v>
       </c>
     </row>
@@ -6407,7 +6439,7 @@
         <v>410358845200</v>
       </c>
       <c r="F259">
-        <f>ROUND(E259/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>6.8</v>
       </c>
     </row>
@@ -6428,7 +6460,7 @@
         <v>39368806600</v>
       </c>
       <c r="F260">
-        <f>ROUND(E260/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
     </row>
@@ -6449,7 +6481,7 @@
         <v>170132369500</v>
       </c>
       <c r="F261">
-        <f>ROUND(E261/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>2.8</v>
       </c>
     </row>
@@ -6470,7 +6502,7 @@
         <v>353450920600</v>
       </c>
       <c r="F262">
-        <f>ROUND(E262/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>5.9</v>
       </c>
     </row>
@@ -6491,7 +6523,7 @@
         <v>38520456001</v>
       </c>
       <c r="F263">
-        <f>ROUND(E263/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>0.6</v>
       </c>
     </row>
@@ -6512,7 +6544,7 @@
         <v>196381812300</v>
       </c>
       <c r="F264">
-        <f>ROUND(E264/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>3.3</v>
       </c>
     </row>
@@ -6533,7 +6565,7 @@
         <v>434733841000</v>
       </c>
       <c r="F265">
-        <f>ROUND(E265/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>7.2</v>
       </c>
     </row>
@@ -6554,7 +6586,7 @@
         <v>40817081700</v>
       </c>
       <c r="F266">
-        <f>ROUND(E266/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
     </row>
@@ -6575,7 +6607,7 @@
         <v>207346187600</v>
       </c>
       <c r="F267">
-        <f>ROUND(E267/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>3.5</v>
       </c>
     </row>
@@ -6596,7 +6628,7 @@
         <v>438098897100</v>
       </c>
       <c r="F268">
-        <f>ROUND(E268/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>7.3</v>
       </c>
     </row>
@@ -6617,7 +6649,7 @@
         <v>39920454900</v>
       </c>
       <c r="F269">
-        <f>ROUND(E269/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
     </row>
@@ -6638,7 +6670,7 @@
         <v>460297189600</v>
       </c>
       <c r="F270">
-        <f>ROUND(E270/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>7.7</v>
       </c>
     </row>
@@ -6659,7 +6691,7 @@
         <v>37911861100</v>
       </c>
       <c r="F271">
-        <f>ROUND(E271/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>0.6</v>
       </c>
     </row>
@@ -6680,7 +6712,7 @@
         <v>216093850000</v>
       </c>
       <c r="F272">
-        <f>ROUND(E272/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>3.6</v>
       </c>
     </row>
@@ -6701,7 +6733,7 @@
         <v>554002494100</v>
       </c>
       <c r="F273">
-        <f>ROUND(E273/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>9.1999999999999993</v>
       </c>
     </row>
@@ -6722,7 +6754,7 @@
         <v>48757422300</v>
       </c>
       <c r="F274">
-        <f>ROUND(E274/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
     </row>
@@ -6743,7 +6775,7 @@
         <v>216261089100</v>
       </c>
       <c r="F275">
-        <f>ROUND(E275/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>3.6</v>
       </c>
     </row>
@@ -6764,7 +6796,7 @@
         <v>613686959600</v>
       </c>
       <c r="F276">
-        <f>ROUND(E276/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>10.199999999999999</v>
       </c>
     </row>
@@ -6785,7 +6817,7 @@
         <v>50791743300</v>
       </c>
       <c r="F277">
-        <f>ROUND(E277/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
     </row>
@@ -6806,7 +6838,7 @@
         <v>280090761200</v>
       </c>
       <c r="F278">
-        <f>ROUND(E278/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>4.7</v>
       </c>
     </row>
@@ -6827,7 +6859,7 @@
         <v>557676122800</v>
       </c>
       <c r="F279">
-        <f>ROUND(E279/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>9.3000000000000007</v>
       </c>
     </row>
@@ -6848,7 +6880,7 @@
         <v>44758813300</v>
       </c>
       <c r="F280">
-        <f>ROUND(E280/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
     </row>
@@ -6869,7 +6901,7 @@
         <v>253354820300</v>
       </c>
       <c r="F281">
-        <f>ROUND(E281/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>4.2</v>
       </c>
     </row>
@@ -6890,7 +6922,7 @@
         <v>571589675000</v>
       </c>
       <c r="F282">
-        <f>ROUND(E282/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>9.5</v>
       </c>
     </row>
@@ -6911,7 +6943,7 @@
         <v>49491584000</v>
       </c>
       <c r="F283">
-        <f>ROUND(E283/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
     </row>
@@ -6932,7 +6964,7 @@
         <v>149277626200</v>
       </c>
       <c r="F284">
-        <f>ROUND(E284/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>2.5</v>
       </c>
     </row>
@@ -6953,7 +6985,7 @@
         <v>124717452500</v>
       </c>
       <c r="F285">
-        <f>ROUND(E285/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>2.1</v>
       </c>
     </row>
@@ -6974,7 +7006,7 @@
         <v>188599305800</v>
       </c>
       <c r="F286">
-        <f>ROUND(E286/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>3.1</v>
       </c>
     </row>
@@ -6995,7 +7027,7 @@
         <v>578428653600</v>
       </c>
       <c r="F287">
-        <f>ROUND(E287/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>9.6</v>
       </c>
     </row>
@@ -7016,7 +7048,7 @@
         <v>102436808400</v>
       </c>
       <c r="F288">
-        <f>ROUND(E288/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>1.7</v>
       </c>
     </row>
@@ -7037,7 +7069,7 @@
         <v>122006801800</v>
       </c>
       <c r="F289">
-        <f>ROUND(E289/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
     </row>
@@ -7058,7 +7090,7 @@
         <v>448076253500</v>
       </c>
       <c r="F290">
-        <f>ROUND(E290/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>7.5</v>
       </c>
     </row>
@@ -7079,7 +7111,7 @@
         <v>92480821900</v>
       </c>
       <c r="F291">
-        <f>ROUND(E291/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
     </row>
@@ -7100,7 +7132,7 @@
         <v>518118455600</v>
       </c>
       <c r="F292">
-        <f>ROUND(E292/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>8.6</v>
       </c>
     </row>
@@ -7121,7 +7153,7 @@
         <v>1456411069900</v>
       </c>
       <c r="F293">
-        <f>ROUND(E293/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>24.3</v>
       </c>
     </row>
@@ -7142,7 +7174,7 @@
         <v>98842782900</v>
       </c>
       <c r="F294">
-        <f>ROUND(E294/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>1.6</v>
       </c>
     </row>
@@ -7163,7 +7195,7 @@
         <v>1271694109000</v>
       </c>
       <c r="F295">
-        <f>ROUND(E295/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>21.2</v>
       </c>
     </row>
@@ -7184,7 +7216,7 @@
         <v>563019876400</v>
       </c>
       <c r="F296">
-        <f>ROUND(E296/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>9.4</v>
       </c>
     </row>
@@ -7205,7 +7237,7 @@
         <v>97913727300</v>
       </c>
       <c r="F297">
-        <f>ROUND(E297/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>1.6</v>
       </c>
     </row>
@@ -7226,7 +7258,7 @@
         <v>1163575096900</v>
       </c>
       <c r="F298">
-        <f>ROUND(E298/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>19.399999999999999</v>
       </c>
     </row>
@@ -7247,7 +7279,7 @@
         <v>563620218600</v>
       </c>
       <c r="F299">
-        <f>ROUND(E299/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>9.4</v>
       </c>
     </row>
@@ -7268,7 +7300,7 @@
         <v>152414414900</v>
       </c>
       <c r="F300">
-        <f>ROUND(E300/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>2.5</v>
       </c>
     </row>
@@ -7289,7 +7321,7 @@
         <v>1206436207400</v>
       </c>
       <c r="F301">
-        <f>ROUND(E301/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>20.100000000000001</v>
       </c>
     </row>
@@ -7310,7 +7342,7 @@
         <v>592079512300</v>
       </c>
       <c r="F302">
-        <f>ROUND(E302/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>9.9</v>
       </c>
     </row>
@@ -7331,7 +7363,7 @@
         <v>134900314100</v>
       </c>
       <c r="F303">
-        <f>ROUND(E303/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -7352,7 +7384,7 @@
         <v>1246095975500</v>
       </c>
       <c r="F304">
-        <f>ROUND(E304/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>20.8</v>
       </c>
     </row>
@@ -7373,7 +7405,7 @@
         <v>586385101000</v>
       </c>
       <c r="F305">
-        <f>ROUND(E305/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>9.8000000000000007</v>
       </c>
     </row>
@@ -7394,7 +7426,7 @@
         <v>164959418100</v>
       </c>
       <c r="F306">
-        <f>ROUND(E306/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>2.7</v>
       </c>
     </row>
@@ -7415,7 +7447,7 @@
         <v>1279592050700</v>
       </c>
       <c r="F307">
-        <f>ROUND(E307/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>21.3</v>
       </c>
     </row>
@@ -7436,7 +7468,7 @@
         <v>539986541100</v>
       </c>
       <c r="F308">
-        <f>ROUND(E308/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
     </row>
@@ -7457,7 +7489,7 @@
         <v>128946923600</v>
       </c>
       <c r="F309">
-        <f>ROUND(E309/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>2.1</v>
       </c>
     </row>
@@ -7478,7 +7510,7 @@
         <v>1475245810100</v>
       </c>
       <c r="F310">
-        <f>ROUND(E310/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>24.6</v>
       </c>
     </row>
@@ -7499,7 +7531,7 @@
         <v>581382703800</v>
       </c>
       <c r="F311">
-        <f>ROUND(E311/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>9.6999999999999993</v>
       </c>
     </row>
@@ -7520,7 +7552,7 @@
         <v>42277436000</v>
       </c>
       <c r="F312">
-        <f>ROUND(E312/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
     </row>
@@ -7541,7 +7573,7 @@
         <v>193099924800</v>
       </c>
       <c r="F313">
-        <f>ROUND(E313/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>3.2</v>
       </c>
     </row>
@@ -7562,7 +7594,7 @@
         <v>390692349600</v>
       </c>
       <c r="F314">
-        <f>ROUND(E314/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>6.5</v>
       </c>
     </row>
@@ -7583,7 +7615,7 @@
         <v>45408488700</v>
       </c>
       <c r="F315">
-        <f>ROUND(E315/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
     </row>
@@ -7604,7 +7636,7 @@
         <v>163975341700</v>
       </c>
       <c r="F316">
-        <f>ROUND(E316/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>2.7</v>
       </c>
     </row>
@@ -7625,7 +7657,7 @@
         <v>327172292600</v>
       </c>
       <c r="F317">
-        <f>ROUND(E317/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>5.5</v>
       </c>
     </row>
@@ -7646,7 +7678,7 @@
         <v>43713663401</v>
       </c>
       <c r="F318">
-        <f>ROUND(E318/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
     </row>
@@ -7667,7 +7699,7 @@
         <v>182052220900</v>
       </c>
       <c r="F319">
-        <f>ROUND(E319/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
     </row>
@@ -7688,7 +7720,7 @@
         <v>383696424499</v>
       </c>
       <c r="F320">
-        <f>ROUND(E320/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>6.4</v>
       </c>
     </row>
@@ -7709,7 +7741,7 @@
         <v>47774192900</v>
       </c>
       <c r="F321">
-        <f>ROUND(E321/60000000000, 1)</f>
+        <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
     </row>
@@ -7730,7 +7762,7 @@
         <v>174724358400</v>
       </c>
       <c r="F322">
-        <f>ROUND(E322/60000000000, 1)</f>
+        <f t="shared" ref="F322:F385" si="5">ROUND(E322/60000000000, 1)</f>
         <v>2.9</v>
       </c>
     </row>
@@ -7751,7 +7783,7 @@
         <v>369850191200</v>
       </c>
       <c r="F323">
-        <f>ROUND(E323/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>6.2</v>
       </c>
     </row>
@@ -7772,7 +7804,7 @@
         <v>52725644500</v>
       </c>
       <c r="F324">
-        <f>ROUND(E324/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>0.9</v>
       </c>
     </row>
@@ -7793,7 +7825,7 @@
         <v>182862821400</v>
       </c>
       <c r="F325">
-        <f>ROUND(E325/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -7814,7 +7846,7 @@
         <v>472376253300</v>
       </c>
       <c r="F326">
-        <f>ROUND(E326/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>7.9</v>
       </c>
     </row>
@@ -7835,7 +7867,7 @@
         <v>61052311200</v>
       </c>
       <c r="F327">
-        <f>ROUND(E327/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -7856,7 +7888,7 @@
         <v>199913149700</v>
       </c>
       <c r="F328">
-        <f>ROUND(E328/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>3.3</v>
       </c>
     </row>
@@ -7877,7 +7909,7 @@
         <v>446844485900</v>
       </c>
       <c r="F329">
-        <f>ROUND(E329/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>7.4</v>
       </c>
     </row>
@@ -7898,7 +7930,7 @@
         <v>50665948500</v>
       </c>
       <c r="F330">
-        <f>ROUND(E330/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>0.8</v>
       </c>
     </row>
@@ -7919,7 +7951,7 @@
         <v>205467151800</v>
       </c>
       <c r="F331">
-        <f>ROUND(E331/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>3.4</v>
       </c>
     </row>
@@ -7940,7 +7972,7 @@
         <v>434823312700</v>
       </c>
       <c r="F332">
-        <f>ROUND(E332/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>7.2</v>
       </c>
     </row>
@@ -7961,7 +7993,7 @@
         <v>45946327400</v>
       </c>
       <c r="F333">
-        <f>ROUND(E333/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>0.8</v>
       </c>
     </row>
@@ -7982,7 +8014,7 @@
         <v>195783449600</v>
       </c>
       <c r="F334">
-        <f>ROUND(E334/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>3.3</v>
       </c>
     </row>
@@ -8003,7 +8035,7 @@
         <v>419208635500</v>
       </c>
       <c r="F335">
-        <f>ROUND(E335/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
@@ -8024,7 +8056,7 @@
         <v>47705829200</v>
       </c>
       <c r="F336">
-        <f>ROUND(E336/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>0.8</v>
       </c>
     </row>
@@ -8045,7 +8077,7 @@
         <v>193492829800</v>
       </c>
       <c r="F337">
-        <f>ROUND(E337/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>3.2</v>
       </c>
     </row>
@@ -8066,7 +8098,7 @@
         <v>467619351900</v>
       </c>
       <c r="F338">
-        <f>ROUND(E338/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>7.8</v>
       </c>
     </row>
@@ -8087,7 +8119,7 @@
         <v>49627693500</v>
       </c>
       <c r="F339">
-        <f>ROUND(E339/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>0.8</v>
       </c>
     </row>
@@ -8108,7 +8140,7 @@
         <v>123708041200</v>
       </c>
       <c r="F340">
-        <f>ROUND(E340/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>2.1</v>
       </c>
     </row>
@@ -8129,7 +8161,7 @@
         <v>1065207484100</v>
       </c>
       <c r="F341">
-        <f>ROUND(E341/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>17.8</v>
       </c>
     </row>
@@ -8150,7 +8182,7 @@
         <v>647300259600</v>
       </c>
       <c r="F342">
-        <f>ROUND(E342/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>10.8</v>
       </c>
     </row>
@@ -8171,7 +8203,7 @@
         <v>129137097900</v>
       </c>
       <c r="F343">
-        <f>ROUND(E343/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -8192,7 +8224,7 @@
         <v>1083299383100</v>
       </c>
       <c r="F344">
-        <f>ROUND(E344/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>18.100000000000001</v>
       </c>
     </row>
@@ -8213,7 +8245,7 @@
         <v>428934114200</v>
       </c>
       <c r="F345">
-        <f>ROUND(E345/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>7.1</v>
       </c>
     </row>
@@ -8234,7 +8266,7 @@
         <v>166940077200</v>
       </c>
       <c r="F346">
-        <f>ROUND(E346/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>2.8</v>
       </c>
     </row>
@@ -8255,7 +8287,7 @@
         <v>1329461872200</v>
       </c>
       <c r="F347">
-        <f>ROUND(E347/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>22.2</v>
       </c>
     </row>
@@ -8276,7 +8308,7 @@
         <v>500269441400</v>
       </c>
       <c r="F348">
-        <f>ROUND(E348/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>8.3000000000000007</v>
       </c>
     </row>
@@ -8297,7 +8329,7 @@
         <v>111395583300</v>
       </c>
       <c r="F349">
-        <f>ROUND(E349/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>1.9</v>
       </c>
     </row>
@@ -8318,7 +8350,7 @@
         <v>2662080599800</v>
       </c>
       <c r="F350">
-        <f>ROUND(E350/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>44.4</v>
       </c>
     </row>
@@ -8339,7 +8371,7 @@
         <v>329003416900</v>
       </c>
       <c r="F351">
-        <f>ROUND(E351/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>5.5</v>
       </c>
     </row>
@@ -8360,7 +8392,7 @@
         <v>144472023800</v>
       </c>
       <c r="F352">
-        <f>ROUND(E352/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>2.4</v>
       </c>
     </row>
@@ -8381,7 +8413,7 @@
         <v>126612438600</v>
       </c>
       <c r="F353">
-        <f>ROUND(E353/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>2.1</v>
       </c>
     </row>
@@ -8402,7 +8434,7 @@
         <v>4335913036900</v>
       </c>
       <c r="F354">
-        <f>ROUND(E354/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>72.3</v>
       </c>
     </row>
@@ -8423,7 +8455,7 @@
         <v>7892300700599</v>
       </c>
       <c r="F355">
-        <f>ROUND(E355/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>131.5</v>
       </c>
     </row>
@@ -8444,7 +8476,7 @@
         <v>539665224900</v>
       </c>
       <c r="F356">
-        <f>ROUND(E356/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
     </row>
@@ -8465,7 +8497,7 @@
         <v>103065769900</v>
       </c>
       <c r="F357">
-        <f>ROUND(E357/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>1.7</v>
       </c>
     </row>
@@ -8486,7 +8518,7 @@
         <v>1037273614500</v>
       </c>
       <c r="F358">
-        <f>ROUND(E358/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>17.3</v>
       </c>
     </row>
@@ -8507,7 +8539,7 @@
         <v>460975460400</v>
       </c>
       <c r="F359">
-        <f>ROUND(E359/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>7.7</v>
       </c>
     </row>
@@ -8528,7 +8560,7 @@
         <v>142051684100</v>
       </c>
       <c r="F360">
-        <f>ROUND(E360/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>2.4</v>
       </c>
     </row>
@@ -8549,7 +8581,7 @@
         <v>1287053896500</v>
       </c>
       <c r="F361">
-        <f>ROUND(E361/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>21.5</v>
       </c>
     </row>
@@ -8570,7 +8602,7 @@
         <v>617814482600</v>
       </c>
       <c r="F362">
-        <f>ROUND(E362/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>10.3</v>
       </c>
     </row>
@@ -8591,7 +8623,7 @@
         <v>106181916000</v>
       </c>
       <c r="F363">
-        <f>ROUND(E363/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>1.8</v>
       </c>
     </row>
@@ -8612,7 +8644,7 @@
         <v>462059154200</v>
       </c>
       <c r="F364">
-        <f>ROUND(E364/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>7.7</v>
       </c>
     </row>
@@ -8633,7 +8665,7 @@
         <v>1290253234000</v>
       </c>
       <c r="F365">
-        <f>ROUND(E365/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>21.5</v>
       </c>
     </row>
@@ -8654,7 +8686,7 @@
         <v>129836683300</v>
       </c>
       <c r="F366">
-        <f>ROUND(E366/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -8675,7 +8707,7 @@
         <v>1236239883500</v>
       </c>
       <c r="F367">
-        <f>ROUND(E367/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>20.6</v>
       </c>
     </row>
@@ -8696,7 +8728,7 @@
         <v>543478202400</v>
       </c>
       <c r="F368">
-        <f>ROUND(E368/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>9.1</v>
       </c>
     </row>
@@ -8717,7 +8749,7 @@
         <v>102313882700</v>
       </c>
       <c r="F369">
-        <f>ROUND(E369/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>1.7</v>
       </c>
     </row>
@@ -8738,7 +8770,7 @@
         <v>614790211000</v>
       </c>
       <c r="F370">
-        <f>ROUND(E370/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>10.199999999999999</v>
       </c>
     </row>
@@ -8759,7 +8791,7 @@
         <v>1470790521200</v>
       </c>
       <c r="F371">
-        <f>ROUND(E371/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>24.5</v>
       </c>
     </row>
@@ -8780,7 +8812,7 @@
         <v>128722598300</v>
       </c>
       <c r="F372">
-        <f>ROUND(E372/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>2.1</v>
       </c>
     </row>
@@ -8801,7 +8833,7 @@
         <v>1140935782300</v>
       </c>
       <c r="F373">
-        <f>ROUND(E373/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>19</v>
       </c>
     </row>
@@ -8822,7 +8854,7 @@
         <v>436005541600</v>
       </c>
       <c r="F374">
-        <f>ROUND(E374/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>7.3</v>
       </c>
     </row>
@@ -8843,7 +8875,7 @@
         <v>91845017500</v>
       </c>
       <c r="F375">
-        <f>ROUND(E375/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>1.5</v>
       </c>
     </row>
@@ -8864,7 +8896,7 @@
         <v>1224173110000</v>
       </c>
       <c r="F376">
-        <f>ROUND(E376/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>20.399999999999999</v>
       </c>
     </row>
@@ -8885,7 +8917,7 @@
         <v>585986488800</v>
       </c>
       <c r="F377">
-        <f>ROUND(E377/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>9.8000000000000007</v>
       </c>
     </row>
@@ -8906,7 +8938,7 @@
         <v>180763019900</v>
       </c>
       <c r="F378">
-        <f>ROUND(E378/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -8927,7 +8959,7 @@
         <v>407564195100</v>
       </c>
       <c r="F379">
-        <f>ROUND(E379/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>6.8</v>
       </c>
     </row>
@@ -8948,7 +8980,7 @@
         <v>260986327700</v>
       </c>
       <c r="F380">
-        <f>ROUND(E380/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>4.3</v>
       </c>
     </row>
@@ -8969,7 +9001,7 @@
         <v>135818307000</v>
       </c>
       <c r="F381">
-        <f>ROUND(E381/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>2.2999999999999998</v>
       </c>
     </row>
@@ -8990,7 +9022,7 @@
         <v>337355933599</v>
       </c>
       <c r="F382">
-        <f>ROUND(E382/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>5.6</v>
       </c>
     </row>
@@ -9011,7 +9043,7 @@
         <v>44558241601</v>
       </c>
       <c r="F383">
-        <f>ROUND(E383/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
     </row>
@@ -9032,7 +9064,7 @@
         <v>154398496600</v>
       </c>
       <c r="F384">
-        <f>ROUND(E384/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>2.6</v>
       </c>
     </row>
@@ -9053,7 +9085,7 @@
         <v>478038466400</v>
       </c>
       <c r="F385">
-        <f>ROUND(E385/60000000000, 1)</f>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
     </row>
@@ -9074,7 +9106,7 @@
         <v>139908893900</v>
       </c>
       <c r="F386">
-        <f>ROUND(E386/60000000000, 1)</f>
+        <f t="shared" ref="F386:F449" si="6">ROUND(E386/60000000000, 1)</f>
         <v>2.2999999999999998</v>
       </c>
     </row>
@@ -9095,7 +9127,7 @@
         <v>159287288400</v>
       </c>
       <c r="F387">
-        <f>ROUND(E387/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>2.7</v>
       </c>
     </row>
@@ -9116,7 +9148,7 @@
         <v>399626796600</v>
       </c>
       <c r="F388">
-        <f>ROUND(E388/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>6.7</v>
       </c>
     </row>
@@ -9137,7 +9169,7 @@
         <v>58598271000</v>
       </c>
       <c r="F389">
-        <f>ROUND(E389/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -9158,7 +9190,7 @@
         <v>171071394100</v>
       </c>
       <c r="F390">
-        <f>ROUND(E390/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>2.9</v>
       </c>
     </row>
@@ -9179,7 +9211,7 @@
         <v>461388813800</v>
       </c>
       <c r="F391">
-        <f>ROUND(E391/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>7.7</v>
       </c>
     </row>
@@ -9200,7 +9232,7 @@
         <v>38372041200</v>
       </c>
       <c r="F392">
-        <f>ROUND(E392/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>0.6</v>
       </c>
     </row>
@@ -9221,7 +9253,7 @@
         <v>207156913600</v>
       </c>
       <c r="F393">
-        <f>ROUND(E393/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>3.5</v>
       </c>
     </row>
@@ -9242,7 +9274,7 @@
         <v>432983068100</v>
       </c>
       <c r="F394">
-        <f>ROUND(E394/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>7.2</v>
       </c>
     </row>
@@ -9263,7 +9295,7 @@
         <v>30813750500</v>
       </c>
       <c r="F395">
-        <f>ROUND(E395/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
     </row>
@@ -9284,7 +9316,7 @@
         <v>144814163500</v>
       </c>
       <c r="F396">
-        <f>ROUND(E396/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>2.4</v>
       </c>
     </row>
@@ -9305,7 +9337,7 @@
         <v>428221132900</v>
       </c>
       <c r="F397">
-        <f>ROUND(E397/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>7.1</v>
       </c>
     </row>
@@ -9326,7 +9358,7 @@
         <v>33763307600</v>
       </c>
       <c r="F398">
-        <f>ROUND(E398/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>0.6</v>
       </c>
     </row>
@@ -9347,7 +9379,7 @@
         <v>175441043500</v>
       </c>
       <c r="F399">
-        <f>ROUND(E399/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>2.9</v>
       </c>
     </row>
@@ -9368,7 +9400,7 @@
         <v>436768908200</v>
       </c>
       <c r="F400">
-        <f>ROUND(E400/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>7.3</v>
       </c>
     </row>
@@ -9389,7 +9421,7 @@
         <v>43054392800</v>
       </c>
       <c r="F401">
-        <f>ROUND(E401/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>0.7</v>
       </c>
     </row>
@@ -9410,7 +9442,7 @@
         <v>336878877000</v>
       </c>
       <c r="F402">
-        <f>ROUND(E402/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>5.6</v>
       </c>
     </row>
@@ -9431,7 +9463,7 @@
         <v>401819104400</v>
       </c>
       <c r="F403">
-        <f>ROUND(E403/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>6.7</v>
       </c>
     </row>
@@ -9452,7 +9484,7 @@
         <v>37712142300</v>
       </c>
       <c r="F404">
-        <f>ROUND(E404/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>0.6</v>
       </c>
     </row>
@@ -9473,7 +9505,7 @@
         <v>74017060300</v>
       </c>
       <c r="F405">
-        <f>ROUND(E405/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>1.2</v>
       </c>
     </row>
@@ -9494,7 +9526,7 @@
         <v>1072304861100</v>
       </c>
       <c r="F406">
-        <f>ROUND(E406/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>17.899999999999999</v>
       </c>
     </row>
@@ -9515,7 +9547,7 @@
         <v>551827716300</v>
       </c>
       <c r="F407">
-        <f>ROUND(E407/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>9.1999999999999993</v>
       </c>
     </row>
@@ -9536,7 +9568,7 @@
         <v>97332346800</v>
       </c>
       <c r="F408">
-        <f>ROUND(E408/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>1.6</v>
       </c>
     </row>
@@ -9557,7 +9589,7 @@
         <v>537959634700</v>
       </c>
       <c r="F409">
-        <f>ROUND(E409/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
     </row>
@@ -9578,7 +9610,7 @@
         <v>1543620777500</v>
       </c>
       <c r="F410">
-        <f>ROUND(E410/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>25.7</v>
       </c>
     </row>
@@ -9599,7 +9631,7 @@
         <v>127646485300</v>
       </c>
       <c r="F411">
-        <f>ROUND(E411/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>2.1</v>
       </c>
     </row>
@@ -9620,7 +9652,7 @@
         <v>574836285100</v>
       </c>
       <c r="F412">
-        <f>ROUND(E412/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>9.6</v>
       </c>
     </row>
@@ -9641,7 +9673,7 @@
         <v>1540364803800</v>
       </c>
       <c r="F413">
-        <f>ROUND(E413/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>25.7</v>
       </c>
     </row>
@@ -9662,7 +9694,7 @@
         <v>98739588600</v>
       </c>
       <c r="F414">
-        <f>ROUND(E414/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>1.6</v>
       </c>
     </row>
@@ -9683,7 +9715,7 @@
         <v>2595822730600</v>
       </c>
       <c r="F415">
-        <f>ROUND(E415/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>43.3</v>
       </c>
     </row>
@@ -9704,7 +9736,7 @@
         <v>449618027300</v>
       </c>
       <c r="F416">
-        <f>ROUND(E416/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>7.5</v>
       </c>
     </row>
@@ -9725,7 +9757,7 @@
         <v>122821914300</v>
       </c>
       <c r="F417">
-        <f>ROUND(E417/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
     </row>
@@ -9746,7 +9778,7 @@
         <v>89819548600</v>
       </c>
       <c r="F418">
-        <f>ROUND(E418/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>1.5</v>
       </c>
     </row>
@@ -9767,7 +9799,7 @@
         <v>30420123800</v>
       </c>
       <c r="F419">
-        <f>ROUND(E419/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
     </row>
@@ -9788,7 +9820,7 @@
         <v>148410404200</v>
       </c>
       <c r="F420">
-        <f>ROUND(E420/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>2.5</v>
       </c>
     </row>
@@ -9809,7 +9841,7 @@
         <v>357097523700</v>
       </c>
       <c r="F421">
-        <f>ROUND(E421/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
     </row>
@@ -9830,7 +9862,7 @@
         <v>30281816700</v>
       </c>
       <c r="F422">
-        <f>ROUND(E422/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
     </row>
@@ -9851,7 +9883,7 @@
         <v>128699408800</v>
       </c>
       <c r="F423">
-        <f>ROUND(E423/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>2.1</v>
       </c>
     </row>
@@ -9872,7 +9904,7 @@
         <v>309286510700</v>
       </c>
       <c r="F424">
-        <f>ROUND(E424/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>5.2</v>
       </c>
     </row>
@@ -9893,7 +9925,7 @@
         <v>27309952800</v>
       </c>
       <c r="F425">
-        <f>ROUND(E425/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
     </row>
@@ -9914,7 +9946,7 @@
         <v>113273333200</v>
       </c>
       <c r="F426">
-        <f>ROUND(E426/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>1.9</v>
       </c>
     </row>
@@ -9935,7 +9967,7 @@
         <v>327700343100</v>
       </c>
       <c r="F427">
-        <f>ROUND(E427/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>5.5</v>
       </c>
     </row>
@@ -9956,7 +9988,7 @@
         <v>26632650200</v>
       </c>
       <c r="F428">
-        <f>ROUND(E428/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>0.4</v>
       </c>
     </row>
@@ -9977,7 +10009,7 @@
         <v>155634539400</v>
       </c>
       <c r="F429">
-        <f>ROUND(E429/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>2.6</v>
       </c>
     </row>
@@ -9998,7 +10030,7 @@
         <v>349079891100</v>
       </c>
       <c r="F430">
-        <f>ROUND(E430/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>5.8</v>
       </c>
     </row>
@@ -10019,7 +10051,7 @@
         <v>34353443100</v>
       </c>
       <c r="F431">
-        <f>ROUND(E431/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>0.6</v>
       </c>
     </row>
@@ -10040,7 +10072,7 @@
         <v>126826872400</v>
       </c>
       <c r="F432">
-        <f>ROUND(E432/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>2.1</v>
       </c>
     </row>
@@ -10061,7 +10093,7 @@
         <v>411929489500</v>
       </c>
       <c r="F433">
-        <f>ROUND(E433/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>6.9</v>
       </c>
     </row>
@@ -10082,7 +10114,7 @@
         <v>32614400100</v>
       </c>
       <c r="F434">
-        <f>ROUND(E434/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
     </row>
@@ -10103,7 +10135,7 @@
         <v>135430584500</v>
       </c>
       <c r="F435">
-        <f>ROUND(E435/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>2.2999999999999998</v>
       </c>
     </row>
@@ -10124,7 +10156,7 @@
         <v>387628232000</v>
       </c>
       <c r="F436">
-        <f>ROUND(E436/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>6.5</v>
       </c>
     </row>
@@ -10145,7 +10177,7 @@
         <v>33211396600</v>
       </c>
       <c r="F437">
-        <f>ROUND(E437/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>0.6</v>
       </c>
     </row>
@@ -10166,7 +10198,7 @@
         <v>342850450600</v>
       </c>
       <c r="F438">
-        <f>ROUND(E438/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>5.7</v>
       </c>
     </row>
@@ -10187,7 +10219,7 @@
         <v>336983632400</v>
       </c>
       <c r="F439">
-        <f>ROUND(E439/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>5.6</v>
       </c>
     </row>
@@ -10208,7 +10240,7 @@
         <v>31897728800</v>
       </c>
       <c r="F440">
-        <f>ROUND(E440/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
     </row>
@@ -10229,7 +10261,7 @@
         <v>183618153000</v>
       </c>
       <c r="F441">
-        <f>ROUND(E441/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>3.1</v>
       </c>
     </row>
@@ -10250,7 +10282,7 @@
         <v>369753768100</v>
       </c>
       <c r="F442">
-        <f>ROUND(E442/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>6.2</v>
       </c>
     </row>
@@ -10271,7 +10303,7 @@
         <v>24671322000</v>
       </c>
       <c r="F443">
-        <f>ROUND(E443/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>0.4</v>
       </c>
     </row>
@@ -10292,7 +10324,7 @@
         <v>177565192900</v>
       </c>
       <c r="F444">
-        <f>ROUND(E444/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
     </row>
@@ -10313,7 +10345,7 @@
         <v>315671887700</v>
       </c>
       <c r="F445">
-        <f>ROUND(E445/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>5.3</v>
       </c>
     </row>
@@ -10334,7 +10366,7 @@
         <v>33954685200</v>
       </c>
       <c r="F446">
-        <f>ROUND(E446/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>0.6</v>
       </c>
     </row>
@@ -10355,7 +10387,7 @@
         <v>81268336800</v>
       </c>
       <c r="F447">
-        <f>ROUND(E447/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>1.4</v>
       </c>
     </row>
@@ -10376,7 +10408,7 @@
         <v>77035253100</v>
       </c>
       <c r="F448">
-        <f>ROUND(E448/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>1.3</v>
       </c>
     </row>
@@ -10397,7 +10429,7 @@
         <v>556085054800</v>
       </c>
       <c r="F449">
-        <f>ROUND(E449/60000000000, 1)</f>
+        <f t="shared" si="6"/>
         <v>9.3000000000000007</v>
       </c>
     </row>
@@ -10418,7 +10450,7 @@
         <v>87079606500</v>
       </c>
       <c r="F450">
-        <f>ROUND(E450/60000000000, 1)</f>
+        <f t="shared" ref="F450:F513" si="7">ROUND(E450/60000000000, 1)</f>
         <v>1.5</v>
       </c>
     </row>
@@ -10439,7 +10471,7 @@
         <v>81647757899</v>
       </c>
       <c r="F451">
-        <f>ROUND(E451/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>1.4</v>
       </c>
     </row>
@@ -10460,7 +10492,7 @@
         <v>367031625399</v>
       </c>
       <c r="F452">
-        <f>ROUND(E452/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>6.1</v>
       </c>
     </row>
@@ -10481,7 +10513,7 @@
         <v>82524327400</v>
       </c>
       <c r="F453">
-        <f>ROUND(E453/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>1.4</v>
       </c>
     </row>
@@ -10502,7 +10534,7 @@
         <v>867923328300</v>
       </c>
       <c r="F454">
-        <f>ROUND(E454/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>14.5</v>
       </c>
     </row>
@@ -10523,7 +10555,7 @@
         <v>407859974501</v>
       </c>
       <c r="F455">
-        <f>ROUND(E455/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>6.8</v>
       </c>
     </row>
@@ -10544,7 +10576,7 @@
         <v>96356030900</v>
       </c>
       <c r="F456">
-        <f>ROUND(E456/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>1.6</v>
       </c>
     </row>
@@ -10565,7 +10597,7 @@
         <v>459857413800</v>
       </c>
       <c r="F457">
-        <f>ROUND(E457/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>7.7</v>
       </c>
     </row>
@@ -10586,7 +10618,7 @@
         <v>79415022900</v>
       </c>
       <c r="F458">
-        <f>ROUND(E458/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>1.3</v>
       </c>
     </row>
@@ -10607,7 +10639,7 @@
         <v>1150208446800</v>
       </c>
       <c r="F459">
-        <f>ROUND(E459/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>19.2</v>
       </c>
     </row>
@@ -10628,7 +10660,7 @@
         <v>452522287100</v>
       </c>
       <c r="F460">
-        <f>ROUND(E460/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>7.5</v>
       </c>
     </row>
@@ -10649,7 +10681,7 @@
         <v>89708184900</v>
       </c>
       <c r="F461">
-        <f>ROUND(E461/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>1.5</v>
       </c>
     </row>
@@ -10670,7 +10702,7 @@
         <v>1066021703700</v>
       </c>
       <c r="F462">
-        <f>ROUND(E462/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>17.8</v>
       </c>
     </row>
@@ -10691,7 +10723,7 @@
         <v>104902898400</v>
       </c>
       <c r="F463">
-        <f>ROUND(E463/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>1.7</v>
       </c>
     </row>
@@ -10712,7 +10744,7 @@
         <v>651180560600</v>
       </c>
       <c r="F464">
-        <f>ROUND(E464/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>10.9</v>
       </c>
     </row>
@@ -10733,7 +10765,7 @@
         <v>1462477166800</v>
       </c>
       <c r="F465">
-        <f>ROUND(E465/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>24.4</v>
       </c>
     </row>
@@ -10754,7 +10786,7 @@
         <v>114143348100</v>
       </c>
       <c r="F466">
-        <f>ROUND(E466/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>1.9</v>
       </c>
     </row>
@@ -10775,7 +10807,7 @@
         <v>1175909573600</v>
       </c>
       <c r="F467">
-        <f>ROUND(E467/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>19.600000000000001</v>
       </c>
     </row>
@@ -10796,7 +10828,7 @@
         <v>432535163400</v>
       </c>
       <c r="F468">
-        <f>ROUND(E468/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>7.2</v>
       </c>
     </row>
@@ -10817,7 +10849,7 @@
         <v>91518548100</v>
       </c>
       <c r="F469">
-        <f>ROUND(E469/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>1.5</v>
       </c>
     </row>
@@ -10838,7 +10870,7 @@
         <v>1009740483600</v>
       </c>
       <c r="F470">
-        <f>ROUND(E470/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>16.8</v>
       </c>
     </row>
@@ -10859,7 +10891,7 @@
         <v>438067394000</v>
       </c>
       <c r="F471">
-        <f>ROUND(E471/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>7.3</v>
       </c>
     </row>
@@ -10880,7 +10912,7 @@
         <v>37320018600</v>
       </c>
       <c r="F472">
-        <f>ROUND(E472/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>0.6</v>
       </c>
     </row>
@@ -10901,7 +10933,7 @@
         <v>122672680300</v>
       </c>
       <c r="F473">
-        <f>ROUND(E473/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
@@ -10922,7 +10954,7 @@
         <v>310965823500</v>
       </c>
       <c r="F474">
-        <f>ROUND(E474/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>5.2</v>
       </c>
     </row>
@@ -10943,7 +10975,7 @@
         <v>33244600600</v>
       </c>
       <c r="F475">
-        <f>ROUND(E475/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>0.6</v>
       </c>
     </row>
@@ -10964,7 +10996,7 @@
         <v>118371956300</v>
       </c>
       <c r="F476">
-        <f>ROUND(E476/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
@@ -10985,7 +11017,7 @@
         <v>278235564100</v>
       </c>
       <c r="F477">
-        <f>ROUND(E477/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -11006,7 +11038,7 @@
         <v>33423260600</v>
       </c>
       <c r="F478">
-        <f>ROUND(E478/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>0.6</v>
       </c>
     </row>
@@ -11027,7 +11059,7 @@
         <v>139094404799</v>
       </c>
       <c r="F479">
-        <f>ROUND(E479/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>2.2999999999999998</v>
       </c>
     </row>
@@ -11048,7 +11080,7 @@
         <v>353462900399</v>
       </c>
       <c r="F480">
-        <f>ROUND(E480/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>5.9</v>
       </c>
     </row>
@@ -11069,7 +11101,7 @@
         <v>30969618400</v>
       </c>
       <c r="F481">
-        <f>ROUND(E481/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
     </row>
@@ -11090,7 +11122,7 @@
         <v>123123151400</v>
       </c>
       <c r="F482">
-        <f>ROUND(E482/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>2.1</v>
       </c>
     </row>
@@ -11111,7 +11143,7 @@
         <v>365761882300</v>
       </c>
       <c r="F483">
-        <f>ROUND(E483/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>6.1</v>
       </c>
     </row>
@@ -11132,7 +11164,7 @@
         <v>32932236300</v>
       </c>
       <c r="F484">
-        <f>ROUND(E484/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
     </row>
@@ -11153,7 +11185,7 @@
         <v>166489049400</v>
       </c>
       <c r="F485">
-        <f>ROUND(E485/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>2.8</v>
       </c>
     </row>
@@ -11174,7 +11206,7 @@
         <v>385916159100</v>
       </c>
       <c r="F486">
-        <f>ROUND(E486/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>6.4</v>
       </c>
     </row>
@@ -11195,7 +11227,7 @@
         <v>42553323700</v>
       </c>
       <c r="F487">
-        <f>ROUND(E487/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>0.7</v>
       </c>
     </row>
@@ -11216,7 +11248,7 @@
         <v>165964655900</v>
       </c>
       <c r="F488">
-        <f>ROUND(E488/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>2.8</v>
       </c>
     </row>
@@ -11237,7 +11269,7 @@
         <v>398648560800</v>
       </c>
       <c r="F489">
-        <f>ROUND(E489/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>6.6</v>
       </c>
     </row>
@@ -11258,7 +11290,7 @@
         <v>37764401300</v>
       </c>
       <c r="F490">
-        <f>ROUND(E490/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>0.6</v>
       </c>
     </row>
@@ -11279,7 +11311,7 @@
         <v>147291328100</v>
       </c>
       <c r="F491">
-        <f>ROUND(E491/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>2.5</v>
       </c>
     </row>
@@ -11300,7 +11332,7 @@
         <v>379402750100</v>
       </c>
       <c r="F492">
-        <f>ROUND(E492/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>6.3</v>
       </c>
     </row>
@@ -11321,7 +11353,7 @@
         <v>42670818500</v>
       </c>
       <c r="F493">
-        <f>ROUND(E493/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>0.7</v>
       </c>
     </row>
@@ -11342,7 +11374,7 @@
         <v>161820175800</v>
       </c>
       <c r="F494">
-        <f>ROUND(E494/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>2.7</v>
       </c>
     </row>
@@ -11363,7 +11395,7 @@
         <v>387244678600</v>
       </c>
       <c r="F495">
-        <f>ROUND(E495/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>6.5</v>
       </c>
     </row>
@@ -11384,7 +11416,7 @@
         <v>35873861900</v>
       </c>
       <c r="F496">
-        <f>ROUND(E496/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>0.6</v>
       </c>
     </row>
@@ -11405,7 +11437,7 @@
         <v>156095024600</v>
       </c>
       <c r="F497">
-        <f>ROUND(E497/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>2.6</v>
       </c>
     </row>
@@ -11426,7 +11458,7 @@
         <v>473808327400</v>
       </c>
       <c r="F498">
-        <f>ROUND(E498/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>7.9</v>
       </c>
     </row>
@@ -11447,7 +11479,7 @@
         <v>42675557800</v>
       </c>
       <c r="F499">
-        <f>ROUND(E499/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>0.7</v>
       </c>
     </row>
@@ -11468,7 +11500,7 @@
         <v>101479085500</v>
       </c>
       <c r="F500">
-        <f>ROUND(E500/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>1.7</v>
       </c>
     </row>
@@ -11489,7 +11521,7 @@
         <v>466086288300</v>
       </c>
       <c r="F501">
-        <f>ROUND(E501/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>7.8</v>
       </c>
     </row>
@@ -11510,7 +11542,7 @@
         <v>1293078684800</v>
       </c>
       <c r="F502">
-        <f>ROUND(E502/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>21.6</v>
       </c>
     </row>
@@ -11531,7 +11563,7 @@
         <v>67777749000</v>
       </c>
       <c r="F503">
-        <f>ROUND(E503/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>1.1000000000000001</v>
       </c>
     </row>
@@ -11552,7 +11584,7 @@
         <v>946682853200</v>
       </c>
       <c r="F504">
-        <f>ROUND(E504/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>15.8</v>
       </c>
     </row>
@@ -11573,7 +11605,7 @@
         <v>468541329000</v>
       </c>
       <c r="F505">
-        <f>ROUND(E505/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>7.8</v>
       </c>
     </row>
@@ -11594,7 +11626,7 @@
         <v>94163107500</v>
       </c>
       <c r="F506">
-        <f>ROUND(E506/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>1.6</v>
       </c>
     </row>
@@ -11615,7 +11647,7 @@
         <v>1202791202000</v>
       </c>
       <c r="F507">
-        <f>ROUND(E507/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
     </row>
@@ -11636,7 +11668,7 @@
         <v>415174290600</v>
       </c>
       <c r="F508">
-        <f>ROUND(E508/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>6.9</v>
       </c>
     </row>
@@ -11657,7 +11689,7 @@
         <v>88450903100</v>
       </c>
       <c r="F509">
-        <f>ROUND(E509/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>1.5</v>
       </c>
     </row>
@@ -11678,7 +11710,7 @@
         <v>2651810591400</v>
       </c>
       <c r="F510">
-        <f>ROUND(E510/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>44.2</v>
       </c>
     </row>
@@ -11699,7 +11731,7 @@
         <v>321937760100</v>
       </c>
       <c r="F511">
-        <f>ROUND(E511/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>5.4</v>
       </c>
     </row>
@@ -11720,7 +11752,7 @@
         <v>86978856500</v>
       </c>
       <c r="F512">
-        <f>ROUND(E512/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>1.4</v>
       </c>
     </row>
@@ -11741,7 +11773,7 @@
         <v>85281095400</v>
       </c>
       <c r="F513">
-        <f>ROUND(E513/60000000000, 1)</f>
+        <f t="shared" si="7"/>
         <v>1.4</v>
       </c>
     </row>
@@ -11762,7 +11794,7 @@
         <v>16603734400</v>
       </c>
       <c r="F514">
-        <f>ROUND(E514/60000000000, 1)</f>
+        <f t="shared" ref="F514:F577" si="8">ROUND(E514/60000000000, 1)</f>
         <v>0.3</v>
       </c>
     </row>
@@ -11783,7 +11815,7 @@
         <v>69707484400</v>
       </c>
       <c r="F515">
-        <f>ROUND(E515/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>1.2</v>
       </c>
     </row>
@@ -11804,7 +11836,7 @@
         <v>115866096200</v>
       </c>
       <c r="F516">
-        <f>ROUND(E516/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>1.9</v>
       </c>
     </row>
@@ -11825,7 +11857,7 @@
         <v>307165262000</v>
       </c>
       <c r="F517">
-        <f>ROUND(E517/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>5.0999999999999996</v>
       </c>
     </row>
@@ -11846,7 +11878,7 @@
         <v>4884922400</v>
       </c>
       <c r="F518">
-        <f>ROUND(E518/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>0.1</v>
       </c>
     </row>
@@ -11867,7 +11899,7 @@
         <v>5739440000</v>
       </c>
       <c r="F519">
-        <f>ROUND(E519/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>0.1</v>
       </c>
     </row>
@@ -11888,7 +11920,7 @@
         <v>7346262300</v>
       </c>
       <c r="F520">
-        <f>ROUND(E520/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>0.1</v>
       </c>
     </row>
@@ -11909,7 +11941,7 @@
         <v>1460378700</v>
       </c>
       <c r="F521">
-        <f>ROUND(E521/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -11930,7 +11962,7 @@
         <v>1989599300</v>
       </c>
       <c r="F522">
-        <f>ROUND(E522/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -11951,7 +11983,7 @@
         <v>2003684800</v>
       </c>
       <c r="F523">
-        <f>ROUND(E523/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -11972,7 +12004,7 @@
         <v>207517283800</v>
       </c>
       <c r="F524">
-        <f>ROUND(E524/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>3.5</v>
       </c>
     </row>
@@ -11993,7 +12025,7 @@
         <v>425582935600</v>
       </c>
       <c r="F525">
-        <f>ROUND(E525/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>7.1</v>
       </c>
     </row>
@@ -12014,7 +12046,7 @@
         <v>70801365401</v>
       </c>
       <c r="F526">
-        <f>ROUND(E526/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>1.2</v>
       </c>
     </row>
@@ -12035,7 +12067,7 @@
         <v>1187596647501</v>
       </c>
       <c r="F527">
-        <f>ROUND(E527/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>19.8</v>
       </c>
     </row>
@@ -12056,7 +12088,7 @@
         <v>478451565300</v>
       </c>
       <c r="F528">
-        <f>ROUND(E528/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
     </row>
@@ -12077,7 +12109,7 @@
         <v>95189440800</v>
       </c>
       <c r="F529">
-        <f>ROUND(E529/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>1.6</v>
       </c>
     </row>
@@ -12098,7 +12130,7 @@
         <v>1231337658300</v>
       </c>
       <c r="F530">
-        <f>ROUND(E530/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>20.5</v>
       </c>
     </row>
@@ -12119,7 +12151,7 @@
         <v>626103617600</v>
       </c>
       <c r="F531">
-        <f>ROUND(E531/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>10.4</v>
       </c>
     </row>
@@ -12140,7 +12172,7 @@
         <v>104543345300</v>
       </c>
       <c r="F532">
-        <f>ROUND(E532/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>1.7</v>
       </c>
     </row>
@@ -12161,7 +12193,7 @@
         <v>1318698840300</v>
       </c>
       <c r="F533">
-        <f>ROUND(E533/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
     </row>
@@ -12182,7 +12214,7 @@
         <v>495906874400</v>
       </c>
       <c r="F534">
-        <f>ROUND(E534/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>8.3000000000000007</v>
       </c>
     </row>
@@ -12203,7 +12235,7 @@
         <v>133589812600</v>
       </c>
       <c r="F535">
-        <f>ROUND(E535/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -12224,7 +12256,7 @@
         <v>1068032220200</v>
       </c>
       <c r="F536">
-        <f>ROUND(E536/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>17.8</v>
       </c>
     </row>
@@ -12245,7 +12277,7 @@
         <v>491419355900</v>
       </c>
       <c r="F537">
-        <f>ROUND(E537/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>8.1999999999999993</v>
       </c>
     </row>
@@ -12266,7 +12298,7 @@
         <v>118281340100</v>
       </c>
       <c r="F538">
-        <f>ROUND(E538/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
     </row>
@@ -12287,7 +12319,7 @@
         <v>1477244753300</v>
       </c>
       <c r="F539">
-        <f>ROUND(E539/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>24.6</v>
       </c>
     </row>
@@ -12308,7 +12340,7 @@
         <v>499869811700</v>
       </c>
       <c r="F540">
-        <f>ROUND(E540/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>8.3000000000000007</v>
       </c>
     </row>
@@ -12329,7 +12361,7 @@
         <v>93438573000</v>
       </c>
       <c r="F541">
-        <f>ROUND(E541/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>1.6</v>
       </c>
     </row>
@@ -12350,7 +12382,7 @@
         <v>530382031400</v>
       </c>
       <c r="F542">
-        <f>ROUND(E542/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>8.8000000000000007</v>
       </c>
     </row>
@@ -12371,7 +12403,7 @@
         <v>1525097162400</v>
       </c>
       <c r="F543">
-        <f>ROUND(E543/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>25.4</v>
       </c>
     </row>
@@ -12392,7 +12424,7 @@
         <v>113301537100</v>
       </c>
       <c r="F544">
-        <f>ROUND(E544/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>1.9</v>
       </c>
     </row>
@@ -12413,7 +12445,7 @@
         <v>1182320568800</v>
       </c>
       <c r="F545">
-        <f>ROUND(E545/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>19.7</v>
       </c>
     </row>
@@ -12434,7 +12466,7 @@
         <v>40959041700</v>
       </c>
       <c r="F546">
-        <f>ROUND(E546/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>0.7</v>
       </c>
     </row>
@@ -12455,7 +12487,7 @@
         <v>161448455700</v>
       </c>
       <c r="F547">
-        <f>ROUND(E547/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>2.7</v>
       </c>
     </row>
@@ -12476,7 +12508,7 @@
         <v>276594763800</v>
       </c>
       <c r="F548">
-        <f>ROUND(E548/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -12497,7 +12529,7 @@
         <v>40592949800</v>
       </c>
       <c r="F549">
-        <f>ROUND(E549/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>0.7</v>
       </c>
     </row>
@@ -12518,7 +12550,7 @@
         <v>142011854900</v>
       </c>
       <c r="F550">
-        <f>ROUND(E550/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>2.4</v>
       </c>
     </row>
@@ -12539,7 +12571,7 @@
         <v>288002689900</v>
       </c>
       <c r="F551">
-        <f>ROUND(E551/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>4.8</v>
       </c>
     </row>
@@ -12560,7 +12592,7 @@
         <v>34285858100</v>
       </c>
       <c r="F552">
-        <f>ROUND(E552/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>0.6</v>
       </c>
     </row>
@@ -12581,7 +12613,7 @@
         <v>148790046100</v>
       </c>
       <c r="F553">
-        <f>ROUND(E553/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>2.5</v>
       </c>
     </row>
@@ -12602,7 +12634,7 @@
         <v>334821017900</v>
       </c>
       <c r="F554">
-        <f>ROUND(E554/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>5.6</v>
       </c>
     </row>
@@ -12623,7 +12655,7 @@
         <v>40537220400</v>
       </c>
       <c r="F555">
-        <f>ROUND(E555/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>0.7</v>
       </c>
     </row>
@@ -12644,7 +12676,7 @@
         <v>148069100700</v>
       </c>
       <c r="F556">
-        <f>ROUND(E556/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>2.5</v>
       </c>
     </row>
@@ -12665,7 +12697,7 @@
         <v>451012884600</v>
       </c>
       <c r="F557">
-        <f>ROUND(E557/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>7.5</v>
       </c>
     </row>
@@ -12686,7 +12718,7 @@
         <v>37930160500</v>
       </c>
       <c r="F558">
-        <f>ROUND(E558/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>0.6</v>
       </c>
     </row>
@@ -12707,7 +12739,7 @@
         <v>186577453600</v>
       </c>
       <c r="F559">
-        <f>ROUND(E559/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>3.1</v>
       </c>
     </row>
@@ -12728,7 +12760,7 @@
         <v>393369956000</v>
       </c>
       <c r="F560">
-        <f>ROUND(E560/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>6.6</v>
       </c>
     </row>
@@ -12749,7 +12781,7 @@
         <v>43468435600</v>
       </c>
       <c r="F561">
-        <f>ROUND(E561/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>0.7</v>
       </c>
     </row>
@@ -12770,7 +12802,7 @@
         <v>189859062500</v>
       </c>
       <c r="F562">
-        <f>ROUND(E562/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>3.2</v>
       </c>
     </row>
@@ -12791,7 +12823,7 @@
         <v>499530327900</v>
       </c>
       <c r="F563">
-        <f>ROUND(E563/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>8.3000000000000007</v>
       </c>
     </row>
@@ -12812,7 +12844,7 @@
         <v>43467916100</v>
       </c>
       <c r="F564">
-        <f>ROUND(E564/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>0.7</v>
       </c>
     </row>
@@ -12833,7 +12865,7 @@
         <v>171795673100</v>
       </c>
       <c r="F565">
-        <f>ROUND(E565/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>2.9</v>
       </c>
     </row>
@@ -12854,7 +12886,7 @@
         <v>432839415300</v>
       </c>
       <c r="F566">
-        <f>ROUND(E566/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>7.2</v>
       </c>
     </row>
@@ -12875,7 +12907,7 @@
         <v>55184476300</v>
       </c>
       <c r="F567">
-        <f>ROUND(E567/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>0.9</v>
       </c>
     </row>
@@ -12896,7 +12928,7 @@
         <v>190530338900</v>
       </c>
       <c r="F568">
-        <f>ROUND(E568/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>3.2</v>
       </c>
     </row>
@@ -12917,7 +12949,7 @@
         <v>444098645700</v>
       </c>
       <c r="F569">
-        <f>ROUND(E569/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>7.4</v>
       </c>
     </row>
@@ -12938,7 +12970,7 @@
         <v>51521167400</v>
       </c>
       <c r="F570">
-        <f>ROUND(E570/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>0.9</v>
       </c>
     </row>
@@ -12959,7 +12991,7 @@
         <v>228676255900</v>
       </c>
       <c r="F571">
-        <f>ROUND(E571/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>3.8</v>
       </c>
     </row>
@@ -12980,7 +13012,7 @@
         <v>316465741600</v>
       </c>
       <c r="F572">
-        <f>ROUND(E572/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>5.3</v>
       </c>
     </row>
@@ -13001,7 +13033,7 @@
         <v>41434673600</v>
       </c>
       <c r="F573">
-        <f>ROUND(E573/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>0.7</v>
       </c>
     </row>
@@ -13022,7 +13054,7 @@
         <v>510506061700</v>
       </c>
       <c r="F574">
-        <f>ROUND(E574/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>8.5</v>
       </c>
     </row>
@@ -13043,7 +13075,7 @@
         <v>101234268200</v>
       </c>
       <c r="F575">
-        <f>ROUND(E575/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>1.7</v>
       </c>
     </row>
@@ -13064,7 +13096,7 @@
         <v>1163814786300</v>
       </c>
       <c r="F576">
-        <f>ROUND(E576/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>19.399999999999999</v>
       </c>
     </row>
@@ -13085,7 +13117,7 @@
         <v>560295973400</v>
       </c>
       <c r="F577">
-        <f>ROUND(E577/60000000000, 1)</f>
+        <f t="shared" si="8"/>
         <v>9.3000000000000007</v>
       </c>
     </row>
@@ -13106,7 +13138,7 @@
         <v>103599231200</v>
       </c>
       <c r="F578">
-        <f>ROUND(E578/60000000000, 1)</f>
+        <f t="shared" ref="F578:F641" si="9">ROUND(E578/60000000000, 1)</f>
         <v>1.7</v>
       </c>
     </row>
@@ -13127,7 +13159,7 @@
         <v>733226697200</v>
       </c>
       <c r="F579">
-        <f>ROUND(E579/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>12.2</v>
       </c>
     </row>
@@ -13148,7 +13180,7 @@
         <v>123203330900</v>
       </c>
       <c r="F580">
-        <f>ROUND(E580/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>2.1</v>
       </c>
     </row>
@@ -13169,7 +13201,7 @@
         <v>2019832216900</v>
       </c>
       <c r="F581">
-        <f>ROUND(E581/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>33.700000000000003</v>
       </c>
     </row>
@@ -13190,7 +13222,7 @@
         <v>3292025204900</v>
       </c>
       <c r="F582">
-        <f>ROUND(E582/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>54.9</v>
       </c>
     </row>
@@ -13211,7 +13243,7 @@
         <v>100732654700</v>
       </c>
       <c r="F583">
-        <f>ROUND(E583/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>1.7</v>
       </c>
     </row>
@@ -13232,7 +13264,7 @@
         <v>1144678472699</v>
       </c>
       <c r="F584">
-        <f>ROUND(E584/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>19.100000000000001</v>
       </c>
     </row>
@@ -13253,7 +13285,7 @@
         <v>312963337500</v>
       </c>
       <c r="F585">
-        <f>ROUND(E585/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>5.2</v>
       </c>
     </row>
@@ -13274,7 +13306,7 @@
         <v>141871510900</v>
       </c>
       <c r="F586">
-        <f>ROUND(E586/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>2.4</v>
       </c>
     </row>
@@ -13295,7 +13327,7 @@
         <v>1893970900</v>
       </c>
       <c r="F587">
-        <f>ROUND(E587/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -13316,7 +13348,7 @@
         <v>802540400</v>
       </c>
       <c r="F588">
-        <f>ROUND(E588/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -13337,7 +13369,7 @@
         <v>962627400</v>
       </c>
       <c r="F589">
-        <f>ROUND(E589/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -13358,7 +13390,7 @@
         <v>5906469500</v>
       </c>
       <c r="F590">
-        <f>ROUND(E590/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0.1</v>
       </c>
     </row>
@@ -13379,7 +13411,7 @@
         <v>1093592200</v>
       </c>
       <c r="F591">
-        <f>ROUND(E591/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -13400,7 +13432,7 @@
         <v>1568688600</v>
       </c>
       <c r="F592">
-        <f>ROUND(E592/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -13421,7 +13453,7 @@
         <v>1181865000</v>
       </c>
       <c r="F593">
-        <f>ROUND(E593/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -13442,7 +13474,7 @@
         <v>1528670300</v>
       </c>
       <c r="F594">
-        <f>ROUND(E594/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -13463,7 +13495,7 @@
         <v>276240900</v>
       </c>
       <c r="F595">
-        <f>ROUND(E595/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -13484,7 +13516,7 @@
         <v>18405542900</v>
       </c>
       <c r="F596">
-        <f>ROUND(E596/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0.3</v>
       </c>
     </row>
@@ -13505,7 +13537,7 @@
         <v>90319390700</v>
       </c>
       <c r="F597">
-        <f>ROUND(E597/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>1.5</v>
       </c>
     </row>
@@ -13526,7 +13558,7 @@
         <v>129486624900</v>
       </c>
       <c r="F598">
-        <f>ROUND(E598/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -13547,7 +13579,7 @@
         <v>80466587100</v>
       </c>
       <c r="F599">
-        <f>ROUND(E599/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>1.3</v>
       </c>
     </row>
@@ -13568,7 +13600,7 @@
         <v>182489600</v>
       </c>
       <c r="F600">
-        <f>ROUND(E600/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -13589,7 +13621,7 @@
         <v>440861100</v>
       </c>
       <c r="F601">
-        <f>ROUND(E601/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -13610,7 +13642,7 @@
         <v>594375400</v>
       </c>
       <c r="F602">
-        <f>ROUND(E602/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -13631,7 +13663,7 @@
         <v>412446200</v>
       </c>
       <c r="F603">
-        <f>ROUND(E603/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -13652,7 +13684,7 @@
         <v>3960075321600</v>
       </c>
       <c r="F604">
-        <f>ROUND(E604/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>66</v>
       </c>
     </row>
@@ -13673,7 +13705,7 @@
         <v>29521577100</v>
       </c>
       <c r="F605">
-        <f>ROUND(E605/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
     </row>
@@ -13694,7 +13726,7 @@
         <v>167816212400</v>
       </c>
       <c r="F606">
-        <f>ROUND(E606/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>2.8</v>
       </c>
     </row>
@@ -13715,7 +13747,7 @@
         <v>329593662200</v>
       </c>
       <c r="F607">
-        <f>ROUND(E607/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>5.5</v>
       </c>
     </row>
@@ -13736,7 +13768,7 @@
         <v>25852844600</v>
       </c>
       <c r="F608">
-        <f>ROUND(E608/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
     </row>
@@ -13757,7 +13789,7 @@
         <v>116221538300</v>
       </c>
       <c r="F609">
-        <f>ROUND(E609/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>1.9</v>
       </c>
     </row>
@@ -13778,7 +13810,7 @@
         <v>311546559700</v>
       </c>
       <c r="F610">
-        <f>ROUND(E610/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>5.2</v>
       </c>
     </row>
@@ -13799,7 +13831,7 @@
         <v>29111894600</v>
       </c>
       <c r="F611">
-        <f>ROUND(E611/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
     </row>
@@ -13820,7 +13852,7 @@
         <v>129027793200</v>
       </c>
       <c r="F612">
-        <f>ROUND(E612/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -13841,7 +13873,7 @@
         <v>322987688300</v>
       </c>
       <c r="F613">
-        <f>ROUND(E613/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>5.4</v>
       </c>
     </row>
@@ -13862,7 +13894,7 @@
         <v>31271190200</v>
       </c>
       <c r="F614">
-        <f>ROUND(E614/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
     </row>
@@ -13883,7 +13915,7 @@
         <v>131747073000</v>
       </c>
       <c r="F615">
-        <f>ROUND(E615/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -13904,7 +13936,7 @@
         <v>364878958200</v>
       </c>
       <c r="F616">
-        <f>ROUND(E616/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>6.1</v>
       </c>
     </row>
@@ -13925,7 +13957,7 @@
         <v>36558000500</v>
       </c>
       <c r="F617">
-        <f>ROUND(E617/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0.6</v>
       </c>
     </row>
@@ -13946,7 +13978,7 @@
         <v>150246826900</v>
       </c>
       <c r="F618">
-        <f>ROUND(E618/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>2.5</v>
       </c>
     </row>
@@ -13967,7 +13999,7 @@
         <v>389942137400</v>
       </c>
       <c r="F619">
-        <f>ROUND(E619/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>6.5</v>
       </c>
     </row>
@@ -13988,7 +14020,7 @@
         <v>32097200300</v>
       </c>
       <c r="F620">
-        <f>ROUND(E620/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
     </row>
@@ -14009,7 +14041,7 @@
         <v>166650282300</v>
       </c>
       <c r="F621">
-        <f>ROUND(E621/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>2.8</v>
       </c>
     </row>
@@ -14030,7 +14062,7 @@
         <v>381138026900</v>
       </c>
       <c r="F622">
-        <f>ROUND(E622/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>6.4</v>
       </c>
     </row>
@@ -14051,7 +14083,7 @@
         <v>40657590900</v>
       </c>
       <c r="F623">
-        <f>ROUND(E623/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0.7</v>
       </c>
     </row>
@@ -14072,7 +14104,7 @@
         <v>142023875700</v>
       </c>
       <c r="F624">
-        <f>ROUND(E624/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>2.4</v>
       </c>
     </row>
@@ -14093,7 +14125,7 @@
         <v>379099522300</v>
       </c>
       <c r="F625">
-        <f>ROUND(E625/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>6.3</v>
       </c>
     </row>
@@ -14114,7 +14146,7 @@
         <v>34088131100</v>
       </c>
       <c r="F626">
-        <f>ROUND(E626/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0.6</v>
       </c>
     </row>
@@ -14135,7 +14167,7 @@
         <v>125679472800</v>
       </c>
       <c r="F627">
-        <f>ROUND(E627/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>2.1</v>
       </c>
     </row>
@@ -14156,7 +14188,7 @@
         <v>407922673600</v>
       </c>
       <c r="F628">
-        <f>ROUND(E628/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>6.8</v>
       </c>
     </row>
@@ -14177,7 +14209,7 @@
         <v>31071341400</v>
       </c>
       <c r="F629">
-        <f>ROUND(E629/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
     </row>
@@ -14198,7 +14230,7 @@
         <v>194212194300</v>
       </c>
       <c r="F630">
-        <f>ROUND(E630/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>3.2</v>
       </c>
     </row>
@@ -14219,7 +14251,7 @@
         <v>330420763500</v>
       </c>
       <c r="F631">
-        <f>ROUND(E631/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>5.5</v>
       </c>
     </row>
@@ -14240,7 +14272,7 @@
         <v>33455588400</v>
       </c>
       <c r="F632">
-        <f>ROUND(E632/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0.6</v>
       </c>
     </row>
@@ -14261,7 +14293,7 @@
         <v>98921298800</v>
       </c>
       <c r="F633">
-        <f>ROUND(E633/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>1.6</v>
       </c>
     </row>
@@ -14282,7 +14314,7 @@
         <v>229209100</v>
       </c>
       <c r="F634">
-        <f>ROUND(E634/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -14303,7 +14335,7 @@
         <v>424108100</v>
       </c>
       <c r="F635">
-        <f>ROUND(E635/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -14324,7 +14356,7 @@
         <v>732338900</v>
       </c>
       <c r="F636">
-        <f>ROUND(E636/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -14345,7 +14377,7 @@
         <v>7224269900</v>
       </c>
       <c r="F637">
-        <f>ROUND(E637/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0.1</v>
       </c>
     </row>
@@ -14366,7 +14398,7 @@
         <v>105239700</v>
       </c>
       <c r="F638">
-        <f>ROUND(E638/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -14387,7 +14419,7 @@
         <v>178599200</v>
       </c>
       <c r="F639">
-        <f>ROUND(E639/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -14408,7 +14440,7 @@
         <v>294253200</v>
       </c>
       <c r="F640">
-        <f>ROUND(E640/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -14429,7 +14461,7 @@
         <v>475551400</v>
       </c>
       <c r="F641">
-        <f>ROUND(E641/60000000000, 1)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -14450,7 +14482,7 @@
         <v>60219613200</v>
       </c>
       <c r="F642">
-        <f>ROUND(E642/60000000000, 1)</f>
+        <f t="shared" ref="F642:F705" si="10">ROUND(E642/60000000000, 1)</f>
         <v>1</v>
       </c>
     </row>
@@ -14471,7 +14503,7 @@
         <v>308660859200</v>
       </c>
       <c r="F643">
-        <f>ROUND(E643/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>5.0999999999999996</v>
       </c>
     </row>
@@ -14492,7 +14524,7 @@
         <v>129320763600</v>
       </c>
       <c r="F644">
-        <f>ROUND(E644/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -14513,7 +14545,7 @@
         <v>16718633300</v>
       </c>
       <c r="F645">
-        <f>ROUND(E645/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>0.3</v>
       </c>
     </row>
@@ -14534,7 +14566,7 @@
         <v>62712146200</v>
       </c>
       <c r="F646">
-        <f>ROUND(E646/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
     </row>
@@ -14555,7 +14587,7 @@
         <v>135692526900</v>
       </c>
       <c r="F647">
-        <f>ROUND(E647/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>2.2999999999999998</v>
       </c>
     </row>
@@ -14576,7 +14608,7 @@
         <v>77145604400</v>
       </c>
       <c r="F648">
-        <f>ROUND(E648/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>1.3</v>
       </c>
     </row>
@@ -14597,7 +14629,7 @@
         <v>759230400</v>
       </c>
       <c r="F649">
-        <f>ROUND(E649/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -14618,7 +14650,7 @@
         <v>793655800</v>
       </c>
       <c r="F650">
-        <f>ROUND(E650/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -14639,7 +14671,7 @@
         <v>658006200</v>
       </c>
       <c r="F651">
-        <f>ROUND(E651/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -14660,7 +14692,7 @@
         <v>1259671600</v>
       </c>
       <c r="F652">
-        <f>ROUND(E652/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -14681,7 +14713,7 @@
         <v>1108063600</v>
       </c>
       <c r="F653">
-        <f>ROUND(E653/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -14702,7 +14734,7 @@
         <v>1904324401</v>
       </c>
       <c r="F654">
-        <f>ROUND(E654/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -14723,7 +14755,7 @@
         <v>207021200</v>
       </c>
       <c r="F655">
-        <f>ROUND(E655/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -14744,7 +14776,7 @@
         <v>337710500</v>
       </c>
       <c r="F656">
-        <f>ROUND(E656/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -14765,7 +14797,7 @@
         <v>639311900</v>
       </c>
       <c r="F657">
-        <f>ROUND(E657/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -14786,7 +14818,7 @@
         <v>741701100</v>
       </c>
       <c r="F658">
-        <f>ROUND(E658/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -14807,7 +14839,7 @@
         <v>128914160600</v>
       </c>
       <c r="F659">
-        <f>ROUND(E659/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>2.1</v>
       </c>
     </row>
@@ -14828,7 +14860,7 @@
         <v>630716304200</v>
       </c>
       <c r="F660">
-        <f>ROUND(E660/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>10.5</v>
       </c>
     </row>
@@ -14849,7 +14881,7 @@
         <v>122366941600</v>
       </c>
       <c r="F661">
-        <f>ROUND(E661/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
     </row>
@@ -14870,7 +14902,7 @@
         <v>79638767899</v>
       </c>
       <c r="F662">
-        <f>ROUND(E662/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>1.3</v>
       </c>
     </row>
@@ -14891,7 +14923,7 @@
         <v>379485554600</v>
       </c>
       <c r="F663">
-        <f>ROUND(E663/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>6.3</v>
       </c>
     </row>
@@ -14912,7 +14944,7 @@
         <v>82941001700</v>
       </c>
       <c r="F664">
-        <f>ROUND(E664/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>1.4</v>
       </c>
     </row>
@@ -14933,7 +14965,7 @@
         <v>866078797001</v>
       </c>
       <c r="F665">
-        <f>ROUND(E665/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>14.4</v>
       </c>
     </row>
@@ -14954,7 +14986,7 @@
         <v>83995101900</v>
       </c>
       <c r="F666">
-        <f>ROUND(E666/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>1.4</v>
       </c>
     </row>
@@ -14975,7 +15007,7 @@
         <v>992875570900</v>
       </c>
       <c r="F667">
-        <f>ROUND(E667/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>16.5</v>
       </c>
     </row>
@@ -14996,7 +15028,7 @@
         <v>464042496800</v>
       </c>
       <c r="F668">
-        <f>ROUND(E668/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>7.7</v>
       </c>
     </row>
@@ -15017,7 +15049,7 @@
         <v>91977917100</v>
       </c>
       <c r="F669">
-        <f>ROUND(E669/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>1.5</v>
       </c>
     </row>
@@ -15038,7 +15070,7 @@
         <v>1054501405500</v>
       </c>
       <c r="F670">
-        <f>ROUND(E670/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>17.600000000000001</v>
       </c>
     </row>
@@ -15059,7 +15091,7 @@
         <v>486834972300</v>
       </c>
       <c r="F671">
-        <f>ROUND(E671/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>8.1</v>
       </c>
     </row>
@@ -15080,7 +15112,7 @@
         <v>85459285300</v>
       </c>
       <c r="F672">
-        <f>ROUND(E672/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>1.4</v>
       </c>
     </row>
@@ -15101,7 +15133,7 @@
         <v>1171273088700</v>
       </c>
       <c r="F673">
-        <f>ROUND(E673/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>19.5</v>
       </c>
     </row>
@@ -15122,7 +15154,7 @@
         <v>409329137500</v>
       </c>
       <c r="F674">
-        <f>ROUND(E674/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>6.8</v>
       </c>
     </row>
@@ -15143,7 +15175,7 @@
         <v>75958840100</v>
       </c>
       <c r="F675">
-        <f>ROUND(E675/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>1.3</v>
       </c>
     </row>
@@ -15164,7 +15196,7 @@
         <v>1184330111900</v>
       </c>
       <c r="F676">
-        <f>ROUND(E676/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>19.7</v>
       </c>
     </row>
@@ -15185,7 +15217,7 @@
         <v>540393009700</v>
       </c>
       <c r="F677">
-        <f>ROUND(E677/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
     </row>
@@ -15206,7 +15238,7 @@
         <v>95767424200</v>
       </c>
       <c r="F678">
-        <f>ROUND(E678/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>1.6</v>
       </c>
     </row>
@@ -15227,7 +15259,7 @@
         <v>1272299081000</v>
       </c>
       <c r="F679">
-        <f>ROUND(E679/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>21.2</v>
       </c>
     </row>
@@ -15248,7 +15280,7 @@
         <v>374993408300</v>
       </c>
       <c r="F680">
-        <f>ROUND(E680/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>6.2</v>
       </c>
     </row>
@@ -15269,7 +15301,7 @@
         <v>95868558100</v>
       </c>
       <c r="F681">
-        <f>ROUND(E681/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>1.6</v>
       </c>
     </row>
@@ -15290,7 +15322,7 @@
         <v>917394517900</v>
       </c>
       <c r="F682">
-        <f>ROUND(E682/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>15.3</v>
       </c>
     </row>
@@ -15311,7 +15343,7 @@
         <v>438945642000</v>
       </c>
       <c r="F683">
-        <f>ROUND(E683/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>7.3</v>
       </c>
     </row>
@@ -15332,7 +15364,7 @@
         <v>41768484300</v>
       </c>
       <c r="F684">
-        <f>ROUND(E684/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>0.7</v>
       </c>
     </row>
@@ -15353,7 +15385,7 @@
         <v>169021521300</v>
       </c>
       <c r="F685">
-        <f>ROUND(E685/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>2.8</v>
       </c>
     </row>
@@ -15374,7 +15406,7 @@
         <v>354276481000</v>
       </c>
       <c r="F686">
-        <f>ROUND(E686/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>5.9</v>
       </c>
     </row>
@@ -15395,7 +15427,7 @@
         <v>35837813600</v>
       </c>
       <c r="F687">
-        <f>ROUND(E687/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>0.6</v>
       </c>
     </row>
@@ -15416,7 +15448,7 @@
         <v>119550504700</v>
       </c>
       <c r="F688">
-        <f>ROUND(E688/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
     </row>
@@ -15437,7 +15469,7 @@
         <v>312968492799</v>
       </c>
       <c r="F689">
-        <f>ROUND(E689/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>5.2</v>
       </c>
     </row>
@@ -15458,7 +15490,7 @@
         <v>33036852400</v>
       </c>
       <c r="F690">
-        <f>ROUND(E690/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>0.6</v>
       </c>
     </row>
@@ -15479,7 +15511,7 @@
         <v>123173533700</v>
       </c>
       <c r="F691">
-        <f>ROUND(E691/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>2.1</v>
       </c>
     </row>
@@ -15500,7 +15532,7 @@
         <v>342448981200</v>
       </c>
       <c r="F692">
-        <f>ROUND(E692/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>5.7</v>
       </c>
     </row>
@@ -15521,7 +15553,7 @@
         <v>41668682100</v>
       </c>
       <c r="F693">
-        <f>ROUND(E693/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>0.7</v>
       </c>
     </row>
@@ -15542,7 +15574,7 @@
         <v>149014213300</v>
       </c>
       <c r="F694">
-        <f>ROUND(E694/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>2.5</v>
       </c>
     </row>
@@ -15563,7 +15595,7 @@
         <v>402928258500</v>
       </c>
       <c r="F695">
-        <f>ROUND(E695/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>6.7</v>
       </c>
     </row>
@@ -15584,7 +15616,7 @@
         <v>47571445300</v>
       </c>
       <c r="F696">
-        <f>ROUND(E696/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>0.8</v>
       </c>
     </row>
@@ -15605,7 +15637,7 @@
         <v>146578794000</v>
       </c>
       <c r="F697">
-        <f>ROUND(E697/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>2.4</v>
       </c>
     </row>
@@ -15626,7 +15658,7 @@
         <v>383282214300</v>
       </c>
       <c r="F698">
-        <f>ROUND(E698/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>6.4</v>
       </c>
     </row>
@@ -15647,7 +15679,7 @@
         <v>34973144600</v>
       </c>
       <c r="F699">
-        <f>ROUND(E699/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>0.6</v>
       </c>
     </row>
@@ -15668,7 +15700,7 @@
         <v>162909923600</v>
       </c>
       <c r="F700">
-        <f>ROUND(E700/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>2.7</v>
       </c>
     </row>
@@ -15689,7 +15721,7 @@
         <v>493944206500</v>
       </c>
       <c r="F701">
-        <f>ROUND(E701/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>8.1999999999999993</v>
       </c>
     </row>
@@ -15710,7 +15742,7 @@
         <v>36369622900</v>
       </c>
       <c r="F702">
-        <f>ROUND(E702/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>0.6</v>
       </c>
     </row>
@@ -15731,7 +15763,7 @@
         <v>154735598400</v>
       </c>
       <c r="F703">
-        <f>ROUND(E703/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>2.6</v>
       </c>
     </row>
@@ -15752,7 +15784,7 @@
         <v>436636536600</v>
       </c>
       <c r="F704">
-        <f>ROUND(E704/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>7.3</v>
       </c>
     </row>
@@ -15773,7 +15805,7 @@
         <v>39751949300</v>
       </c>
       <c r="F705">
-        <f>ROUND(E705/60000000000, 1)</f>
+        <f t="shared" si="10"/>
         <v>0.7</v>
       </c>
     </row>
@@ -15794,7 +15826,7 @@
         <v>171135523300</v>
       </c>
       <c r="F706">
-        <f>ROUND(E706/60000000000, 1)</f>
+        <f t="shared" ref="F706:F769" si="11">ROUND(E706/60000000000, 1)</f>
         <v>2.9</v>
       </c>
     </row>
@@ -15815,7 +15847,7 @@
         <v>426454545100</v>
       </c>
       <c r="F707">
-        <f>ROUND(E707/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>7.1</v>
       </c>
     </row>
@@ -15836,7 +15868,7 @@
         <v>32825241500</v>
       </c>
       <c r="F708">
-        <f>ROUND(E708/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
     </row>
@@ -15857,7 +15889,7 @@
         <v>167363768000</v>
       </c>
       <c r="F709">
-        <f>ROUND(E709/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>2.8</v>
       </c>
     </row>
@@ -15878,7 +15910,7 @@
         <v>427996802300</v>
       </c>
       <c r="F710">
-        <f>ROUND(E710/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>7.1</v>
       </c>
     </row>
@@ -15899,7 +15931,7 @@
         <v>39013680400</v>
       </c>
       <c r="F711">
-        <f>ROUND(E711/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>0.7</v>
       </c>
     </row>
@@ -15920,7 +15952,7 @@
         <v>68701797800</v>
       </c>
       <c r="F712">
-        <f>ROUND(E712/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>1.1000000000000001</v>
       </c>
     </row>
@@ -15941,7 +15973,7 @@
         <v>882850436000</v>
       </c>
       <c r="F713">
-        <f>ROUND(E713/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>14.7</v>
       </c>
     </row>
@@ -15962,7 +15994,7 @@
         <v>446909573600</v>
       </c>
       <c r="F714">
-        <f>ROUND(E714/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>7.4</v>
       </c>
     </row>
@@ -15983,7 +16015,7 @@
         <v>96004722900</v>
       </c>
       <c r="F715">
-        <f>ROUND(E715/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>1.6</v>
       </c>
     </row>
@@ -16004,7 +16036,7 @@
         <v>1018275979800</v>
       </c>
       <c r="F716">
-        <f>ROUND(E716/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>17</v>
       </c>
     </row>
@@ -16025,7 +16057,7 @@
         <v>494801897200</v>
       </c>
       <c r="F717">
-        <f>ROUND(E717/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>8.1999999999999993</v>
       </c>
     </row>
@@ -16046,7 +16078,7 @@
         <v>119362994200</v>
       </c>
       <c r="F718">
-        <f>ROUND(E718/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
@@ -16067,7 +16099,7 @@
         <v>1283661955900</v>
       </c>
       <c r="F719">
-        <f>ROUND(E719/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>21.4</v>
       </c>
     </row>
@@ -16088,7 +16120,7 @@
         <v>2051473481200</v>
       </c>
       <c r="F720">
-        <f>ROUND(E720/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>34.200000000000003</v>
       </c>
     </row>
@@ -16109,7 +16141,7 @@
         <v>80918131500</v>
       </c>
       <c r="F721">
-        <f>ROUND(E721/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>1.3</v>
       </c>
     </row>
@@ -16130,7 +16162,7 @@
         <v>815262363500</v>
       </c>
       <c r="F722">
-        <f>ROUND(E722/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>13.6</v>
       </c>
     </row>
@@ -16151,7 +16183,7 @@
         <v>269363038300</v>
       </c>
       <c r="F723">
-        <f>ROUND(E723/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>4.5</v>
       </c>
     </row>
@@ -16172,7 +16204,7 @@
         <v>127996870600</v>
       </c>
       <c r="F724">
-        <f>ROUND(E724/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>2.1</v>
       </c>
     </row>
@@ -16193,7 +16225,7 @@
         <v>5452443400</v>
       </c>
       <c r="F725">
-        <f>ROUND(E725/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>0.1</v>
       </c>
     </row>
@@ -16214,7 +16246,7 @@
         <v>1503362599</v>
       </c>
       <c r="F726">
-        <f>ROUND(E726/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -16235,7 +16267,7 @@
         <v>1502045500</v>
       </c>
       <c r="F727">
-        <f>ROUND(E727/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -16256,7 +16288,7 @@
         <v>1605545300</v>
       </c>
       <c r="F728">
-        <f>ROUND(E728/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -16277,7 +16309,7 @@
         <v>1320852700</v>
       </c>
       <c r="F729">
-        <f>ROUND(E729/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -16298,7 +16330,7 @@
         <v>1140253200</v>
       </c>
       <c r="F730">
-        <f>ROUND(E730/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -16319,7 +16351,7 @@
         <v>3228647500</v>
       </c>
       <c r="F731">
-        <f>ROUND(E731/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>0.1</v>
       </c>
     </row>
@@ -16340,7 +16372,7 @@
         <v>113798900</v>
       </c>
       <c r="F732">
-        <f>ROUND(E732/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -16361,7 +16393,7 @@
         <v>225703600</v>
       </c>
       <c r="F733">
-        <f>ROUND(E733/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -16382,7 +16414,7 @@
         <v>185095100</v>
       </c>
       <c r="F734">
-        <f>ROUND(E734/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -16403,7 +16435,7 @@
         <v>266044700</v>
       </c>
       <c r="F735">
-        <f>ROUND(E735/60000000000, 1)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -16416,8 +16448,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:L25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A2:L51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.33203125" customWidth="1"/>
@@ -16436,7 +16468,7 @@
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -16476,50 +16508,50 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="3">
-        <f>COUNTIFS(Table1[Player-1],C$3,Table1[Player-2],$B4)</f>
+        <f>COUNTIFS(Table1[Player-1],$B4,Table1[Player-2],C$3)</f>
         <v>0</v>
       </c>
       <c r="D4" s="3">
-        <f>COUNTIFS(Table1[Player-1],D$3,Table1[Player-2],$B4)</f>
+        <f>COUNTIFS(Table1[Player-1],$B4,Table1[Player-2],D$3)</f>
         <v>0</v>
       </c>
       <c r="E4" s="3">
-        <f>COUNTIFS(Table1[Player-1],E$3,Table1[Player-2],$B4)</f>
+        <f>COUNTIFS(Table1[Player-1],$B4,Table1[Player-2],E$3)</f>
         <v>1</v>
       </c>
       <c r="F4" s="3">
-        <f>COUNTIFS(Table1[Player-1],F$3,Table1[Player-2],$B4)</f>
+        <f>COUNTIFS(Table1[Player-1],$B4,Table1[Player-2],F$3)</f>
         <v>0</v>
       </c>
       <c r="G4" s="3">
-        <f>COUNTIFS(Table1[Player-1],G$3,Table1[Player-2],$B4)</f>
-        <v>0</v>
+        <f>COUNTIFS(Table1[Player-1],$B4,Table1[Player-2],G$3)</f>
+        <v>1</v>
       </c>
       <c r="H4" s="3">
-        <f>COUNTIFS(Table1[Player-1],H$3,Table1[Player-2],$B4)</f>
+        <f>COUNTIFS(Table1[Player-1],$B4,Table1[Player-2],H$3)</f>
         <v>0</v>
       </c>
       <c r="I4" s="3">
-        <f>COUNTIFS(Table1[Player-1],I$3,Table1[Player-2],$B4)</f>
+        <f>COUNTIFS(Table1[Player-1],$B4,Table1[Player-2],I$3)</f>
         <v>1</v>
       </c>
       <c r="J4" s="3">
-        <f>COUNTIFS(Table1[Player-1],J$3,Table1[Player-2],$B4)</f>
+        <f>COUNTIFS(Table1[Player-1],$B4,Table1[Player-2],J$3)</f>
         <v>0</v>
       </c>
       <c r="K4" s="3">
-        <f>COUNTIFS(Table1[Player-1],K$3,Table1[Player-2],$B4)</f>
-        <v>0</v>
+        <f>COUNTIFS(Table1[Player-1],$B4,Table1[Player-2],K$3)</f>
+        <v>1</v>
       </c>
       <c r="L4" s="3">
-        <f>COUNTIFS(Table1[Player-1],L$3,Table1[Player-2],$B4)</f>
-        <v>0</v>
+        <f>COUNTIFS(Table1[Player-1],$B4,Table1[Player-2],L$3)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -16527,44 +16559,44 @@
         <v>9</v>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIFS(Table1[Player-1],C$3,Table1[Player-2],$B5)</f>
+        <f>COUNTIFS(Table1[Player-1],$B5,Table1[Player-2],C$3)</f>
         <v>0</v>
       </c>
       <c r="D5" s="3">
-        <f>COUNTIFS(Table1[Player-1],D$3,Table1[Player-2],$B5)</f>
+        <f>COUNTIFS(Table1[Player-1],$B5,Table1[Player-2],D$3)</f>
         <v>0</v>
       </c>
       <c r="E5" s="3">
-        <f>COUNTIFS(Table1[Player-1],E$3,Table1[Player-2],$B5)</f>
-        <v>4</v>
+        <f>COUNTIFS(Table1[Player-1],$B5,Table1[Player-2],E$3)</f>
+        <v>2</v>
       </c>
       <c r="F5" s="3">
-        <f>COUNTIFS(Table1[Player-1],F$3,Table1[Player-2],$B5)</f>
+        <f>COUNTIFS(Table1[Player-1],$B5,Table1[Player-2],F$3)</f>
         <v>0</v>
       </c>
       <c r="G5" s="3">
-        <f>COUNTIFS(Table1[Player-1],G$3,Table1[Player-2],$B5)</f>
-        <v>0</v>
+        <f>COUNTIFS(Table1[Player-1],$B5,Table1[Player-2],G$3)</f>
+        <v>1</v>
       </c>
       <c r="H5" s="3">
-        <f>COUNTIFS(Table1[Player-1],H$3,Table1[Player-2],$B5)</f>
+        <f>COUNTIFS(Table1[Player-1],$B5,Table1[Player-2],H$3)</f>
         <v>0</v>
       </c>
       <c r="I5" s="3">
-        <f>COUNTIFS(Table1[Player-1],I$3,Table1[Player-2],$B5)</f>
-        <v>0</v>
+        <f>COUNTIFS(Table1[Player-1],$B5,Table1[Player-2],I$3)</f>
+        <v>3</v>
       </c>
       <c r="J5" s="3">
-        <f>COUNTIFS(Table1[Player-1],J$3,Table1[Player-2],$B5)</f>
-        <v>0</v>
+        <f>COUNTIFS(Table1[Player-1],$B5,Table1[Player-2],J$3)</f>
+        <v>1</v>
       </c>
       <c r="K5" s="3">
-        <f>COUNTIFS(Table1[Player-1],K$3,Table1[Player-2],$B5)</f>
+        <f>COUNTIFS(Table1[Player-1],$B5,Table1[Player-2],K$3)</f>
         <v>0</v>
       </c>
       <c r="L5" s="3">
-        <f>COUNTIFS(Table1[Player-1],L$3,Table1[Player-2],$B5)</f>
-        <v>0</v>
+        <f>COUNTIFS(Table1[Player-1],$B5,Table1[Player-2],L$3)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -16572,44 +16604,44 @@
         <v>7</v>
       </c>
       <c r="C6" s="3">
-        <f>COUNTIFS(Table1[Player-1],C$3,Table1[Player-2],$B6)</f>
+        <f>COUNTIFS(Table1[Player-1],$B6,Table1[Player-2],C$3)</f>
         <v>1</v>
       </c>
       <c r="D6" s="3">
-        <f>COUNTIFS(Table1[Player-1],D$3,Table1[Player-2],$B6)</f>
-        <v>2</v>
+        <f>COUNTIFS(Table1[Player-1],$B6,Table1[Player-2],D$3)</f>
+        <v>4</v>
       </c>
       <c r="E6" s="3">
-        <f>COUNTIFS(Table1[Player-1],E$3,Table1[Player-2],$B6)</f>
+        <f>COUNTIFS(Table1[Player-1],$B6,Table1[Player-2],E$3)</f>
         <v>0</v>
       </c>
       <c r="F6" s="3">
-        <f>COUNTIFS(Table1[Player-1],F$3,Table1[Player-2],$B6)</f>
-        <v>4</v>
+        <f>COUNTIFS(Table1[Player-1],$B6,Table1[Player-2],F$3)</f>
+        <v>23</v>
       </c>
       <c r="G6" s="3">
-        <f>COUNTIFS(Table1[Player-1],G$3,Table1[Player-2],$B6)</f>
-        <v>1</v>
+        <f>COUNTIFS(Table1[Player-1],$B6,Table1[Player-2],G$3)</f>
+        <v>3</v>
       </c>
       <c r="H6" s="3">
-        <f>COUNTIFS(Table1[Player-1],H$3,Table1[Player-2],$B6)</f>
-        <v>1</v>
+        <f>COUNTIFS(Table1[Player-1],$B6,Table1[Player-2],H$3)</f>
+        <v>4</v>
       </c>
       <c r="I6" s="3">
-        <f>COUNTIFS(Table1[Player-1],I$3,Table1[Player-2],$B6)</f>
-        <v>30</v>
+        <f>COUNTIFS(Table1[Player-1],$B6,Table1[Player-2],I$3)</f>
+        <v>48</v>
       </c>
       <c r="J6" s="3">
-        <f>COUNTIFS(Table1[Player-1],J$3,Table1[Player-2],$B6)</f>
-        <v>4</v>
+        <f>COUNTIFS(Table1[Player-1],$B6,Table1[Player-2],J$3)</f>
+        <v>19</v>
       </c>
       <c r="K6" s="3">
-        <f>COUNTIFS(Table1[Player-1],K$3,Table1[Player-2],$B6)</f>
-        <v>4</v>
+        <f>COUNTIFS(Table1[Player-1],$B6,Table1[Player-2],K$3)</f>
+        <v>21</v>
       </c>
       <c r="L6" s="3">
-        <f>COUNTIFS(Table1[Player-1],L$3,Table1[Player-2],$B6)</f>
-        <v>7</v>
+        <f>COUNTIFS(Table1[Player-1],$B6,Table1[Player-2],L$3)</f>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -16617,44 +16649,44 @@
         <v>6</v>
       </c>
       <c r="C7" s="3">
-        <f>COUNTIFS(Table1[Player-1],C$3,Table1[Player-2],$B7)</f>
+        <f>COUNTIFS(Table1[Player-1],$B7,Table1[Player-2],C$3)</f>
         <v>0</v>
       </c>
       <c r="D7" s="3">
-        <f>COUNTIFS(Table1[Player-1],D$3,Table1[Player-2],$B7)</f>
+        <f>COUNTIFS(Table1[Player-1],$B7,Table1[Player-2],D$3)</f>
         <v>0</v>
       </c>
       <c r="E7" s="3">
-        <f>COUNTIFS(Table1[Player-1],E$3,Table1[Player-2],$B7)</f>
-        <v>23</v>
+        <f>COUNTIFS(Table1[Player-1],$B7,Table1[Player-2],E$3)</f>
+        <v>4</v>
       </c>
       <c r="F7" s="3">
-        <f>COUNTIFS(Table1[Player-1],F$3,Table1[Player-2],$B7)</f>
+        <f>COUNTIFS(Table1[Player-1],$B7,Table1[Player-2],F$3)</f>
         <v>0</v>
       </c>
       <c r="G7" s="3">
-        <f>COUNTIFS(Table1[Player-1],G$3,Table1[Player-2],$B7)</f>
-        <v>1</v>
+        <f>COUNTIFS(Table1[Player-1],$B7,Table1[Player-2],G$3)</f>
+        <v>0</v>
       </c>
       <c r="H7" s="3">
-        <f>COUNTIFS(Table1[Player-1],H$3,Table1[Player-2],$B7)</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="4">
-        <f>COUNTIFS(Table1[Player-1],I$3,Table1[Player-2],$B7)</f>
-        <v>68</v>
+        <f>COUNTIFS(Table1[Player-1],$B7,Table1[Player-2],H$3)</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B7,Table1[Player-2],I$3)</f>
+        <v>63</v>
       </c>
       <c r="J7" s="3">
-        <f>COUNTIFS(Table1[Player-1],J$3,Table1[Player-2],$B7)</f>
+        <f>COUNTIFS(Table1[Player-1],$B7,Table1[Player-2],J$3)</f>
         <v>6</v>
       </c>
       <c r="K7" s="3">
-        <f>COUNTIFS(Table1[Player-1],K$3,Table1[Player-2],$B7)</f>
-        <v>4</v>
+        <f>COUNTIFS(Table1[Player-1],$B7,Table1[Player-2],K$3)</f>
+        <v>3</v>
       </c>
       <c r="L7" s="3">
-        <f>COUNTIFS(Table1[Player-1],L$3,Table1[Player-2],$B7)</f>
-        <v>10</v>
+        <f>COUNTIFS(Table1[Player-1],$B7,Table1[Player-2],L$3)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -16662,44 +16694,44 @@
         <v>11</v>
       </c>
       <c r="C8" s="3">
-        <f>COUNTIFS(Table1[Player-1],C$3,Table1[Player-2],$B8)</f>
-        <v>1</v>
+        <f>COUNTIFS(Table1[Player-1],$B8,Table1[Player-2],C$3)</f>
+        <v>0</v>
       </c>
       <c r="D8" s="3">
-        <f>COUNTIFS(Table1[Player-1],D$3,Table1[Player-2],$B8)</f>
-        <v>1</v>
+        <f>COUNTIFS(Table1[Player-1],$B8,Table1[Player-2],D$3)</f>
+        <v>0</v>
       </c>
       <c r="E8" s="3">
-        <f>COUNTIFS(Table1[Player-1],E$3,Table1[Player-2],$B8)</f>
-        <v>3</v>
+        <f>COUNTIFS(Table1[Player-1],$B8,Table1[Player-2],E$3)</f>
+        <v>1</v>
       </c>
       <c r="F8" s="3">
-        <f>COUNTIFS(Table1[Player-1],F$3,Table1[Player-2],$B8)</f>
-        <v>0</v>
+        <f>COUNTIFS(Table1[Player-1],$B8,Table1[Player-2],F$3)</f>
+        <v>1</v>
       </c>
       <c r="G8" s="3">
-        <f>COUNTIFS(Table1[Player-1],G$3,Table1[Player-2],$B8)</f>
+        <f>COUNTIFS(Table1[Player-1],$B8,Table1[Player-2],G$3)</f>
         <v>0</v>
       </c>
       <c r="H8" s="3">
-        <f>COUNTIFS(Table1[Player-1],H$3,Table1[Player-2],$B8)</f>
+        <f>COUNTIFS(Table1[Player-1],$B8,Table1[Player-2],H$3)</f>
         <v>0</v>
       </c>
       <c r="I8" s="3">
-        <f>COUNTIFS(Table1[Player-1],I$3,Table1[Player-2],$B8)</f>
-        <v>2</v>
+        <f>COUNTIFS(Table1[Player-1],$B8,Table1[Player-2],I$3)</f>
+        <v>1</v>
       </c>
       <c r="J8" s="3">
-        <f>COUNTIFS(Table1[Player-1],J$3,Table1[Player-2],$B8)</f>
-        <v>0</v>
+        <f>COUNTIFS(Table1[Player-1],$B8,Table1[Player-2],J$3)</f>
+        <v>1</v>
       </c>
       <c r="K8" s="3">
-        <f>COUNTIFS(Table1[Player-1],K$3,Table1[Player-2],$B8)</f>
+        <f>COUNTIFS(Table1[Player-1],$B8,Table1[Player-2],K$3)</f>
         <v>1</v>
       </c>
       <c r="L8" s="3">
-        <f>COUNTIFS(Table1[Player-1],L$3,Table1[Player-2],$B8)</f>
-        <v>0</v>
+        <f>COUNTIFS(Table1[Player-1],$B8,Table1[Player-2],L$3)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -16707,43 +16739,43 @@
         <v>10</v>
       </c>
       <c r="C9" s="3">
-        <f>COUNTIFS(Table1[Player-1],C$3,Table1[Player-2],$B9)</f>
+        <f>COUNTIFS(Table1[Player-1],$B9,Table1[Player-2],C$3)</f>
         <v>0</v>
       </c>
       <c r="D9" s="3">
-        <f>COUNTIFS(Table1[Player-1],D$3,Table1[Player-2],$B9)</f>
+        <f>COUNTIFS(Table1[Player-1],$B9,Table1[Player-2],D$3)</f>
         <v>0</v>
       </c>
       <c r="E9" s="3">
-        <f>COUNTIFS(Table1[Player-1],E$3,Table1[Player-2],$B9)</f>
-        <v>4</v>
+        <f>COUNTIFS(Table1[Player-1],$B9,Table1[Player-2],E$3)</f>
+        <v>1</v>
       </c>
       <c r="F9" s="3">
-        <f>COUNTIFS(Table1[Player-1],F$3,Table1[Player-2],$B9)</f>
+        <f>COUNTIFS(Table1[Player-1],$B9,Table1[Player-2],F$3)</f>
         <v>0</v>
       </c>
       <c r="G9" s="3">
-        <f>COUNTIFS(Table1[Player-1],G$3,Table1[Player-2],$B9)</f>
+        <f>COUNTIFS(Table1[Player-1],$B9,Table1[Player-2],G$3)</f>
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <f>COUNTIFS(Table1[Player-1],H$3,Table1[Player-2],$B9)</f>
+        <f>COUNTIFS(Table1[Player-1],$B9,Table1[Player-2],H$3)</f>
         <v>0</v>
       </c>
       <c r="I9" s="3">
-        <f>COUNTIFS(Table1[Player-1],I$3,Table1[Player-2],$B9)</f>
-        <v>0</v>
+        <f>COUNTIFS(Table1[Player-1],$B9,Table1[Player-2],I$3)</f>
+        <v>1</v>
       </c>
       <c r="J9" s="3">
-        <f>COUNTIFS(Table1[Player-1],J$3,Table1[Player-2],$B9)</f>
+        <f>COUNTIFS(Table1[Player-1],$B9,Table1[Player-2],J$3)</f>
         <v>0</v>
       </c>
       <c r="K9" s="3">
-        <f>COUNTIFS(Table1[Player-1],K$3,Table1[Player-2],$B9)</f>
+        <f>COUNTIFS(Table1[Player-1],$B9,Table1[Player-2],K$3)</f>
         <v>0</v>
       </c>
       <c r="L9" s="3">
-        <f>COUNTIFS(Table1[Player-1],L$3,Table1[Player-2],$B9)</f>
+        <f>COUNTIFS(Table1[Player-1],$B9,Table1[Player-2],L$3)</f>
         <v>0</v>
       </c>
     </row>
@@ -16752,44 +16784,44 @@
         <v>8</v>
       </c>
       <c r="C10" s="3">
-        <f>COUNTIFS(Table1[Player-1],C$3,Table1[Player-2],$B10)</f>
+        <f>COUNTIFS(Table1[Player-1],$B10,Table1[Player-2],C$3)</f>
         <v>1</v>
       </c>
       <c r="D10" s="3">
-        <f>COUNTIFS(Table1[Player-1],D$3,Table1[Player-2],$B10)</f>
-        <v>3</v>
+        <f>COUNTIFS(Table1[Player-1],$B10,Table1[Player-2],D$3)</f>
+        <v>0</v>
       </c>
       <c r="E10" s="3">
-        <f>COUNTIFS(Table1[Player-1],E$3,Table1[Player-2],$B10)</f>
-        <v>48</v>
-      </c>
-      <c r="F10" s="4">
-        <f>COUNTIFS(Table1[Player-1],F$3,Table1[Player-2],$B10)</f>
+        <f>COUNTIFS(Table1[Player-1],$B10,Table1[Player-2],E$3)</f>
+        <v>30</v>
+      </c>
+      <c r="F10" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B10,Table1[Player-2],F$3)</f>
+        <v>68</v>
+      </c>
+      <c r="G10" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B10,Table1[Player-2],G$3)</f>
+        <v>2</v>
+      </c>
+      <c r="H10" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B10,Table1[Player-2],H$3)</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B10,Table1[Player-2],I$3)</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B10,Table1[Player-2],J$3)</f>
         <v>63</v>
       </c>
-      <c r="G10" s="3">
-        <f>COUNTIFS(Table1[Player-1],G$3,Table1[Player-2],$B10)</f>
-        <v>1</v>
-      </c>
-      <c r="H10" s="3">
-        <f>COUNTIFS(Table1[Player-1],H$3,Table1[Player-2],$B10)</f>
-        <v>1</v>
-      </c>
-      <c r="I10" s="3">
-        <f>COUNTIFS(Table1[Player-1],I$3,Table1[Player-2],$B10)</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="3">
-        <f>COUNTIFS(Table1[Player-1],J$3,Table1[Player-2],$B10)</f>
-        <v>63</v>
-      </c>
       <c r="K10" s="3">
-        <f>COUNTIFS(Table1[Player-1],K$3,Table1[Player-2],$B10)</f>
-        <v>29</v>
+        <f>COUNTIFS(Table1[Player-1],$B10,Table1[Player-2],K$3)</f>
+        <v>30</v>
       </c>
       <c r="L10" s="3">
-        <f>COUNTIFS(Table1[Player-1],L$3,Table1[Player-2],$B10)</f>
-        <v>66</v>
+        <f>COUNTIFS(Table1[Player-1],$B10,Table1[Player-2],L$3)</f>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
@@ -16797,44 +16829,44 @@
         <v>4</v>
       </c>
       <c r="C11" s="3">
-        <f>COUNTIFS(Table1[Player-1],C$3,Table1[Player-2],$B11)</f>
+        <f>COUNTIFS(Table1[Player-1],$B11,Table1[Player-2],C$3)</f>
         <v>0</v>
       </c>
       <c r="D11" s="3">
-        <f>COUNTIFS(Table1[Player-1],D$3,Table1[Player-2],$B11)</f>
-        <v>1</v>
+        <f>COUNTIFS(Table1[Player-1],$B11,Table1[Player-2],D$3)</f>
+        <v>0</v>
       </c>
       <c r="E11" s="3">
-        <f>COUNTIFS(Table1[Player-1],E$3,Table1[Player-2],$B11)</f>
-        <v>19</v>
+        <f>COUNTIFS(Table1[Player-1],$B11,Table1[Player-2],E$3)</f>
+        <v>4</v>
       </c>
       <c r="F11" s="3">
-        <f>COUNTIFS(Table1[Player-1],F$3,Table1[Player-2],$B11)</f>
+        <f>COUNTIFS(Table1[Player-1],$B11,Table1[Player-2],F$3)</f>
         <v>6</v>
       </c>
       <c r="G11" s="3">
-        <f>COUNTIFS(Table1[Player-1],G$3,Table1[Player-2],$B11)</f>
-        <v>1</v>
+        <f>COUNTIFS(Table1[Player-1],$B11,Table1[Player-2],G$3)</f>
+        <v>0</v>
       </c>
       <c r="H11" s="3">
-        <f>COUNTIFS(Table1[Player-1],H$3,Table1[Player-2],$B11)</f>
+        <f>COUNTIFS(Table1[Player-1],$B11,Table1[Player-2],H$3)</f>
         <v>0</v>
       </c>
       <c r="I11" s="3">
-        <f>COUNTIFS(Table1[Player-1],I$3,Table1[Player-2],$B11)</f>
+        <f>COUNTIFS(Table1[Player-1],$B11,Table1[Player-2],I$3)</f>
         <v>63</v>
       </c>
       <c r="J11" s="3">
-        <f>COUNTIFS(Table1[Player-1],J$3,Table1[Player-2],$B11)</f>
+        <f>COUNTIFS(Table1[Player-1],$B11,Table1[Player-2],J$3)</f>
         <v>0</v>
       </c>
       <c r="K11" s="3">
-        <f>COUNTIFS(Table1[Player-1],K$3,Table1[Player-2],$B11)</f>
-        <v>4</v>
+        <f>COUNTIFS(Table1[Player-1],$B11,Table1[Player-2],K$3)</f>
+        <v>3</v>
       </c>
       <c r="L11" s="3">
-        <f>COUNTIFS(Table1[Player-1],L$3,Table1[Player-2],$B11)</f>
-        <v>7</v>
+        <f>COUNTIFS(Table1[Player-1],$B11,Table1[Player-2],L$3)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
@@ -16842,43 +16874,43 @@
         <v>5</v>
       </c>
       <c r="C12" s="3">
-        <f>COUNTIFS(Table1[Player-1],C$3,Table1[Player-2],$B12)</f>
-        <v>1</v>
+        <f>COUNTIFS(Table1[Player-1],$B12,Table1[Player-2],C$3)</f>
+        <v>0</v>
       </c>
       <c r="D12" s="3">
-        <f>COUNTIFS(Table1[Player-1],D$3,Table1[Player-2],$B12)</f>
+        <f>COUNTIFS(Table1[Player-1],$B12,Table1[Player-2],D$3)</f>
         <v>0</v>
       </c>
       <c r="E12" s="3">
-        <f>COUNTIFS(Table1[Player-1],E$3,Table1[Player-2],$B12)</f>
-        <v>21</v>
+        <f>COUNTIFS(Table1[Player-1],$B12,Table1[Player-2],E$3)</f>
+        <v>4</v>
       </c>
       <c r="F12" s="3">
-        <f>COUNTIFS(Table1[Player-1],F$3,Table1[Player-2],$B12)</f>
-        <v>3</v>
+        <f>COUNTIFS(Table1[Player-1],$B12,Table1[Player-2],F$3)</f>
+        <v>4</v>
       </c>
       <c r="G12" s="3">
-        <f>COUNTIFS(Table1[Player-1],G$3,Table1[Player-2],$B12)</f>
+        <f>COUNTIFS(Table1[Player-1],$B12,Table1[Player-2],G$3)</f>
         <v>1</v>
       </c>
       <c r="H12" s="3">
-        <f>COUNTIFS(Table1[Player-1],H$3,Table1[Player-2],$B12)</f>
+        <f>COUNTIFS(Table1[Player-1],$B12,Table1[Player-2],H$3)</f>
         <v>0</v>
       </c>
       <c r="I12" s="3">
-        <f>COUNTIFS(Table1[Player-1],I$3,Table1[Player-2],$B12)</f>
-        <v>30</v>
+        <f>COUNTIFS(Table1[Player-1],$B12,Table1[Player-2],I$3)</f>
+        <v>29</v>
       </c>
       <c r="J12" s="3">
-        <f>COUNTIFS(Table1[Player-1],J$3,Table1[Player-2],$B12)</f>
-        <v>3</v>
+        <f>COUNTIFS(Table1[Player-1],$B12,Table1[Player-2],J$3)</f>
+        <v>4</v>
       </c>
       <c r="K12" s="3">
-        <f>COUNTIFS(Table1[Player-1],K$3,Table1[Player-2],$B12)</f>
+        <f>COUNTIFS(Table1[Player-1],$B12,Table1[Player-2],K$3)</f>
         <v>0</v>
       </c>
       <c r="L12" s="3">
-        <f>COUNTIFS(Table1[Player-1],L$3,Table1[Player-2],$B12)</f>
+        <f>COUNTIFS(Table1[Player-1],$B12,Table1[Player-2],L$3)</f>
         <v>4</v>
       </c>
     </row>
@@ -16887,528 +16919,1334 @@
         <v>13</v>
       </c>
       <c r="C13" s="3">
-        <f>COUNTIFS(Table1[Player-1],C$3,Table1[Player-2],$B13)</f>
-        <v>1</v>
+        <f>COUNTIFS(Table1[Player-1],$B13,Table1[Player-2],C$3)</f>
+        <v>0</v>
       </c>
       <c r="D13" s="3">
-        <f>COUNTIFS(Table1[Player-1],D$3,Table1[Player-2],$B13)</f>
-        <v>1</v>
+        <f>COUNTIFS(Table1[Player-1],$B13,Table1[Player-2],D$3)</f>
+        <v>0</v>
       </c>
       <c r="E13" s="3">
-        <f>COUNTIFS(Table1[Player-1],E$3,Table1[Player-2],$B13)</f>
-        <v>24</v>
+        <f>COUNTIFS(Table1[Player-1],$B13,Table1[Player-2],E$3)</f>
+        <v>7</v>
       </c>
       <c r="F13" s="3">
-        <f>COUNTIFS(Table1[Player-1],F$3,Table1[Player-2],$B13)</f>
+        <f>COUNTIFS(Table1[Player-1],$B13,Table1[Player-2],F$3)</f>
+        <v>10</v>
+      </c>
+      <c r="G13" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B13,Table1[Player-2],G$3)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B13,Table1[Player-2],H$3)</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B13,Table1[Player-2],I$3)</f>
+        <v>66</v>
+      </c>
+      <c r="J13" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B13,Table1[Player-2],J$3)</f>
+        <v>7</v>
+      </c>
+      <c r="K13" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B13,Table1[Player-2],K$3)</f>
+        <v>4</v>
+      </c>
+      <c r="L13" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B13,Table1[Player-2],L$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G13" s="3">
-        <f>COUNTIFS(Table1[Player-1],G$3,Table1[Player-2],$B13)</f>
-        <v>1</v>
-      </c>
-      <c r="H13" s="3">
-        <f>COUNTIFS(Table1[Player-1],H$3,Table1[Player-2],$B13)</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="3">
-        <f>COUNTIFS(Table1[Player-1],I$3,Table1[Player-2],$B13)</f>
-        <v>65</v>
-      </c>
-      <c r="J13" s="3">
-        <f>COUNTIFS(Table1[Player-1],J$3,Table1[Player-2],$B13)</f>
-        <v>6</v>
-      </c>
-      <c r="K13" s="3">
-        <f>COUNTIFS(Table1[Player-1],K$3,Table1[Player-2],$B13)</f>
-        <v>4</v>
-      </c>
-      <c r="L13" s="3">
-        <f>COUNTIFS(Table1[Player-1],L$3,Table1[Player-2],$B13)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
+      <c r="E16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],C$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],C$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],D$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],D$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],E$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],E$16,Table1[ [ Winner] ], 1)</f>
+        <v>2</v>
+      </c>
+      <c r="F17" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],F$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],F$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],G$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],G$16,Table1[ [ Winner] ], 1)</f>
+        <v>1</v>
+      </c>
+      <c r="H17" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],H$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],H$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],I$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],I$16,Table1[ [ Winner] ], 1)</f>
+        <v>2</v>
+      </c>
+      <c r="J17" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],J$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],J$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],K$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],K$16,Table1[ [ Winner] ], 1)</f>
+        <v>1</v>
+      </c>
+      <c r="L17" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],L$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],L$16,Table1[ [ Winner] ], 1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],C$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],C$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],D$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],D$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],E$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],E$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],F$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],F$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],G$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],G$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],H$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],H$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],I$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],I$16,Table1[ [ Winner] ], 1)</f>
+        <v>1</v>
+      </c>
+      <c r="J18" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],J$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],J$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],K$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],K$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],L$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],L$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],C$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],C$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],D$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],D$16,Table1[ [ Winner] ], 1)</f>
+        <v>6</v>
+      </c>
+      <c r="E19" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],E$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],E$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],F$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],F$16,Table1[ [ Winner] ], 1)</f>
+        <v>4</v>
+      </c>
+      <c r="G19" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],G$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],G$16,Table1[ [ Winner] ], 1)</f>
+        <v>1</v>
+      </c>
+      <c r="H19" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],H$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],H$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],I$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],I$16,Table1[ [ Winner] ], 1)</f>
+        <v>23</v>
+      </c>
+      <c r="J19" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],J$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],J$16,Table1[ [ Winner] ], 1)</f>
+        <v>8</v>
+      </c>
+      <c r="K19" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],K$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],K$16,Table1[ [ Winner] ], 1)</f>
+        <v>20</v>
+      </c>
+      <c r="L19" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],L$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],L$16,Table1[ [ Winner] ], 1)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],C$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],C$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],D$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],D$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],E$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],E$16,Table1[ [ Winner] ], 1)</f>
+        <v>23</v>
+      </c>
+      <c r="F20" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],F$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],F$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],G$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],G$16,Table1[ [ Winner] ], 1)</f>
+        <v>1</v>
+      </c>
+      <c r="H20" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],H$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],H$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],I$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],I$16,Table1[ [ Winner] ], 1)</f>
+        <v>127</v>
+      </c>
+      <c r="J20" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],J$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],J$16,Table1[ [ Winner] ], 1)</f>
+        <v>6</v>
+      </c>
+      <c r="K20" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],K$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],K$16,Table1[ [ Winner] ], 1)</f>
+        <v>7</v>
+      </c>
+      <c r="L20" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],L$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],L$16,Table1[ [ Winner] ], 1)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],C$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],C$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],D$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],D$16,Table1[ [ Winner] ], 1)</f>
+        <v>1</v>
+      </c>
+      <c r="E21" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],E$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],E$16,Table1[ [ Winner] ], 1)</f>
+        <v>3</v>
+      </c>
+      <c r="F21" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],F$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],F$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],G$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],G$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],H$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],H$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],I$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],I$16,Table1[ [ Winner] ], 1)</f>
+        <v>3</v>
+      </c>
+      <c r="J21" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],J$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],J$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],K$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],K$16,Table1[ [ Winner] ], 1)</f>
+        <v>2</v>
+      </c>
+      <c r="L21" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],L$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],L$16,Table1[ [ Winner] ], 1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],C$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],C$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],D$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],D$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],E$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],E$16,Table1[ [ Winner] ], 1)</f>
+        <v>5</v>
+      </c>
+      <c r="F22" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],F$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],F$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],G$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],G$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],H$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],H$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],I$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],I$16,Table1[ [ Winner] ], 1)</f>
+        <v>1</v>
+      </c>
+      <c r="J22" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],J$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],J$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],K$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],K$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],L$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],L$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],C$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],C$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],D$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],D$16,Table1[ [ Winner] ], 1)</f>
+        <v>2</v>
+      </c>
+      <c r="E23" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],E$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],E$16,Table1[ [ Winner] ], 1)</f>
+        <v>55</v>
+      </c>
+      <c r="F23" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],F$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],F$16,Table1[ [ Winner] ], 1)</f>
+        <v>4</v>
+      </c>
+      <c r="G23" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],G$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],G$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],H$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],H$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],I$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],I$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],J$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],J$16,Table1[ [ Winner] ], 1)</f>
+        <v>1</v>
+      </c>
+      <c r="K23" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],K$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],K$16,Table1[ [ Winner] ], 1)</f>
+        <v>59</v>
+      </c>
+      <c r="L23" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],L$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],L$16,Table1[ [ Winner] ], 1)</f>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],C$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],C$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],D$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],D$16,Table1[ [ Winner] ], 1)</f>
+        <v>1</v>
+      </c>
+      <c r="E24" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],E$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],E$16,Table1[ [ Winner] ], 1)</f>
+        <v>15</v>
+      </c>
+      <c r="F24" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],F$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],F$16,Table1[ [ Winner] ], 1)</f>
+        <v>6</v>
+      </c>
+      <c r="G24" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],G$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],G$16,Table1[ [ Winner] ], 1)</f>
+        <v>1</v>
+      </c>
+      <c r="H24" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],H$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],H$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],I$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],I$16,Table1[ [ Winner] ], 1)</f>
+        <v>125</v>
+      </c>
+      <c r="J24" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],J$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],J$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],K$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],K$16,Table1[ [ Winner] ], 1)</f>
+        <v>6</v>
+      </c>
+      <c r="L24" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],L$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],L$16,Table1[ [ Winner] ], 1)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],C$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],C$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],D$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],D$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],E$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],E$16,Table1[ [ Winner] ], 1)</f>
+        <v>5</v>
+      </c>
+      <c r="F25" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],F$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],F$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],G$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],G$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],H$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],H$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],I$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],I$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],J$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],J$16,Table1[ [ Winner] ], 1)</f>
+        <v>1</v>
+      </c>
+      <c r="K25" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],K$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],K$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],L$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],L$16,Table1[ [ Winner] ], 1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],C$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],C$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],D$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],D$16,Table1[ [ Winner] ], 1)</f>
+        <v>1</v>
+      </c>
+      <c r="E26" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],E$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],E$16,Table1[ [ Winner] ], 1)</f>
         <v>19</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="F26" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],F$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],F$16,Table1[ [ Winner] ], 1)</f>
+        <v>8</v>
+      </c>
+      <c r="G26" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],G$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],G$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],H$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],H$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],I$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],I$16,Table1[ [ Winner] ], 1)</f>
+        <v>53</v>
+      </c>
+      <c r="J26" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],J$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],J$16,Table1[ [ Winner] ], 1)</f>
+        <v>5</v>
+      </c>
+      <c r="K26" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],K$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],K$16,Table1[ [ Winner] ], 1)</f>
+        <v>7</v>
+      </c>
+      <c r="L26" s="3">
+        <f>COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],L$16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],L$16,Table1[ [ Winner] ], 1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C28" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B29" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G15" s="1" t="s">
+      <c r="E29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H29" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K15" s="1" t="s">
+      <c r="I29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L15" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="1" t="s">
+      <c r="L29" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="3">
-        <f>COUNTIFS(Table1[Player-1],C$3,Table1[Player-2],$B16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],C$3,Table1[Player-1],$B16,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="3">
-        <f>COUNTIFS(Table1[Player-1],D$3,Table1[Player-2],$B16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],D$3,Table1[Player-1],$B16,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="3">
-        <f>COUNTIFS(Table1[Player-1],E$3,Table1[Player-2],$B16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],E$3,Table1[Player-1],$B16,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="3">
-        <f>COUNTIFS(Table1[Player-1],F$3,Table1[Player-2],$B16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],F$3,Table1[Player-1],$B16,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="3">
-        <f>COUNTIFS(Table1[Player-1],G$3,Table1[Player-2],$B16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],G$3,Table1[Player-1],$B16,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="3">
-        <f>COUNTIFS(Table1[Player-1],H$3,Table1[Player-2],$B16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],H$3,Table1[Player-1],$B16,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="3">
-        <f>COUNTIFS(Table1[Player-1],I$3,Table1[Player-2],$B16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],I$3,Table1[Player-1],$B16,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="3">
-        <f>COUNTIFS(Table1[Player-1],J$3,Table1[Player-2],$B16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],J$3,Table1[Player-1],$B16,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="3">
-        <f>COUNTIFS(Table1[Player-1],K$3,Table1[Player-2],$B16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],K$3,Table1[Player-1],$B16,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="L16" s="3">
-        <f>COUNTIFS(Table1[Player-1],L$3,Table1[Player-2],$B16,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],L$3,Table1[Player-1],$B16,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B17" s="1" t="s">
+      <c r="C30" s="5" t="str">
+        <f>IF(C42 &gt; 0,C17 / (COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],C$16) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],C$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="D30" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],D$16) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],D$16) &gt; 0,D17 / (COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],D$16) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],D$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="E30" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],E$16) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],E$16) &gt; 0,E17 / (COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],E$16) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],E$16)),"N/A")</f>
+        <v>1</v>
+      </c>
+      <c r="F30" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],F$16) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],F$16) &gt; 0,F17 / (COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],F$16) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],F$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="G30" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],G$16) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],G$16) &gt; 0,G17 / (COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],G$16) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],G$16)),"N/A")</f>
+        <v>1</v>
+      </c>
+      <c r="H30" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],H$16) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],H$16) &gt; 0,H17 / (COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],H$16) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],H$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="I30" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],I$16) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],I$16) &gt; 0,I17 / (COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],I$16) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],I$16)),"N/A")</f>
+        <v>1</v>
+      </c>
+      <c r="J30" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],J$16) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],J$16) &gt; 0,J17 / (COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],J$16) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],J$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="K30" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],K$16) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],K$16) &gt; 0,K17 / (COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],K$16) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],K$16)),"N/A")</f>
+        <v>1</v>
+      </c>
+      <c r="L30" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],L$16) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],L$16) &gt; 0,L17 / (COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],L$16) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],L$16)),"N/A")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B31" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="3">
-        <f>COUNTIFS(Table1[Player-1],C$3,Table1[Player-2],$B17,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],C$3,Table1[Player-1],$B17,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="3">
-        <f>COUNTIFS(Table1[Player-1],D$3,Table1[Player-2],$B17,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],D$3,Table1[Player-1],$B17,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="3">
-        <f>COUNTIFS(Table1[Player-1],E$3,Table1[Player-2],$B17,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],E$3,Table1[Player-1],$B17,Table1[ [ Winner] ], 1)</f>
-        <v>6</v>
-      </c>
-      <c r="F17" s="3">
-        <f>COUNTIFS(Table1[Player-1],F$3,Table1[Player-2],$B17,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],F$3,Table1[Player-1],$B17,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="3">
-        <f>COUNTIFS(Table1[Player-1],G$3,Table1[Player-2],$B17,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],G$3,Table1[Player-1],$B17,Table1[ [ Winner] ], 1)</f>
-        <v>1</v>
-      </c>
-      <c r="H17" s="3">
-        <f>COUNTIFS(Table1[Player-1],H$3,Table1[Player-2],$B17,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],H$3,Table1[Player-1],$B17,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="3">
-        <f>COUNTIFS(Table1[Player-1],I$3,Table1[Player-2],$B17,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],I$3,Table1[Player-1],$B17,Table1[ [ Winner] ], 1)</f>
-        <v>2</v>
-      </c>
-      <c r="J17" s="3">
-        <f>COUNTIFS(Table1[Player-1],J$3,Table1[Player-2],$B17,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],J$3,Table1[Player-1],$B17,Table1[ [ Winner] ], 1)</f>
-        <v>1</v>
-      </c>
-      <c r="K17" s="3">
-        <f>COUNTIFS(Table1[Player-1],K$3,Table1[Player-2],$B17,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],K$3,Table1[Player-1],$B17,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="L17" s="3">
-        <f>COUNTIFS(Table1[Player-1],L$3,Table1[Player-2],$B17,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],L$3,Table1[Player-1],$B17,Table1[ [ Winner] ], 1)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="3">
-        <f>COUNTIFS(Table1[Player-1],C$3,Table1[Player-2],$B18,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],C$3,Table1[Player-1],$B18,Table1[ [ Winner] ], 1)</f>
-        <v>2</v>
-      </c>
-      <c r="D18" s="3">
-        <f>COUNTIFS(Table1[Player-1],D$3,Table1[Player-2],$B18,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],D$3,Table1[Player-1],$B18,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="3">
-        <f>COUNTIFS(Table1[Player-1],E$3,Table1[Player-2],$B18,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],E$3,Table1[Player-1],$B18,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="3">
-        <f>COUNTIFS(Table1[Player-1],F$3,Table1[Player-2],$B18,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],F$3,Table1[Player-1],$B18,Table1[ [ Winner] ], 1)</f>
+      <c r="C31" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],C$16) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],C$16) &gt; 0,C18 / (COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],C$16) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],C$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="D31" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],D$16) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],D$16) &gt; 0,D18 / (COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],D$16) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],D$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="E31" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],E$16) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],E$16) &gt; 0,E18 / (COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],E$16) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],E$16)),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],F$16) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],F$16) &gt; 0,F18 / (COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],F$16) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],F$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="G31" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],G$16) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],G$16) &gt; 0,G18 / (COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],G$16) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],G$16)),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="H31" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],H$16) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],H$16) &gt; 0,H18 / (COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],H$16) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],H$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="I31" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],I$16) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],I$16) &gt; 0,I18 / (COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],I$16) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],I$16)),"N/A")</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J31" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],J$16) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],J$16) &gt; 0,J18 / (COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],J$16) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],J$16)),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],K$16) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],K$16) &gt; 0,K18 / (COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],K$16) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],K$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="L31" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],L$16) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],L$16) &gt; 0,L18 / (COUNTIFS(Table1[Player-1],$B18,Table1[Player-2],L$16) + COUNTIFS(Table1[Player-2],$B18,Table1[Player-1],L$16)),"N/A")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],C$16) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],C$16) &gt; 0,C19 / (COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],C$16) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],C$16)),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="D32" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],D$16) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],D$16) &gt; 0,D19 / (COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],D$16) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],D$16)),"N/A")</f>
+        <v>1</v>
+      </c>
+      <c r="E32" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],E$16) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],E$16) &gt; 0,E19 / (COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],E$16) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],E$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="F32" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],F$16) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],F$16) &gt; 0,F19 / (COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],F$16) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],F$16)),"N/A")</f>
+        <v>0.14814814814814814</v>
+      </c>
+      <c r="G32" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],G$16) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],G$16) &gt; 0,G19 / (COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],G$16) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],G$16)),"N/A")</f>
+        <v>0.25</v>
+      </c>
+      <c r="H32" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],H$16) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],H$16) &gt; 0,H19 / (COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],H$16) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],H$16)),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],I$16) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],I$16) &gt; 0,I19 / (COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],I$16) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],I$16)),"N/A")</f>
+        <v>0.29487179487179488</v>
+      </c>
+      <c r="J32" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],J$16) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],J$16) &gt; 0,J19 / (COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],J$16) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],J$16)),"N/A")</f>
+        <v>0.34782608695652173</v>
+      </c>
+      <c r="K32" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],K$16) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],K$16) &gt; 0,K19 / (COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],K$16) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],K$16)),"N/A")</f>
+        <v>0.8</v>
+      </c>
+      <c r="L32" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],L$16) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],L$16) &gt; 0,L19 / (COUNTIFS(Table1[Player-1],$B19,Table1[Player-2],L$16) + COUNTIFS(Table1[Player-2],$B19,Table1[Player-1],L$16)),"N/A")</f>
+        <v>0.38709677419354838</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],C$16) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],C$16) &gt; 0,C20 / (COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],C$16) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],C$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="D33" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],D$16) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],D$16) &gt; 0,D20 / (COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],D$16) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],D$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="E33" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],E$16) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],E$16) &gt; 0,E20 / (COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],E$16) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],E$16)),"N/A")</f>
+        <v>0.85185185185185186</v>
+      </c>
+      <c r="F33" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],F$16) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],F$16) &gt; 0,F20 / (COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],F$16) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],F$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="G33" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],G$16) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],G$16) &gt; 0,G20 / (COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],G$16) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],G$16)),"N/A")</f>
+        <v>1</v>
+      </c>
+      <c r="H33" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],H$16) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],H$16) &gt; 0,H20 / (COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],H$16) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],H$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="I33" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],I$16) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],I$16) &gt; 0,I20 / (COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],I$16) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],I$16)),"N/A")</f>
+        <v>0.96946564885496178</v>
+      </c>
+      <c r="J33" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],J$16) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],J$16) &gt; 0,J20 / (COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],J$16) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],J$16)),"N/A")</f>
+        <v>0.5</v>
+      </c>
+      <c r="K33" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],K$16) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],K$16) &gt; 0,K20 / (COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],K$16) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],K$16)),"N/A")</f>
+        <v>1</v>
+      </c>
+      <c r="L33" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],L$16) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],L$16) &gt; 0,L20 / (COUNTIFS(Table1[Player-1],$B20,Table1[Player-2],L$16) + COUNTIFS(Table1[Player-2],$B20,Table1[Player-1],L$16)),"N/A")</f>
+        <v>0.57894736842105265</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],C$16) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],C$16) &gt; 0,C21 / (COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],C$16) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],C$16)),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],D$16) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],D$16) &gt; 0,D21 / (COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],D$16) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],D$16)),"N/A")</f>
+        <v>1</v>
+      </c>
+      <c r="E34" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],E$16) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],E$16) &gt; 0,E21 / (COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],E$16) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],E$16)),"N/A")</f>
+        <v>0.75</v>
+      </c>
+      <c r="F34" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],F$16) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],F$16) &gt; 0,F21 / (COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],F$16) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],F$16)),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],G$16) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],G$16) &gt; 0,G21 / (COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],G$16) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],G$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="H34" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],H$16) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],H$16) &gt; 0,H21 / (COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],H$16) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],H$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="I34" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],I$16) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],I$16) &gt; 0,I21 / (COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],I$16) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],I$16)),"N/A")</f>
+        <v>1</v>
+      </c>
+      <c r="J34" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],J$16) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],J$16) &gt; 0,J21 / (COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],J$16) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],J$16)),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],K$16) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],K$16) &gt; 0,K21 / (COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],K$16) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],K$16)),"N/A")</f>
+        <v>1</v>
+      </c>
+      <c r="L34" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],L$16) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],L$16) &gt; 0,L21 / (COUNTIFS(Table1[Player-1],$B21,Table1[Player-2],L$16) + COUNTIFS(Table1[Player-2],$B21,Table1[Player-1],L$16)),"N/A")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],C$16) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],C$16) &gt; 0,C22 / (COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],C$16) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],C$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="D35" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],D$16) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],D$16) &gt; 0,D22 / (COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],D$16) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],D$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="E35" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],E$16) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],E$16) &gt; 0,E22 / (COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],E$16) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],E$16)),"N/A")</f>
+        <v>1</v>
+      </c>
+      <c r="F35" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],F$16) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],F$16) &gt; 0,F22 / (COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],F$16) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],F$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="G35" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],G$16) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],G$16) &gt; 0,G22 / (COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],G$16) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],G$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="H35" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],H$16) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],H$16) &gt; 0,H22 / (COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],H$16) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],H$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="I35" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],I$16) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],I$16) &gt; 0,I22 / (COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],I$16) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],I$16)),"N/A")</f>
+        <v>1</v>
+      </c>
+      <c r="J35" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],J$16) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],J$16) &gt; 0,J22 / (COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],J$16) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],J$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="K35" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],K$16) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],K$16) &gt; 0,K22 / (COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],K$16) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],K$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="L35" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],L$16) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],L$16) &gt; 0,L22 / (COUNTIFS(Table1[Player-1],$B22,Table1[Player-2],L$16) + COUNTIFS(Table1[Player-2],$B22,Table1[Player-1],L$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],C$16) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],C$16) &gt; 0,C23 / (COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],C$16) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],C$16)),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],D$16) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],D$16) &gt; 0,D23 / (COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],D$16) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],D$16)),"N/A")</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E36" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],E$16) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],E$16) &gt; 0,E23 / (COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],E$16) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],E$16)),"N/A")</f>
+        <v>0.70512820512820518</v>
+      </c>
+      <c r="F36" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],F$16) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],F$16) &gt; 0,F23 / (COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],F$16) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],F$16)),"N/A")</f>
+        <v>3.0534351145038167E-2</v>
+      </c>
+      <c r="G36" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],G$16) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],G$16) &gt; 0,G23 / (COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],G$16) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],G$16)),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="H36" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],H$16) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],H$16) &gt; 0,H23 / (COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],H$16) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],H$16)),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="I36" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],I$16) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],I$16) &gt; 0,I23 / (COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],I$16) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],I$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="J36" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],J$16) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],J$16) &gt; 0,J23 / (COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],J$16) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],J$16)),"N/A")</f>
+        <v>7.9365079365079361E-3</v>
+      </c>
+      <c r="K36" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],K$16) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],K$16) &gt; 0,K23 / (COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],K$16) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],K$16)),"N/A")</f>
+        <v>1</v>
+      </c>
+      <c r="L36" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],L$16) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],L$16) &gt; 0,L23 / (COUNTIFS(Table1[Player-1],$B23,Table1[Player-2],L$16) + COUNTIFS(Table1[Player-2],$B23,Table1[Player-1],L$16)),"N/A")</f>
+        <v>0.59541984732824427</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],C$16) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],C$16) &gt; 0,C24 / (COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],C$16) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],C$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="D37" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],D$16) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],D$16) &gt; 0,D24 / (COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],D$16) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],D$16)),"N/A")</f>
+        <v>1</v>
+      </c>
+      <c r="E37" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],E$16) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],E$16) &gt; 0,E24 / (COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],E$16) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],E$16)),"N/A")</f>
+        <v>0.65217391304347827</v>
+      </c>
+      <c r="F37" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],F$16) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],F$16) &gt; 0,F24 / (COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],F$16) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],F$16)),"N/A")</f>
+        <v>0.5</v>
+      </c>
+      <c r="G37" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],G$16) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],G$16) &gt; 0,G24 / (COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],G$16) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],G$16)),"N/A")</f>
+        <v>1</v>
+      </c>
+      <c r="H37" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],H$16) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],H$16) &gt; 0,H24 / (COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],H$16) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],H$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="I37" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],I$16) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],I$16) &gt; 0,I24 / (COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],I$16) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],I$16)),"N/A")</f>
+        <v>0.99206349206349209</v>
+      </c>
+      <c r="J37" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],J$16) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],J$16) &gt; 0,J24 / (COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],J$16) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],J$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="K37" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],K$16) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],K$16) &gt; 0,K24 / (COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],K$16) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],K$16)),"N/A")</f>
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="L37" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],L$16) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],L$16) &gt; 0,L24 / (COUNTIFS(Table1[Player-1],$B24,Table1[Player-2],L$16) + COUNTIFS(Table1[Player-2],$B24,Table1[Player-1],L$16)),"N/A")</f>
+        <v>0.61538461538461542</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],C$16) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],C$16) &gt; 0,C25 / (COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],C$16) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],C$16)),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="D38" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],D$16) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],D$16) &gt; 0,D25 / (COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],D$16) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],D$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="E38" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],E$16) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],E$16) &gt; 0,E25 / (COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],E$16) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],E$16)),"N/A")</f>
+        <v>0.2</v>
+      </c>
+      <c r="F38" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],F$16) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],F$16) &gt; 0,F25 / (COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],F$16) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],F$16)),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="G38" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],G$16) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],G$16) &gt; 0,G25 / (COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],G$16) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],G$16)),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="H38" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],H$16) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],H$16) &gt; 0,H25 / (COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],H$16) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],H$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="I38" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],I$16) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],I$16) &gt; 0,I25 / (COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],I$16) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],I$16)),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],J$16) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],J$16) &gt; 0,J25 / (COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],J$16) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],J$16)),"N/A")</f>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="K38" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],K$16) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],K$16) &gt; 0,K25 / (COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],K$16) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],K$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="L38" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],L$16) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],L$16) &gt; 0,L25 / (COUNTIFS(Table1[Player-1],$B25,Table1[Player-2],L$16) + COUNTIFS(Table1[Player-2],$B25,Table1[Player-1],L$16)),"N/A")</f>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],C$16) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],C$16) &gt; 0,C26 / (COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],C$16) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],C$16)),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="D39" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],D$16) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],D$16) &gt; 0,D26 / (COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],D$16) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],D$16)),"N/A")</f>
+        <v>1</v>
+      </c>
+      <c r="E39" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],E$16) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],E$16) &gt; 0,E26 / (COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],E$16) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],E$16)),"N/A")</f>
+        <v>0.61290322580645162</v>
+      </c>
+      <c r="F39" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],F$16) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],F$16) &gt; 0,F26 / (COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],F$16) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],F$16)),"N/A")</f>
+        <v>0.42105263157894735</v>
+      </c>
+      <c r="G39" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],G$16) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],G$16) &gt; 0,G26 / (COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],G$16) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],G$16)),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="H39" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],H$16) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],H$16) &gt; 0,H26 / (COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],H$16) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],H$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="I39" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],I$16) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],I$16) &gt; 0,I26 / (COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],I$16) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],I$16)),"N/A")</f>
+        <v>0.40458015267175573</v>
+      </c>
+      <c r="J39" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],J$16) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],J$16) &gt; 0,J26 / (COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],J$16) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],J$16)),"N/A")</f>
+        <v>0.38461538461538464</v>
+      </c>
+      <c r="K39" s="5">
+        <f>IF(COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],K$16) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],K$16) &gt; 0,K26 / (COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],K$16) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],K$16)),"N/A")</f>
+        <v>0.875</v>
+      </c>
+      <c r="L39" s="5" t="str">
+        <f>IF(COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],L$16) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],L$16) &gt; 0,L26 / (COUNTIFS(Table1[Player-1],$B26,Table1[Player-2],L$16) + COUNTIFS(Table1[Player-2],$B26,Table1[Player-1],L$16)),"N/A")</f>
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B41" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="7">
+        <f>COUNTIFS(Table1[Player-1],$B42,Table1[Player-2],C$41) + COUNTIFS(Table1[Player-2],$B42,Table1[Player-1],C$41)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B43" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B43,Table1[Player-2],C$41) + COUNTIFS(Table1[Player-2],$B43,Table1[Player-1],C$41)</f>
+        <v>0</v>
+      </c>
+      <c r="D43" s="7">
+        <f>COUNTIFS(Table1[Player-1],$B43,Table1[Player-2],D$41) + COUNTIFS(Table1[Player-2],$B43,Table1[Player-1],D$41)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B44,Table1[Player-2],C$41) + COUNTIFS(Table1[Player-2],$B44,Table1[Player-1],C$41)</f>
+        <v>2</v>
+      </c>
+      <c r="D44" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B44,Table1[Player-2],D$41) + COUNTIFS(Table1[Player-2],$B44,Table1[Player-1],D$41)</f>
+        <v>6</v>
+      </c>
+      <c r="E44" s="7">
+        <f>COUNTIFS(Table1[Player-1],$B44,Table1[Player-2],E$41) + COUNTIFS(Table1[Player-2],$B44,Table1[Player-1],E$41)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B45,Table1[Player-2],C$41) + COUNTIFS(Table1[Player-2],$B45,Table1[Player-1],C$41)</f>
+        <v>0</v>
+      </c>
+      <c r="D45" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B45,Table1[Player-2],D$41) + COUNTIFS(Table1[Player-2],$B45,Table1[Player-1],D$41)</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B45,Table1[Player-2],E$41) + COUNTIFS(Table1[Player-2],$B45,Table1[Player-1],E$41)</f>
+        <v>27</v>
+      </c>
+      <c r="F45" s="7">
+        <f>COUNTIFS(Table1[Player-1],$B45,Table1[Player-2],F$41) + COUNTIFS(Table1[Player-2],$B45,Table1[Player-1],F$41)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B46" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B46,Table1[Player-2],C$41) + COUNTIFS(Table1[Player-2],$B46,Table1[Player-1],C$41)</f>
+        <v>1</v>
+      </c>
+      <c r="D46" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B46,Table1[Player-2],D$41) + COUNTIFS(Table1[Player-2],$B46,Table1[Player-1],D$41)</f>
+        <v>1</v>
+      </c>
+      <c r="E46" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B46,Table1[Player-2],E$41) + COUNTIFS(Table1[Player-2],$B46,Table1[Player-1],E$41)</f>
+        <v>4</v>
+      </c>
+      <c r="F46" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B46,Table1[Player-2],F$41) + COUNTIFS(Table1[Player-2],$B46,Table1[Player-1],F$41)</f>
+        <v>1</v>
+      </c>
+      <c r="G46" s="7">
+        <f>COUNTIFS(Table1[Player-1],$B46,Table1[Player-2],G$41) + COUNTIFS(Table1[Player-2],$B46,Table1[Player-1],G$41)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B47,Table1[Player-2],C$41) + COUNTIFS(Table1[Player-2],$B47,Table1[Player-1],C$41)</f>
+        <v>0</v>
+      </c>
+      <c r="D47" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B47,Table1[Player-2],D$41) + COUNTIFS(Table1[Player-2],$B47,Table1[Player-1],D$41)</f>
+        <v>0</v>
+      </c>
+      <c r="E47" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B47,Table1[Player-2],E$41) + COUNTIFS(Table1[Player-2],$B47,Table1[Player-1],E$41)</f>
+        <v>5</v>
+      </c>
+      <c r="F47" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B47,Table1[Player-2],F$41) + COUNTIFS(Table1[Player-2],$B47,Table1[Player-1],F$41)</f>
+        <v>0</v>
+      </c>
+      <c r="G47" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B47,Table1[Player-2],G$41) + COUNTIFS(Table1[Player-2],$B47,Table1[Player-1],G$41)</f>
+        <v>0</v>
+      </c>
+      <c r="H47" s="7">
+        <f>COUNTIFS(Table1[Player-1],$B47,Table1[Player-2],H$41) + COUNTIFS(Table1[Player-2],$B47,Table1[Player-1],H$41)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B48,Table1[Player-2],C$41) + COUNTIFS(Table1[Player-2],$B48,Table1[Player-1],C$41)</f>
+        <v>2</v>
+      </c>
+      <c r="D48" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B48,Table1[Player-2],D$41) + COUNTIFS(Table1[Player-2],$B48,Table1[Player-1],D$41)</f>
+        <v>3</v>
+      </c>
+      <c r="E48" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B48,Table1[Player-2],E$41) + COUNTIFS(Table1[Player-2],$B48,Table1[Player-1],E$41)</f>
+        <v>78</v>
+      </c>
+      <c r="F48" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B48,Table1[Player-2],F$41) + COUNTIFS(Table1[Player-2],$B48,Table1[Player-1],F$41)</f>
+        <v>131</v>
+      </c>
+      <c r="G48" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B48,Table1[Player-2],G$41) + COUNTIFS(Table1[Player-2],$B48,Table1[Player-1],G$41)</f>
+        <v>3</v>
+      </c>
+      <c r="H48" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B48,Table1[Player-2],H$41) + COUNTIFS(Table1[Player-2],$B48,Table1[Player-1],H$41)</f>
+        <v>1</v>
+      </c>
+      <c r="I48" s="7">
+        <f>COUNTIFS(Table1[Player-1],$B48,Table1[Player-2],I$41) + COUNTIFS(Table1[Player-2],$B48,Table1[Player-1],I$41)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B49" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B49,Table1[Player-2],C$41) + COUNTIFS(Table1[Player-2],$B49,Table1[Player-1],C$41)</f>
+        <v>0</v>
+      </c>
+      <c r="D49" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B49,Table1[Player-2],D$41) + COUNTIFS(Table1[Player-2],$B49,Table1[Player-1],D$41)</f>
+        <v>1</v>
+      </c>
+      <c r="E49" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B49,Table1[Player-2],E$41) + COUNTIFS(Table1[Player-2],$B49,Table1[Player-1],E$41)</f>
         <v>23</v>
       </c>
-      <c r="G18" s="3">
-        <f>COUNTIFS(Table1[Player-1],G$3,Table1[Player-2],$B18,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],G$3,Table1[Player-1],$B18,Table1[ [ Winner] ], 1)</f>
-        <v>3</v>
-      </c>
-      <c r="H18" s="3">
-        <f>COUNTIFS(Table1[Player-1],H$3,Table1[Player-2],$B18,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],H$3,Table1[Player-1],$B18,Table1[ [ Winner] ], 1)</f>
+      <c r="F49" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B49,Table1[Player-2],F$41) + COUNTIFS(Table1[Player-2],$B49,Table1[Player-1],F$41)</f>
+        <v>12</v>
+      </c>
+      <c r="G49" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B49,Table1[Player-2],G$41) + COUNTIFS(Table1[Player-2],$B49,Table1[Player-1],G$41)</f>
+        <v>1</v>
+      </c>
+      <c r="H49" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B49,Table1[Player-2],H$41) + COUNTIFS(Table1[Player-2],$B49,Table1[Player-1],H$41)</f>
+        <v>0</v>
+      </c>
+      <c r="I49" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B49,Table1[Player-2],I$41) + COUNTIFS(Table1[Player-2],$B49,Table1[Player-1],I$41)</f>
+        <v>126</v>
+      </c>
+      <c r="J49" s="7">
+        <f>COUNTIFS(Table1[Player-1],$B49,Table1[Player-2],J$41) + COUNTIFS(Table1[Player-2],$B49,Table1[Player-1],J$41)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I18" s="3">
-        <f>COUNTIFS(Table1[Player-1],I$3,Table1[Player-2],$B18,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],I$3,Table1[Player-1],$B18,Table1[ [ Winner] ], 1)</f>
-        <v>55</v>
-      </c>
-      <c r="J18" s="3">
-        <f>COUNTIFS(Table1[Player-1],J$3,Table1[Player-2],$B18,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],J$3,Table1[Player-1],$B18,Table1[ [ Winner] ], 1)</f>
-        <v>15</v>
-      </c>
-      <c r="K18" s="3">
-        <f>COUNTIFS(Table1[Player-1],K$3,Table1[Player-2],$B18,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],K$3,Table1[Player-1],$B18,Table1[ [ Winner] ], 1)</f>
-        <v>5</v>
-      </c>
-      <c r="L18" s="3">
-        <f>COUNTIFS(Table1[Player-1],L$3,Table1[Player-2],$B18,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],L$3,Table1[Player-1],$B18,Table1[ [ Winner] ], 1)</f>
+      <c r="C50" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B50,Table1[Player-2],C$41) + COUNTIFS(Table1[Player-2],$B50,Table1[Player-1],C$41)</f>
+        <v>1</v>
+      </c>
+      <c r="D50" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B50,Table1[Player-2],D$41) + COUNTIFS(Table1[Player-2],$B50,Table1[Player-1],D$41)</f>
+        <v>0</v>
+      </c>
+      <c r="E50" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B50,Table1[Player-2],E$41) + COUNTIFS(Table1[Player-2],$B50,Table1[Player-1],E$41)</f>
+        <v>25</v>
+      </c>
+      <c r="F50" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B50,Table1[Player-2],F$41) + COUNTIFS(Table1[Player-2],$B50,Table1[Player-1],F$41)</f>
+        <v>7</v>
+      </c>
+      <c r="G50" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B50,Table1[Player-2],G$41) + COUNTIFS(Table1[Player-2],$B50,Table1[Player-1],G$41)</f>
+        <v>2</v>
+      </c>
+      <c r="H50" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B50,Table1[Player-2],H$41) + COUNTIFS(Table1[Player-2],$B50,Table1[Player-1],H$41)</f>
+        <v>0</v>
+      </c>
+      <c r="I50" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B50,Table1[Player-2],I$41) + COUNTIFS(Table1[Player-2],$B50,Table1[Player-1],I$41)</f>
+        <v>59</v>
+      </c>
+      <c r="J50" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B50,Table1[Player-2],J$41) + COUNTIFS(Table1[Player-2],$B50,Table1[Player-1],J$41)</f>
+        <v>7</v>
+      </c>
+      <c r="K50" s="7">
+        <f>COUNTIFS(Table1[Player-1],$B50,Table1[Player-2],K$41) + COUNTIFS(Table1[Player-2],$B50,Table1[Player-1],K$41)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B51" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B51,Table1[Player-2],C$41) + COUNTIFS(Table1[Player-2],$B51,Table1[Player-1],C$41)</f>
+        <v>1</v>
+      </c>
+      <c r="D51" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B51,Table1[Player-2],D$41) + COUNTIFS(Table1[Player-2],$B51,Table1[Player-1],D$41)</f>
+        <v>1</v>
+      </c>
+      <c r="E51" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B51,Table1[Player-2],E$41) + COUNTIFS(Table1[Player-2],$B51,Table1[Player-1],E$41)</f>
+        <v>31</v>
+      </c>
+      <c r="F51" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B51,Table1[Player-2],F$41) + COUNTIFS(Table1[Player-2],$B51,Table1[Player-1],F$41)</f>
         <v>19</v>
       </c>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B19" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="3">
-        <f>COUNTIFS(Table1[Player-1],C$3,Table1[Player-2],$B19,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],C$3,Table1[Player-1],$B19,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="3">
-        <f>COUNTIFS(Table1[Player-1],D$3,Table1[Player-2],$B19,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],D$3,Table1[Player-1],$B19,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="3">
-        <f>COUNTIFS(Table1[Player-1],E$3,Table1[Player-2],$B19,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],E$3,Table1[Player-1],$B19,Table1[ [ Winner] ], 1)</f>
-        <v>4</v>
-      </c>
-      <c r="F19" s="3">
-        <f>COUNTIFS(Table1[Player-1],F$3,Table1[Player-2],$B19,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],F$3,Table1[Player-1],$B19,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="G19" s="3">
-        <f>COUNTIFS(Table1[Player-1],G$3,Table1[Player-2],$B19,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],G$3,Table1[Player-1],$B19,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="3">
-        <f>COUNTIFS(Table1[Player-1],H$3,Table1[Player-2],$B19,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],H$3,Table1[Player-1],$B19,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="3">
-        <f>COUNTIFS(Table1[Player-1],I$3,Table1[Player-2],$B19,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],I$3,Table1[Player-1],$B19,Table1[ [ Winner] ], 1)</f>
-        <v>4</v>
-      </c>
-      <c r="J19" s="3">
-        <f>COUNTIFS(Table1[Player-1],J$3,Table1[Player-2],$B19,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],J$3,Table1[Player-1],$B19,Table1[ [ Winner] ], 1)</f>
-        <v>6</v>
-      </c>
-      <c r="K19" s="3">
-        <f>COUNTIFS(Table1[Player-1],K$3,Table1[Player-2],$B19,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],K$3,Table1[Player-1],$B19,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="L19" s="3">
-        <f>COUNTIFS(Table1[Player-1],L$3,Table1[Player-2],$B19,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],L$3,Table1[Player-1],$B19,Table1[ [ Winner] ], 1)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="3">
-        <f>COUNTIFS(Table1[Player-1],C$3,Table1[Player-2],$B20,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],C$3,Table1[Player-1],$B20,Table1[ [ Winner] ], 1)</f>
-        <v>1</v>
-      </c>
-      <c r="D20" s="3">
-        <f>COUNTIFS(Table1[Player-1],D$3,Table1[Player-2],$B20,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],D$3,Table1[Player-1],$B20,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <f>COUNTIFS(Table1[Player-1],E$3,Table1[Player-2],$B20,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],E$3,Table1[Player-1],$B20,Table1[ [ Winner] ], 1)</f>
-        <v>1</v>
-      </c>
-      <c r="F20" s="3">
-        <f>COUNTIFS(Table1[Player-1],F$3,Table1[Player-2],$B20,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],F$3,Table1[Player-1],$B20,Table1[ [ Winner] ], 1)</f>
-        <v>1</v>
-      </c>
-      <c r="G20" s="3">
-        <f>COUNTIFS(Table1[Player-1],G$3,Table1[Player-2],$B20,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],G$3,Table1[Player-1],$B20,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <f>COUNTIFS(Table1[Player-1],H$3,Table1[Player-2],$B20,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],H$3,Table1[Player-1],$B20,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <f>COUNTIFS(Table1[Player-1],I$3,Table1[Player-2],$B20,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],I$3,Table1[Player-1],$B20,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <f>COUNTIFS(Table1[Player-1],J$3,Table1[Player-2],$B20,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],J$3,Table1[Player-1],$B20,Table1[ [ Winner] ], 1)</f>
-        <v>1</v>
-      </c>
-      <c r="K20" s="3">
-        <f>COUNTIFS(Table1[Player-1],K$3,Table1[Player-2],$B20,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],K$3,Table1[Player-1],$B20,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <f>COUNTIFS(Table1[Player-1],L$3,Table1[Player-2],$B20,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],L$3,Table1[Player-1],$B20,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="3">
-        <f>COUNTIFS(Table1[Player-1],C$3,Table1[Player-2],$B21,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],C$3,Table1[Player-1],$B21,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="D21" s="3">
-        <f>COUNTIFS(Table1[Player-1],D$3,Table1[Player-2],$B21,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],D$3,Table1[Player-1],$B21,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="3">
-        <f>COUNTIFS(Table1[Player-1],E$3,Table1[Player-2],$B21,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],E$3,Table1[Player-1],$B21,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="3">
-        <f>COUNTIFS(Table1[Player-1],F$3,Table1[Player-2],$B21,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],F$3,Table1[Player-1],$B21,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="G21" s="3">
-        <f>COUNTIFS(Table1[Player-1],G$3,Table1[Player-2],$B21,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],G$3,Table1[Player-1],$B21,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="H21" s="3">
-        <f>COUNTIFS(Table1[Player-1],H$3,Table1[Player-2],$B21,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],H$3,Table1[Player-1],$B21,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <f>COUNTIFS(Table1[Player-1],I$3,Table1[Player-2],$B21,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],I$3,Table1[Player-1],$B21,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="3">
-        <f>COUNTIFS(Table1[Player-1],J$3,Table1[Player-2],$B21,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],J$3,Table1[Player-1],$B21,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="K21" s="3">
-        <f>COUNTIFS(Table1[Player-1],K$3,Table1[Player-2],$B21,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],K$3,Table1[Player-1],$B21,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="L21" s="3">
-        <f>COUNTIFS(Table1[Player-1],L$3,Table1[Player-2],$B21,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],L$3,Table1[Player-1],$B21,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="3">
-        <f>COUNTIFS(Table1[Player-1],C$3,Table1[Player-2],$B22,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],C$3,Table1[Player-1],$B22,Table1[ [ Winner] ], 1)</f>
-        <v>2</v>
-      </c>
-      <c r="D22" s="3">
-        <f>COUNTIFS(Table1[Player-1],D$3,Table1[Player-2],$B22,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],D$3,Table1[Player-1],$B22,Table1[ [ Winner] ], 1)</f>
-        <v>1</v>
-      </c>
-      <c r="E22" s="3">
-        <f>COUNTIFS(Table1[Player-1],E$3,Table1[Player-2],$B22,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],E$3,Table1[Player-1],$B22,Table1[ [ Winner] ], 1)</f>
-        <v>23</v>
-      </c>
-      <c r="F22" s="3">
-        <f>COUNTIFS(Table1[Player-1],F$3,Table1[Player-2],$B22,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],F$3,Table1[Player-1],$B22,Table1[ [ Winner] ], 1)</f>
-        <v>127</v>
-      </c>
-      <c r="G22" s="3">
-        <f>COUNTIFS(Table1[Player-1],G$3,Table1[Player-2],$B22,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],G$3,Table1[Player-1],$B22,Table1[ [ Winner] ], 1)</f>
-        <v>3</v>
-      </c>
-      <c r="H22" s="3">
-        <f>COUNTIFS(Table1[Player-1],H$3,Table1[Player-2],$B22,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],H$3,Table1[Player-1],$B22,Table1[ [ Winner] ], 1)</f>
-        <v>1</v>
-      </c>
-      <c r="I22" s="3">
-        <f>COUNTIFS(Table1[Player-1],I$3,Table1[Player-2],$B22,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],I$3,Table1[Player-1],$B22,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <f>COUNTIFS(Table1[Player-1],J$3,Table1[Player-2],$B22,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],J$3,Table1[Player-1],$B22,Table1[ [ Winner] ], 1)</f>
-        <v>125</v>
-      </c>
-      <c r="K22" s="3">
-        <f>COUNTIFS(Table1[Player-1],K$3,Table1[Player-2],$B22,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],K$3,Table1[Player-1],$B22,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <f>COUNTIFS(Table1[Player-1],L$3,Table1[Player-2],$B22,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],L$3,Table1[Player-1],$B22,Table1[ [ Winner] ], 1)</f>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="3">
-        <f>COUNTIFS(Table1[Player-1],C$3,Table1[Player-2],$B23,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],C$3,Table1[Player-1],$B23,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="D23" s="3">
-        <f>COUNTIFS(Table1[Player-1],D$3,Table1[Player-2],$B23,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],D$3,Table1[Player-1],$B23,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="3">
-        <f>COUNTIFS(Table1[Player-1],E$3,Table1[Player-2],$B23,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],E$3,Table1[Player-1],$B23,Table1[ [ Winner] ], 1)</f>
-        <v>8</v>
-      </c>
-      <c r="F23" s="3">
-        <f>COUNTIFS(Table1[Player-1],F$3,Table1[Player-2],$B23,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],F$3,Table1[Player-1],$B23,Table1[ [ Winner] ], 1)</f>
-        <v>6</v>
-      </c>
-      <c r="G23" s="3">
-        <f>COUNTIFS(Table1[Player-1],G$3,Table1[Player-2],$B23,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],G$3,Table1[Player-1],$B23,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="H23" s="3">
-        <f>COUNTIFS(Table1[Player-1],H$3,Table1[Player-2],$B23,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],H$3,Table1[Player-1],$B23,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="I23" s="3">
-        <f>COUNTIFS(Table1[Player-1],I$3,Table1[Player-2],$B23,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],I$3,Table1[Player-1],$B23,Table1[ [ Winner] ], 1)</f>
-        <v>1</v>
-      </c>
-      <c r="J23" s="3">
-        <f>COUNTIFS(Table1[Player-1],J$3,Table1[Player-2],$B23,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],J$3,Table1[Player-1],$B23,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="K23" s="3">
-        <f>COUNTIFS(Table1[Player-1],K$3,Table1[Player-2],$B23,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],K$3,Table1[Player-1],$B23,Table1[ [ Winner] ], 1)</f>
-        <v>1</v>
-      </c>
-      <c r="L23" s="3">
-        <f>COUNTIFS(Table1[Player-1],L$3,Table1[Player-2],$B23,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],L$3,Table1[Player-1],$B23,Table1[ [ Winner] ], 1)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" s="3">
-        <f>COUNTIFS(Table1[Player-1],C$3,Table1[Player-2],$B24,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],C$3,Table1[Player-1],$B24,Table1[ [ Winner] ], 1)</f>
-        <v>1</v>
-      </c>
-      <c r="D24" s="3">
-        <f>COUNTIFS(Table1[Player-1],D$3,Table1[Player-2],$B24,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],D$3,Table1[Player-1],$B24,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <f>COUNTIFS(Table1[Player-1],E$3,Table1[Player-2],$B24,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],E$3,Table1[Player-1],$B24,Table1[ [ Winner] ], 1)</f>
-        <v>20</v>
-      </c>
-      <c r="F24" s="3">
-        <f>COUNTIFS(Table1[Player-1],F$3,Table1[Player-2],$B24,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],F$3,Table1[Player-1],$B24,Table1[ [ Winner] ], 1)</f>
-        <v>7</v>
-      </c>
-      <c r="G24" s="3">
-        <f>COUNTIFS(Table1[Player-1],G$3,Table1[Player-2],$B24,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],G$3,Table1[Player-1],$B24,Table1[ [ Winner] ], 1)</f>
-        <v>2</v>
-      </c>
-      <c r="H24" s="3">
-        <f>COUNTIFS(Table1[Player-1],H$3,Table1[Player-2],$B24,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],H$3,Table1[Player-1],$B24,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <f>COUNTIFS(Table1[Player-1],I$3,Table1[Player-2],$B24,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],I$3,Table1[Player-1],$B24,Table1[ [ Winner] ], 1)</f>
-        <v>59</v>
-      </c>
-      <c r="J24" s="3">
-        <f>COUNTIFS(Table1[Player-1],J$3,Table1[Player-2],$B24,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],J$3,Table1[Player-1],$B24,Table1[ [ Winner] ], 1)</f>
-        <v>6</v>
-      </c>
-      <c r="K24" s="3">
-        <f>COUNTIFS(Table1[Player-1],K$3,Table1[Player-2],$B24,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],K$3,Table1[Player-1],$B24,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <f>COUNTIFS(Table1[Player-1],L$3,Table1[Player-2],$B24,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],L$3,Table1[Player-1],$B24,Table1[ [ Winner] ], 1)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="3">
-        <f>COUNTIFS(Table1[Player-1],C$3,Table1[Player-2],$B25,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],C$3,Table1[Player-1],$B25,Table1[ [ Winner] ], 1)</f>
-        <v>1</v>
-      </c>
-      <c r="D25" s="3">
-        <f>COUNTIFS(Table1[Player-1],D$3,Table1[Player-2],$B25,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],D$3,Table1[Player-1],$B25,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="3">
-        <f>COUNTIFS(Table1[Player-1],E$3,Table1[Player-2],$B25,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],E$3,Table1[Player-1],$B25,Table1[ [ Winner] ], 1)</f>
-        <v>12</v>
-      </c>
-      <c r="F25" s="3">
-        <f>COUNTIFS(Table1[Player-1],F$3,Table1[Player-2],$B25,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],F$3,Table1[Player-1],$B25,Table1[ [ Winner] ], 1)</f>
-        <v>11</v>
-      </c>
-      <c r="G25" s="3">
-        <f>COUNTIFS(Table1[Player-1],G$3,Table1[Player-2],$B25,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],G$3,Table1[Player-1],$B25,Table1[ [ Winner] ], 1)</f>
-        <v>1</v>
-      </c>
-      <c r="H25" s="3">
-        <f>COUNTIFS(Table1[Player-1],H$3,Table1[Player-2],$B25,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],H$3,Table1[Player-1],$B25,Table1[ [ Winner] ], 1)</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="3">
-        <f>COUNTIFS(Table1[Player-1],I$3,Table1[Player-2],$B25,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],I$3,Table1[Player-1],$B25,Table1[ [ Winner] ], 1)</f>
-        <v>78</v>
-      </c>
-      <c r="J25" s="3">
-        <f>COUNTIFS(Table1[Player-1],J$3,Table1[Player-2],$B25,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],J$3,Table1[Player-1],$B25,Table1[ [ Winner] ], 1)</f>
-        <v>8</v>
-      </c>
-      <c r="K25" s="3">
-        <f>COUNTIFS(Table1[Player-1],K$3,Table1[Player-2],$B25,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],K$3,Table1[Player-1],$B25,Table1[ [ Winner] ], 1)</f>
-        <v>1</v>
-      </c>
-      <c r="L25" s="3">
-        <f>COUNTIFS(Table1[Player-1],L$3,Table1[Player-2],$B25,Table1[ [ Winner] ], 0) + COUNTIFS(Table1[Player-2],L$3,Table1[Player-1],$B25,Table1[ [ Winner] ], 1)</f>
+      <c r="G51" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B51,Table1[Player-2],G$41) + COUNTIFS(Table1[Player-2],$B51,Table1[Player-1],G$41)</f>
+        <v>1</v>
+      </c>
+      <c r="H51" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B51,Table1[Player-2],H$41) + COUNTIFS(Table1[Player-2],$B51,Table1[Player-1],H$41)</f>
+        <v>0</v>
+      </c>
+      <c r="I51" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B51,Table1[Player-2],I$41) + COUNTIFS(Table1[Player-2],$B51,Table1[Player-1],I$41)</f>
+        <v>131</v>
+      </c>
+      <c r="J51" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B51,Table1[Player-2],J$41) + COUNTIFS(Table1[Player-2],$B51,Table1[Player-1],J$41)</f>
+        <v>13</v>
+      </c>
+      <c r="K51" s="6">
+        <f>COUNTIFS(Table1[Player-1],$B51,Table1[Player-2],K$41) + COUNTIFS(Table1[Player-2],$B51,Table1[Player-1],K$41)</f>
+        <v>8</v>
+      </c>
+      <c r="L51" s="7">
+        <f>COUNTIFS(Table1[Player-1],$B51,Table1[Player-2],L$41) + COUNTIFS(Table1[Player-2],$B51,Table1[Player-1],L$41)</f>
         <v>0</v>
       </c>
     </row>

--- a/assets/testing_data/complete_testing.xlsx
+++ b/assets/testing_data/complete_testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anema\OneDrive\Documenten\GitHub\Risky-Game-Development\assets\testing_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2934D10-EA3A-41AB-A2B1-C91C81C847E8}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C90197-8AB2-4DEC-B327-1730FAEA713E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1564" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="35">
   <si>
     <t>Player-1</t>
   </si>
@@ -98,6 +98,45 @@
   </si>
   <si>
     <t>Total number of tests</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>1v1 Wins</t>
+  </si>
+  <si>
+    <t>1v1 Losses</t>
+  </si>
+  <si>
+    <t>2v2 Wins</t>
+  </si>
+  <si>
+    <t>2v2 Losses</t>
+  </si>
+  <si>
+    <t>3v3 Wins</t>
+  </si>
+  <si>
+    <t>3v3 Losses</t>
+  </si>
+  <si>
+    <t>1v1 Wins (%)</t>
+  </si>
+  <si>
+    <t>2v2 Wins (%)</t>
+  </si>
+  <si>
+    <t>3v3 Wins (%)</t>
+  </si>
+  <si>
+    <t>1v1 Games</t>
+  </si>
+  <si>
+    <t>2v2 Games</t>
+  </si>
+  <si>
+    <t>3v3 Games</t>
   </si>
 </sst>
 </file>
@@ -240,7 +279,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -432,6 +471,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -607,7 +664,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
@@ -618,6 +675,10 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="37" borderId="0" xfId="42" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -15826,7 +15887,7 @@
         <v>171135523300</v>
       </c>
       <c r="F706">
-        <f t="shared" ref="F706:F769" si="11">ROUND(E706/60000000000, 1)</f>
+        <f t="shared" ref="F706:F735" si="11">ROUND(E706/60000000000, 1)</f>
         <v>2.9</v>
       </c>
     </row>
@@ -16449,7 +16510,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:L51"/>
+  <dimension ref="A2:M76"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.33203125" customWidth="1"/>
@@ -17500,7 +17561,7 @@
         <v>12</v>
       </c>
       <c r="C30" s="5" t="str">
-        <f>IF(C42 &gt; 0,C17 / (COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],C$16) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],C$16)),"N/A")</f>
+        <f>IF(COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],C$16) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],C$16) &gt; 0,C17 / (COUNTIFS(Table1[Player-1],$B17,Table1[Player-2],C$16) + COUNTIFS(Table1[Player-2],$B17,Table1[Player-1],C$16)),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="D30" s="5" t="str">
@@ -17630,7 +17691,7 @@
         <v>0.38709677419354838</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
@@ -17675,7 +17736,7 @@
         <v>0.57894736842105265</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
         <v>11</v>
       </c>
@@ -17720,7 +17781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="2" t="s">
         <v>10</v>
       </c>
@@ -17765,7 +17826,7 @@
         <v>N/A</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
         <v>8</v>
       </c>
@@ -17810,7 +17871,7 @@
         <v>0.59541984732824427</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
         <v>4</v>
       </c>
@@ -17855,7 +17916,7 @@
         <v>0.61538461538461542</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
         <v>5</v>
       </c>
@@ -17900,7 +17961,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
         <v>13</v>
       </c>
@@ -17945,7 +18006,7 @@
         <v>N/A</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>21</v>
       </c>
@@ -17980,7 +18041,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
         <v>12</v>
       </c>
@@ -17988,8 +18049,12 @@
         <f>COUNTIFS(Table1[Player-1],$B42,Table1[Player-2],C$41) + COUNTIFS(Table1[Player-2],$B42,Table1[Player-1],C$41)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="M42" s="10">
+        <f>SUM(C42:L42)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
         <v>9</v>
       </c>
@@ -18001,8 +18066,12 @@
         <f>COUNTIFS(Table1[Player-1],$B43,Table1[Player-2],D$41) + COUNTIFS(Table1[Player-2],$B43,Table1[Player-1],D$41)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="M43" s="10">
+        <f t="shared" ref="M43:M51" si="0">SUM(C43:L43)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
@@ -18018,8 +18087,12 @@
         <f>COUNTIFS(Table1[Player-1],$B44,Table1[Player-2],E$41) + COUNTIFS(Table1[Player-2],$B44,Table1[Player-1],E$41)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="M44" s="10">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
         <v>6</v>
       </c>
@@ -18039,8 +18112,12 @@
         <f>COUNTIFS(Table1[Player-1],$B45,Table1[Player-2],F$41) + COUNTIFS(Table1[Player-2],$B45,Table1[Player-1],F$41)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="M45" s="10">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B46" s="1" t="s">
         <v>11</v>
       </c>
@@ -18064,8 +18141,12 @@
         <f>COUNTIFS(Table1[Player-1],$B46,Table1[Player-2],G$41) + COUNTIFS(Table1[Player-2],$B46,Table1[Player-1],G$41)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="M46" s="10">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B47" s="2" t="s">
         <v>10</v>
       </c>
@@ -18093,8 +18174,12 @@
         <f>COUNTIFS(Table1[Player-1],$B47,Table1[Player-2],H$41) + COUNTIFS(Table1[Player-2],$B47,Table1[Player-1],H$41)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="M47" s="10">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
         <v>8</v>
       </c>
@@ -18126,8 +18211,12 @@
         <f>COUNTIFS(Table1[Player-1],$B48,Table1[Player-2],I$41) + COUNTIFS(Table1[Player-2],$B48,Table1[Player-1],I$41)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="M48" s="10">
+        <f t="shared" si="0"/>
+        <v>218</v>
+      </c>
+    </row>
+    <row r="49" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
         <v>4</v>
       </c>
@@ -18163,8 +18252,12 @@
         <f>COUNTIFS(Table1[Player-1],$B49,Table1[Player-2],J$41) + COUNTIFS(Table1[Player-2],$B49,Table1[Player-1],J$41)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="M49" s="10">
+        <f t="shared" si="0"/>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="50" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
@@ -18204,8 +18297,12 @@
         <f>COUNTIFS(Table1[Player-1],$B50,Table1[Player-2],K$41) + COUNTIFS(Table1[Player-2],$B50,Table1[Player-1],K$41)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="M50" s="10">
+        <f t="shared" si="0"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
         <v>13</v>
       </c>
@@ -18249,8 +18346,692 @@
         <f>COUNTIFS(Table1[Player-1],$B51,Table1[Player-2],L$41) + COUNTIFS(Table1[Player-2],$B51,Table1[Player-1],L$41)</f>
         <v>0</v>
       </c>
+      <c r="M51" s="10">
+        <f t="shared" si="0"/>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B52" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C52" s="8">
+        <f>SUM(C42:C51)+LOOKUP(C41,$B42:$B51,$M42:$M51)</f>
+        <v>7</v>
+      </c>
+      <c r="D52" s="8">
+        <f t="shared" ref="D52:L52" si="1">SUM(D42:D51)+LOOKUP(D41,$B42:$B51,$M42:$M51)</f>
+        <v>12</v>
+      </c>
+      <c r="E52" s="8">
+        <f t="shared" si="1"/>
+        <v>201</v>
+      </c>
+      <c r="F52" s="8">
+        <f t="shared" si="1"/>
+        <v>197</v>
+      </c>
+      <c r="G52" s="8">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="H52" s="8">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="I52" s="8">
+        <f t="shared" si="1"/>
+        <v>534</v>
+      </c>
+      <c r="J52" s="8">
+        <f t="shared" si="1"/>
+        <v>183</v>
+      </c>
+      <c r="K52" s="8">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+      <c r="L52" s="8">
+        <f t="shared" si="1"/>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C53" s="9"/>
+    </row>
+    <row r="54" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C54" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B55" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B55,Table1[[ Winner]],0,Table1[[ Number of Players]],2) + COUNTIFS(Table1[Player-2],Sheet1!$B55,Table1[[ Winner]],1,Table1[[ Number of Players]],2)</f>
+        <v>7</v>
+      </c>
+      <c r="D55">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B55,Table1[[ Winner]],1,Table1[[ Number of Players]],2) + COUNTIFS(Table1[Player-2],Sheet1!$B55,Table1[[ Winner]],0,Table1[[ Number of Players]],2)</f>
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B55,Table1[[ Winner]],0,Table1[[ Number of Players]],4) + COUNTIFS(Table1[Player-2],Sheet1!$B55,Table1[[ Winner]],1,Table1[[ Number of Players]],4)</f>
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B55,Table1[[ Winner]],1,Table1[[ Number of Players]],4) + COUNTIFS(Table1[Player-2],Sheet1!$B55,Table1[[ Winner]],0,Table1[[ Number of Players]],4)</f>
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B55,Table1[[ Winner]],0,Table1[[ Number of Players]],6) + COUNTIFS(Table1[Player-2],Sheet1!$B55,Table1[[ Winner]],1,Table1[[ Number of Players]],6)</f>
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B55,Table1[[ Winner]],1,Table1[[ Number of Players]],6) + COUNTIFS(Table1[Player-2],Sheet1!$B55,Table1[[ Winner]],0,Table1[[ Number of Players]],6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B56" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B56,Table1[[ Winner]],0,Table1[[ Number of Players]],2) + COUNTIFS(Table1[Player-2],Sheet1!$B56,Table1[[ Winner]],1,Table1[[ Number of Players]],2)</f>
+        <v>1</v>
+      </c>
+      <c r="D56">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B56,Table1[[ Winner]],1,Table1[[ Number of Players]],2) + COUNTIFS(Table1[Player-2],Sheet1!$B56,Table1[[ Winner]],0,Table1[[ Number of Players]],2)</f>
+        <v>11</v>
+      </c>
+      <c r="E56">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B56,Table1[[ Winner]],0,Table1[[ Number of Players]],4) + COUNTIFS(Table1[Player-2],Sheet1!$B56,Table1[[ Winner]],1,Table1[[ Number of Players]],4)</f>
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B56,Table1[[ Winner]],1,Table1[[ Number of Players]],4) + COUNTIFS(Table1[Player-2],Sheet1!$B56,Table1[[ Winner]],0,Table1[[ Number of Players]],4)</f>
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B56,Table1[[ Winner]],0,Table1[[ Number of Players]],6) + COUNTIFS(Table1[Player-2],Sheet1!$B56,Table1[[ Winner]],1,Table1[[ Number of Players]],6)</f>
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B56,Table1[[ Winner]],1,Table1[[ Number of Players]],6) + COUNTIFS(Table1[Player-2],Sheet1!$B56,Table1[[ Winner]],0,Table1[[ Number of Players]],6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B57,Table1[[ Winner]],0,Table1[[ Number of Players]],2) + COUNTIFS(Table1[Player-2],Sheet1!$B57,Table1[[ Winner]],1,Table1[[ Number of Players]],2)</f>
+        <v>53</v>
+      </c>
+      <c r="D57">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B57,Table1[[ Winner]],1,Table1[[ Number of Players]],2) + COUNTIFS(Table1[Player-2],Sheet1!$B57,Table1[[ Winner]],0,Table1[[ Number of Players]],2)</f>
+        <v>93</v>
+      </c>
+      <c r="E57">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B57,Table1[[ Winner]],0,Table1[[ Number of Players]],4) + COUNTIFS(Table1[Player-2],Sheet1!$B57,Table1[[ Winner]],1,Table1[[ Number of Players]],4)</f>
+        <v>12</v>
+      </c>
+      <c r="F57">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B57,Table1[[ Winner]],1,Table1[[ Number of Players]],4) + COUNTIFS(Table1[Player-2],Sheet1!$B57,Table1[[ Winner]],0,Table1[[ Number of Players]],4)</f>
+        <v>17</v>
+      </c>
+      <c r="G57">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B57,Table1[[ Winner]],0,Table1[[ Number of Players]],6) + COUNTIFS(Table1[Player-2],Sheet1!$B57,Table1[[ Winner]],1,Table1[[ Number of Players]],6)</f>
+        <v>9</v>
+      </c>
+      <c r="H57">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B57,Table1[[ Winner]],1,Table1[[ Number of Players]],6) + COUNTIFS(Table1[Player-2],Sheet1!$B57,Table1[[ Winner]],0,Table1[[ Number of Players]],6)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B58,Table1[[ Winner]],0,Table1[[ Number of Players]],2) + COUNTIFS(Table1[Player-2],Sheet1!$B58,Table1[[ Winner]],1,Table1[[ Number of Players]],2)</f>
+        <v>75</v>
+      </c>
+      <c r="D58">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B58,Table1[[ Winner]],1,Table1[[ Number of Players]],2) + COUNTIFS(Table1[Player-2],Sheet1!$B58,Table1[[ Winner]],0,Table1[[ Number of Players]],2)</f>
+        <v>13</v>
+      </c>
+      <c r="E58">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B58,Table1[[ Winner]],0,Table1[[ Number of Players]],4) + COUNTIFS(Table1[Player-2],Sheet1!$B58,Table1[[ Winner]],1,Table1[[ Number of Players]],4)</f>
+        <v>53</v>
+      </c>
+      <c r="F58">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B58,Table1[[ Winner]],1,Table1[[ Number of Players]],4) + COUNTIFS(Table1[Player-2],Sheet1!$B58,Table1[[ Winner]],0,Table1[[ Number of Players]],4)</f>
+        <v>5</v>
+      </c>
+      <c r="G58">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B58,Table1[[ Winner]],0,Table1[[ Number of Players]],6) + COUNTIFS(Table1[Player-2],Sheet1!$B58,Table1[[ Winner]],1,Table1[[ Number of Players]],6)</f>
+        <v>47</v>
+      </c>
+      <c r="H58">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B58,Table1[[ Winner]],1,Table1[[ Number of Players]],6) + COUNTIFS(Table1[Player-2],Sheet1!$B58,Table1[[ Winner]],0,Table1[[ Number of Players]],6)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B59" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B59,Table1[[ Winner]],0,Table1[[ Number of Players]],2) + COUNTIFS(Table1[Player-2],Sheet1!$B59,Table1[[ Winner]],1,Table1[[ Number of Players]],2)</f>
+        <v>10</v>
+      </c>
+      <c r="D59">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B59,Table1[[ Winner]],1,Table1[[ Number of Players]],2) + COUNTIFS(Table1[Player-2],Sheet1!$B59,Table1[[ Winner]],0,Table1[[ Number of Players]],2)</f>
+        <v>4</v>
+      </c>
+      <c r="E59">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B59,Table1[[ Winner]],0,Table1[[ Number of Players]],4) + COUNTIFS(Table1[Player-2],Sheet1!$B59,Table1[[ Winner]],1,Table1[[ Number of Players]],4)</f>
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B59,Table1[[ Winner]],1,Table1[[ Number of Players]],4) + COUNTIFS(Table1[Player-2],Sheet1!$B59,Table1[[ Winner]],0,Table1[[ Number of Players]],4)</f>
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B59,Table1[[ Winner]],0,Table1[[ Number of Players]],6) + COUNTIFS(Table1[Player-2],Sheet1!$B59,Table1[[ Winner]],1,Table1[[ Number of Players]],6)</f>
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B59,Table1[[ Winner]],1,Table1[[ Number of Players]],6) + COUNTIFS(Table1[Player-2],Sheet1!$B59,Table1[[ Winner]],0,Table1[[ Number of Players]],6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B60" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B60,Table1[[ Winner]],0,Table1[[ Number of Players]],2) + COUNTIFS(Table1[Player-2],Sheet1!$B60,Table1[[ Winner]],1,Table1[[ Number of Players]],2)</f>
+        <v>6</v>
+      </c>
+      <c r="D60">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B60,Table1[[ Winner]],1,Table1[[ Number of Players]],2) + COUNTIFS(Table1[Player-2],Sheet1!$B60,Table1[[ Winner]],0,Table1[[ Number of Players]],2)</f>
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B60,Table1[[ Winner]],0,Table1[[ Number of Players]],4) + COUNTIFS(Table1[Player-2],Sheet1!$B60,Table1[[ Winner]],1,Table1[[ Number of Players]],4)</f>
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B60,Table1[[ Winner]],1,Table1[[ Number of Players]],4) + COUNTIFS(Table1[Player-2],Sheet1!$B60,Table1[[ Winner]],0,Table1[[ Number of Players]],4)</f>
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B60,Table1[[ Winner]],0,Table1[[ Number of Players]],6) + COUNTIFS(Table1[Player-2],Sheet1!$B60,Table1[[ Winner]],1,Table1[[ Number of Players]],6)</f>
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B60,Table1[[ Winner]],1,Table1[[ Number of Players]],6) + COUNTIFS(Table1[Player-2],Sheet1!$B60,Table1[[ Winner]],0,Table1[[ Number of Players]],6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B61" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B61,Table1[[ Winner]],0,Table1[[ Number of Players]],2) + COUNTIFS(Table1[Player-2],Sheet1!$B61,Table1[[ Winner]],1,Table1[[ Number of Players]],2)</f>
+        <v>85</v>
+      </c>
+      <c r="D61">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B61,Table1[[ Winner]],1,Table1[[ Number of Players]],2) + COUNTIFS(Table1[Player-2],Sheet1!$B61,Table1[[ Winner]],0,Table1[[ Number of Players]],2)</f>
+        <v>133</v>
+      </c>
+      <c r="E61">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B61,Table1[[ Winner]],0,Table1[[ Number of Players]],4) + COUNTIFS(Table1[Player-2],Sheet1!$B61,Table1[[ Winner]],1,Table1[[ Number of Players]],4)</f>
+        <v>55</v>
+      </c>
+      <c r="F61">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B61,Table1[[ Winner]],1,Table1[[ Number of Players]],4) + COUNTIFS(Table1[Player-2],Sheet1!$B61,Table1[[ Winner]],0,Table1[[ Number of Players]],4)</f>
+        <v>108</v>
+      </c>
+      <c r="G61">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B61,Table1[[ Winner]],0,Table1[[ Number of Players]],6) + COUNTIFS(Table1[Player-2],Sheet1!$B61,Table1[[ Winner]],1,Table1[[ Number of Players]],6)</f>
+        <v>59</v>
+      </c>
+      <c r="H61">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B61,Table1[[ Winner]],1,Table1[[ Number of Players]],6) + COUNTIFS(Table1[Player-2],Sheet1!$B61,Table1[[ Winner]],0,Table1[[ Number of Players]],6)</f>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="62" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B62" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C62">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B62,Table1[[ Winner]],0,Table1[[ Number of Players]],2) + COUNTIFS(Table1[Player-2],Sheet1!$B62,Table1[[ Winner]],1,Table1[[ Number of Players]],2)</f>
+        <v>63</v>
+      </c>
+      <c r="D62">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B62,Table1[[ Winner]],1,Table1[[ Number of Players]],2) + COUNTIFS(Table1[Player-2],Sheet1!$B62,Table1[[ Winner]],0,Table1[[ Number of Players]],2)</f>
+        <v>15</v>
+      </c>
+      <c r="E62">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B62,Table1[[ Winner]],0,Table1[[ Number of Players]],4) + COUNTIFS(Table1[Player-2],Sheet1!$B62,Table1[[ Winner]],1,Table1[[ Number of Players]],4)</f>
+        <v>51</v>
+      </c>
+      <c r="F62">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B62,Table1[[ Winner]],1,Table1[[ Number of Players]],4) + COUNTIFS(Table1[Player-2],Sheet1!$B62,Table1[[ Winner]],0,Table1[[ Number of Players]],4)</f>
+        <v>3</v>
+      </c>
+      <c r="G62">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B62,Table1[[ Winner]],0,Table1[[ Number of Players]],6) + COUNTIFS(Table1[Player-2],Sheet1!$B62,Table1[[ Winner]],1,Table1[[ Number of Players]],6)</f>
+        <v>48</v>
+      </c>
+      <c r="H62">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B62,Table1[[ Winner]],1,Table1[[ Number of Players]],6) + COUNTIFS(Table1[Player-2],Sheet1!$B62,Table1[[ Winner]],0,Table1[[ Number of Players]],6)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B63" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C63">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B63,Table1[[ Winner]],0,Table1[[ Number of Players]],2) + COUNTIFS(Table1[Player-2],Sheet1!$B63,Table1[[ Winner]],1,Table1[[ Number of Players]],2)</f>
+        <v>5</v>
+      </c>
+      <c r="D63">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B63,Table1[[ Winner]],1,Table1[[ Number of Players]],2) + COUNTIFS(Table1[Player-2],Sheet1!$B63,Table1[[ Winner]],0,Table1[[ Number of Players]],2)</f>
+        <v>52</v>
+      </c>
+      <c r="E63">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B63,Table1[[ Winner]],0,Table1[[ Number of Players]],4) + COUNTIFS(Table1[Player-2],Sheet1!$B63,Table1[[ Winner]],1,Table1[[ Number of Players]],4)</f>
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B63,Table1[[ Winner]],1,Table1[[ Number of Players]],4) + COUNTIFS(Table1[Player-2],Sheet1!$B63,Table1[[ Winner]],0,Table1[[ Number of Players]],4)</f>
+        <v>26</v>
+      </c>
+      <c r="G63">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B63,Table1[[ Winner]],0,Table1[[ Number of Players]],6) + COUNTIFS(Table1[Player-2],Sheet1!$B63,Table1[[ Winner]],1,Table1[[ Number of Players]],6)</f>
+        <v>2</v>
+      </c>
+      <c r="H63">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B63,Table1[[ Winner]],1,Table1[[ Number of Players]],6) + COUNTIFS(Table1[Player-2],Sheet1!$B63,Table1[[ Winner]],0,Table1[[ Number of Players]],6)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B64" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B64,Table1[[ Winner]],0,Table1[[ Number of Players]],2) + COUNTIFS(Table1[Player-2],Sheet1!$B64,Table1[[ Winner]],1,Table1[[ Number of Players]],2)</f>
+        <v>56</v>
+      </c>
+      <c r="D64">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B64,Table1[[ Winner]],1,Table1[[ Number of Players]],2) + COUNTIFS(Table1[Player-2],Sheet1!$B64,Table1[[ Winner]],0,Table1[[ Number of Players]],2)</f>
+        <v>40</v>
+      </c>
+      <c r="E64">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B64,Table1[[ Winner]],0,Table1[[ Number of Players]],4) + COUNTIFS(Table1[Player-2],Sheet1!$B64,Table1[[ Winner]],1,Table1[[ Number of Players]],4)</f>
+        <v>23</v>
+      </c>
+      <c r="F64">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B64,Table1[[ Winner]],1,Table1[[ Number of Players]],4) + COUNTIFS(Table1[Player-2],Sheet1!$B64,Table1[[ Winner]],0,Table1[[ Number of Players]],4)</f>
+        <v>35</v>
+      </c>
+      <c r="G64">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B64,Table1[[ Winner]],0,Table1[[ Number of Players]],6) + COUNTIFS(Table1[Player-2],Sheet1!$B64,Table1[[ Winner]],1,Table1[[ Number of Players]],6)</f>
+        <v>14</v>
+      </c>
+      <c r="H64">
+        <f>COUNTIFS(Table1[Player-1],Sheet1!$B64,Table1[[ Winner]],1,Table1[[ Number of Players]],6) + COUNTIFS(Table1[Player-2],Sheet1!$B64,Table1[[ Winner]],0,Table1[[ Number of Players]],6)</f>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C66" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B67" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" s="11">
+        <f>IF(F67 &gt; 0,C55 / F67,"N/A")</f>
+        <v>1</v>
+      </c>
+      <c r="D67" s="5" t="str">
+        <f>IF(G67 &gt; 0,E55 / G67,"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="E67" s="5" t="str">
+        <f>IF(H67 &gt; 0,G55 / H67,"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="F67">
+        <f>SUM(C55:D55)</f>
+        <v>7</v>
+      </c>
+      <c r="G67">
+        <f>SUM(E55:F55)</f>
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <f>SUM(G55:H55)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B68" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" s="11">
+        <f t="shared" ref="C68:C76" si="2">IF(F68 &gt; 0,C56 / F68,"N/A")</f>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="D68" s="5" t="str">
+        <f t="shared" ref="D68:D76" si="3">IF(G68 &gt; 0,E56 / G68,"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="E68" s="5" t="str">
+        <f t="shared" ref="E68:E76" si="4">IF(H68 &gt; 0,G56 / H68,"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="F68">
+        <f t="shared" ref="F68:F76" si="5">SUM(C56:D56)</f>
+        <v>12</v>
+      </c>
+      <c r="G68">
+        <f t="shared" ref="G68:G76" si="6">SUM(E56:F56)</f>
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <f t="shared" ref="H68:H76" si="7">SUM(G56:H56)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="11">
+        <f t="shared" si="2"/>
+        <v>0.36301369863013699</v>
+      </c>
+      <c r="D69" s="11">
+        <f t="shared" si="3"/>
+        <v>0.41379310344827586</v>
+      </c>
+      <c r="E69" s="11">
+        <f t="shared" si="4"/>
+        <v>0.34615384615384615</v>
+      </c>
+      <c r="F69">
+        <f t="shared" si="5"/>
+        <v>146</v>
+      </c>
+      <c r="G69">
+        <f t="shared" si="6"/>
+        <v>29</v>
+      </c>
+      <c r="H69">
+        <f t="shared" si="7"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="11">
+        <f t="shared" si="2"/>
+        <v>0.85227272727272729</v>
+      </c>
+      <c r="D70" s="11">
+        <f t="shared" si="3"/>
+        <v>0.91379310344827591</v>
+      </c>
+      <c r="E70" s="11">
+        <f t="shared" si="4"/>
+        <v>0.92156862745098034</v>
+      </c>
+      <c r="F70">
+        <f t="shared" si="5"/>
+        <v>88</v>
+      </c>
+      <c r="G70">
+        <f t="shared" si="6"/>
+        <v>58</v>
+      </c>
+      <c r="H70">
+        <f t="shared" si="7"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B71" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" s="11">
+        <f t="shared" si="2"/>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="D71" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>N/A</v>
+      </c>
+      <c r="E71" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>N/A</v>
+      </c>
+      <c r="F71">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="G71">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B72" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="11">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="D72" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>N/A</v>
+      </c>
+      <c r="E72" s="5" t="str">
+        <f t="shared" si="4"/>
+        <v>N/A</v>
+      </c>
+      <c r="F72">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="G72">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B73" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73" s="11">
+        <f t="shared" si="2"/>
+        <v>0.38990825688073394</v>
+      </c>
+      <c r="D73" s="11">
+        <f t="shared" si="3"/>
+        <v>0.33742331288343558</v>
+      </c>
+      <c r="E73" s="11">
+        <f t="shared" si="4"/>
+        <v>0.38562091503267976</v>
+      </c>
+      <c r="F73">
+        <f t="shared" si="5"/>
+        <v>218</v>
+      </c>
+      <c r="G73">
+        <f t="shared" si="6"/>
+        <v>163</v>
+      </c>
+      <c r="H73">
+        <f t="shared" si="7"/>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B74" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C74" s="11">
+        <f t="shared" si="2"/>
+        <v>0.80769230769230771</v>
+      </c>
+      <c r="D74" s="11">
+        <f t="shared" si="3"/>
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="E74" s="11">
+        <f t="shared" si="4"/>
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="F74">
+        <f t="shared" si="5"/>
+        <v>78</v>
+      </c>
+      <c r="G74">
+        <f t="shared" si="6"/>
+        <v>54</v>
+      </c>
+      <c r="H74">
+        <f t="shared" si="7"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="75" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B75" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C75" s="11">
+        <f t="shared" si="2"/>
+        <v>8.771929824561403E-2</v>
+      </c>
+      <c r="D75" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E75" s="11">
+        <f t="shared" si="4"/>
+        <v>7.6923076923076927E-2</v>
+      </c>
+      <c r="F75">
+        <f t="shared" si="5"/>
+        <v>57</v>
+      </c>
+      <c r="G75">
+        <f t="shared" si="6"/>
+        <v>26</v>
+      </c>
+      <c r="H75">
+        <f t="shared" si="7"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="76" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B76" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C76" s="11">
+        <f t="shared" si="2"/>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D76" s="11">
+        <f t="shared" si="3"/>
+        <v>0.39655172413793105</v>
+      </c>
+      <c r="E76" s="11">
+        <f t="shared" si="4"/>
+        <v>0.27450980392156865</v>
+      </c>
+      <c r="F76">
+        <f t="shared" si="5"/>
+        <v>96</v>
+      </c>
+      <c r="G76">
+        <f t="shared" si="6"/>
+        <v>58</v>
+      </c>
+      <c r="H76">
+        <f t="shared" si="7"/>
+        <v>51</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="F67:H76">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
 </worksheet>
